--- a/DPET SALES INVENTORY.xlsx
+++ b/DPET SALES INVENTORY.xlsx
@@ -1,14 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Doyen\Desktop\InventoryManagementSystem\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <bookViews>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7500"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="Sheet1" sheetId="1" r:id="rId5"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName hidden="1" localSheetId="0" name="_xlnm._FilterDatabase">Sheet1!$B$2:$K$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$B$2:$K$10</definedName>
   </definedNames>
-  <calcPr/>
+  <calcPr calcId="162913"/>
 </workbook>
 </file>
 
@@ -63,23 +72,25 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="mmm d, yyyy"/>
+    <numFmt numFmtId="164" formatCode="mmm\ d\,\ yyyy"/>
   </numFmts>
-  <fonts count="3">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Verdana"/>
     </font>
     <font>
       <b/>
+      <sz val="10"/>
       <color rgb="FFFFFFFF"/>
       <name val="Verdana"/>
     </font>
@@ -89,7 +100,7 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -99,7 +110,13 @@
     </fill>
   </fills>
   <borders count="2">
-    <border/>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
     <border>
       <left style="thin">
         <color rgb="FFFFFFFF"/>
@@ -113,46 +130,60 @@
       <bottom style="thin">
         <color rgb="FFFFFFFF"/>
       </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+  <cellXfs count="12">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="3" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="3" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
 </file>
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
@@ -160,7 +191,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -350,29 +381,32 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:L1000"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="1.75"/>
-    <col customWidth="1" min="2" max="2" width="78.75"/>
-    <col customWidth="1" min="3" max="3" width="15.38"/>
-    <col customWidth="1" min="4" max="4" width="20.88"/>
-    <col customWidth="1" min="7" max="7" width="19.63"/>
-    <col customWidth="1" min="8" max="8" width="16.38"/>
-    <col customWidth="1" min="9" max="9" width="25.13"/>
-    <col customWidth="1" min="10" max="10" width="22.0"/>
-    <col customWidth="1" min="11" max="11" width="22.13"/>
-    <col customWidth="1" min="12" max="12" width="2.0"/>
+    <col min="1" max="1" width="1.7109375" customWidth="1"/>
+    <col min="2" max="2" width="78.7109375" customWidth="1"/>
+    <col min="3" max="3" width="15.42578125" customWidth="1"/>
+    <col min="4" max="4" width="20.85546875" customWidth="1"/>
+    <col min="7" max="7" width="19.5703125" customWidth="1"/>
+    <col min="8" max="8" width="16.42578125" customWidth="1"/>
+    <col min="9" max="9" width="25.140625" customWidth="1"/>
+    <col min="10" max="10" width="22" customWidth="1"/>
+    <col min="11" max="11" width="22.140625" customWidth="1"/>
+    <col min="12" max="12" width="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30.75" customHeight="1">
+    <row r="1" spans="1:12" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -386,7 +420,7 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
     </row>
-    <row r="2" ht="55.5" customHeight="1">
+    <row r="2" spans="1:12" ht="55.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="1"/>
       <c r="B2" s="2" t="s">
         <v>0</v>
@@ -420,28 +454,28 @@
       </c>
       <c r="L2" s="1"/>
     </row>
-    <row r="3" ht="19.5" customHeight="1">
+    <row r="3" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="1"/>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="4">
-        <v>46204.0</v>
+      <c r="C3" s="10">
+        <v>46204</v>
       </c>
-      <c r="D3" s="5">
-        <v>80000.0</v>
+      <c r="D3" s="11">
+        <v>80000</v>
       </c>
-      <c r="E3" s="3">
-        <v>123.0</v>
+      <c r="E3" s="8">
+        <v>123</v>
       </c>
       <c r="F3" s="3">
-        <v>456.0</v>
+        <v>456</v>
       </c>
       <c r="G3" s="4">
-        <v>46205.0</v>
+        <v>46205</v>
       </c>
       <c r="H3" s="5">
-        <v>20000.0</v>
+        <v>20000</v>
       </c>
       <c r="I3" s="6">
         <f>D3-H3</f>
@@ -453,19 +487,23 @@
       <c r="K3" s="3"/>
       <c r="L3" s="1"/>
     </row>
-    <row r="4" ht="19.5" customHeight="1">
+    <row r="4" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="1"/>
+      <c r="B4" s="9"/>
+      <c r="C4" s="9"/>
+      <c r="D4" s="9"/>
+      <c r="E4" s="9"/>
       <c r="F4" s="3">
-        <v>457.0</v>
+        <v>457</v>
       </c>
       <c r="G4" s="4">
-        <v>46206.0</v>
+        <v>46206</v>
       </c>
       <c r="H4" s="5">
-        <v>20000.0</v>
+        <v>20000</v>
       </c>
       <c r="I4" s="6">
-        <f t="shared" ref="I4:I6" si="1">I3-H4</f>
+        <f t="shared" ref="I4:I6" si="0">I3-H4</f>
         <v>40000</v>
       </c>
       <c r="J4" s="3" t="s">
@@ -474,19 +512,23 @@
       <c r="K4" s="7"/>
       <c r="L4" s="1"/>
     </row>
-    <row r="5" ht="19.5" customHeight="1">
+    <row r="5" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="1"/>
+      <c r="B5" s="9"/>
+      <c r="C5" s="9"/>
+      <c r="D5" s="9"/>
+      <c r="E5" s="9"/>
       <c r="F5" s="3">
-        <v>458.0</v>
+        <v>458</v>
       </c>
       <c r="G5" s="4">
-        <v>46207.0</v>
+        <v>46207</v>
       </c>
       <c r="H5" s="5">
-        <v>20000.0</v>
+        <v>20000</v>
       </c>
       <c r="I5" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>20000</v>
       </c>
       <c r="J5" s="3" t="s">
@@ -495,19 +537,23 @@
       <c r="K5" s="7"/>
       <c r="L5" s="1"/>
     </row>
-    <row r="6" ht="19.5" customHeight="1">
+    <row r="6" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="1"/>
+      <c r="B6" s="9"/>
+      <c r="C6" s="9"/>
+      <c r="D6" s="9"/>
+      <c r="E6" s="9"/>
       <c r="F6" s="3">
-        <v>459.0</v>
+        <v>459</v>
       </c>
       <c r="G6" s="4">
-        <v>46209.0</v>
+        <v>46209</v>
       </c>
       <c r="H6" s="5">
-        <v>20000.0</v>
+        <v>20000</v>
       </c>
       <c r="I6" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="J6" s="3" t="s">
@@ -516,31 +562,31 @@
       <c r="K6" s="7"/>
       <c r="L6" s="1"/>
     </row>
-    <row r="7" ht="19.5" customHeight="1">
+    <row r="7" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="1"/>
       <c r="B7" s="3" t="s">
         <v>13</v>
       </c>
       <c r="C7" s="4">
-        <v>46204.0</v>
+        <v>46204</v>
       </c>
       <c r="D7" s="5">
-        <v>35000.0</v>
+        <v>35000</v>
       </c>
       <c r="E7" s="3">
-        <v>124.0</v>
+        <v>124</v>
       </c>
       <c r="F7" s="3">
-        <v>460.0</v>
+        <v>460</v>
       </c>
       <c r="G7" s="4">
-        <v>46204.0</v>
+        <v>46204</v>
       </c>
       <c r="H7" s="5">
-        <v>35000.0</v>
+        <v>35000</v>
       </c>
       <c r="I7" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="J7" s="3" t="s">
         <v>11</v>
@@ -548,28 +594,28 @@
       <c r="K7" s="7"/>
       <c r="L7" s="1"/>
     </row>
-    <row r="8" ht="19.5" customHeight="1">
+    <row r="8" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="1"/>
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="C8" s="4">
-        <v>46204.0</v>
+      <c r="C8" s="10">
+        <v>46204</v>
       </c>
-      <c r="D8" s="5">
-        <v>40000.0</v>
+      <c r="D8" s="11">
+        <v>40000</v>
       </c>
-      <c r="E8" s="3">
-        <v>125.0</v>
+      <c r="E8" s="8">
+        <v>125</v>
       </c>
       <c r="F8" s="3">
-        <v>461.0</v>
+        <v>461</v>
       </c>
       <c r="G8" s="4">
-        <v>46205.0</v>
+        <v>46205</v>
       </c>
       <c r="H8" s="5">
-        <v>20000.0</v>
+        <v>20000</v>
       </c>
       <c r="I8" s="6">
         <f>D8-H8</f>
@@ -581,16 +627,20 @@
       <c r="K8" s="7"/>
       <c r="L8" s="1"/>
     </row>
-    <row r="9" ht="19.5" customHeight="1">
+    <row r="9" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="1"/>
+      <c r="B9" s="9"/>
+      <c r="C9" s="9"/>
+      <c r="D9" s="9"/>
+      <c r="E9" s="9"/>
       <c r="F9" s="3">
-        <v>461.0</v>
+        <v>462</v>
       </c>
       <c r="G9" s="4">
-        <v>46207.0</v>
+        <v>46207</v>
       </c>
       <c r="H9" s="5">
-        <v>20000.0</v>
+        <v>20000</v>
       </c>
       <c r="I9" s="6">
         <f>I8-H9</f>
@@ -602,7 +652,7 @@
       <c r="K9" s="7"/>
       <c r="L9" s="1"/>
     </row>
-    <row r="10" ht="19.5" customHeight="1">
+    <row r="10" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="1"/>
       <c r="B10" s="3"/>
       <c r="C10" s="7"/>
@@ -616,7 +666,7 @@
       <c r="K10" s="7"/>
       <c r="L10" s="1"/>
     </row>
-    <row r="11" ht="19.5" customHeight="1">
+    <row r="11" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="1"/>
       <c r="B11" s="7"/>
       <c r="C11" s="4"/>
@@ -630,7 +680,7 @@
       <c r="K11" s="7"/>
       <c r="L11" s="1"/>
     </row>
-    <row r="12" ht="19.5" customHeight="1">
+    <row r="12" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="1"/>
       <c r="B12" s="7"/>
       <c r="C12" s="7"/>
@@ -644,7 +694,7 @@
       <c r="K12" s="7"/>
       <c r="L12" s="1"/>
     </row>
-    <row r="13" ht="19.5" customHeight="1">
+    <row r="13" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="1"/>
       <c r="B13" s="7"/>
       <c r="C13" s="7"/>
@@ -658,7 +708,7 @@
       <c r="K13" s="7"/>
       <c r="L13" s="1"/>
     </row>
-    <row r="14" ht="19.5" customHeight="1">
+    <row r="14" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="1"/>
       <c r="B14" s="7"/>
       <c r="C14" s="7"/>
@@ -672,7 +722,7 @@
       <c r="K14" s="7"/>
       <c r="L14" s="1"/>
     </row>
-    <row r="15" ht="19.5" customHeight="1">
+    <row r="15" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="1"/>
       <c r="B15" s="7"/>
       <c r="C15" s="7"/>
@@ -686,7 +736,7 @@
       <c r="K15" s="7"/>
       <c r="L15" s="1"/>
     </row>
-    <row r="16" ht="19.5" customHeight="1">
+    <row r="16" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="1"/>
       <c r="B16" s="7"/>
       <c r="C16" s="7"/>
@@ -700,7 +750,7 @@
       <c r="K16" s="7"/>
       <c r="L16" s="1"/>
     </row>
-    <row r="17" ht="19.5" customHeight="1">
+    <row r="17" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="1"/>
       <c r="B17" s="7"/>
       <c r="C17" s="7"/>
@@ -714,7 +764,7 @@
       <c r="K17" s="7"/>
       <c r="L17" s="1"/>
     </row>
-    <row r="18" ht="19.5" customHeight="1">
+    <row r="18" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="1"/>
       <c r="B18" s="7"/>
       <c r="C18" s="7"/>
@@ -728,7 +778,7 @@
       <c r="K18" s="7"/>
       <c r="L18" s="1"/>
     </row>
-    <row r="19" ht="19.5" customHeight="1">
+    <row r="19" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="1"/>
       <c r="B19" s="7"/>
       <c r="C19" s="7"/>
@@ -742,7 +792,7 @@
       <c r="K19" s="7"/>
       <c r="L19" s="1"/>
     </row>
-    <row r="20" ht="19.5" customHeight="1">
+    <row r="20" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="1"/>
       <c r="B20" s="7"/>
       <c r="C20" s="7"/>
@@ -756,7 +806,7 @@
       <c r="K20" s="7"/>
       <c r="L20" s="1"/>
     </row>
-    <row r="21" ht="19.5" customHeight="1">
+    <row r="21" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="1"/>
       <c r="B21" s="7"/>
       <c r="C21" s="7"/>
@@ -770,7 +820,7 @@
       <c r="K21" s="7"/>
       <c r="L21" s="1"/>
     </row>
-    <row r="22" ht="19.5" customHeight="1">
+    <row r="22" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="1"/>
       <c r="B22" s="7"/>
       <c r="C22" s="7"/>
@@ -784,7 +834,7 @@
       <c r="K22" s="7"/>
       <c r="L22" s="1"/>
     </row>
-    <row r="23" ht="19.5" customHeight="1">
+    <row r="23" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="1"/>
       <c r="B23" s="7"/>
       <c r="C23" s="7"/>
@@ -798,7 +848,7 @@
       <c r="K23" s="7"/>
       <c r="L23" s="1"/>
     </row>
-    <row r="24" ht="19.5" customHeight="1">
+    <row r="24" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="1"/>
       <c r="B24" s="7"/>
       <c r="C24" s="7"/>
@@ -812,7 +862,7 @@
       <c r="K24" s="7"/>
       <c r="L24" s="1"/>
     </row>
-    <row r="25" ht="19.5" customHeight="1">
+    <row r="25" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="1"/>
       <c r="B25" s="7"/>
       <c r="C25" s="7"/>
@@ -826,7 +876,7 @@
       <c r="K25" s="7"/>
       <c r="L25" s="1"/>
     </row>
-    <row r="26" ht="19.5" customHeight="1">
+    <row r="26" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="1"/>
       <c r="B26" s="7"/>
       <c r="C26" s="7"/>
@@ -840,7 +890,7 @@
       <c r="K26" s="7"/>
       <c r="L26" s="1"/>
     </row>
-    <row r="27" ht="19.5" customHeight="1">
+    <row r="27" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="1"/>
       <c r="B27" s="7"/>
       <c r="C27" s="7"/>
@@ -854,7 +904,7 @@
       <c r="K27" s="7"/>
       <c r="L27" s="1"/>
     </row>
-    <row r="28" ht="19.5" customHeight="1">
+    <row r="28" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="1"/>
       <c r="B28" s="7"/>
       <c r="C28" s="7"/>
@@ -868,7 +918,7 @@
       <c r="K28" s="7"/>
       <c r="L28" s="1"/>
     </row>
-    <row r="29" ht="19.5" customHeight="1">
+    <row r="29" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="1"/>
       <c r="B29" s="7"/>
       <c r="C29" s="7"/>
@@ -882,7 +932,7 @@
       <c r="K29" s="7"/>
       <c r="L29" s="1"/>
     </row>
-    <row r="30" ht="19.5" customHeight="1">
+    <row r="30" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="1"/>
       <c r="B30" s="7"/>
       <c r="C30" s="7"/>
@@ -896,7 +946,7 @@
       <c r="K30" s="7"/>
       <c r="L30" s="1"/>
     </row>
-    <row r="31" ht="19.5" customHeight="1">
+    <row r="31" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="1"/>
       <c r="B31" s="7"/>
       <c r="C31" s="7"/>
@@ -910,7 +960,7 @@
       <c r="K31" s="7"/>
       <c r="L31" s="1"/>
     </row>
-    <row r="32" ht="19.5" customHeight="1">
+    <row r="32" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="1"/>
       <c r="B32" s="7"/>
       <c r="C32" s="7"/>
@@ -924,7 +974,7 @@
       <c r="K32" s="7"/>
       <c r="L32" s="1"/>
     </row>
-    <row r="33" ht="19.5" customHeight="1">
+    <row r="33" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="1"/>
       <c r="B33" s="7"/>
       <c r="C33" s="7"/>
@@ -938,7 +988,7 @@
       <c r="K33" s="7"/>
       <c r="L33" s="1"/>
     </row>
-    <row r="34" ht="19.5" customHeight="1">
+    <row r="34" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="1"/>
       <c r="B34" s="7"/>
       <c r="C34" s="7"/>
@@ -952,7 +1002,7 @@
       <c r="K34" s="7"/>
       <c r="L34" s="1"/>
     </row>
-    <row r="35" ht="19.5" customHeight="1">
+    <row r="35" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="1"/>
       <c r="B35" s="7"/>
       <c r="C35" s="7"/>
@@ -966,7 +1016,7 @@
       <c r="K35" s="7"/>
       <c r="L35" s="1"/>
     </row>
-    <row r="36" ht="19.5" customHeight="1">
+    <row r="36" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="1"/>
       <c r="B36" s="7"/>
       <c r="C36" s="7"/>
@@ -980,7 +1030,7 @@
       <c r="K36" s="7"/>
       <c r="L36" s="1"/>
     </row>
-    <row r="37" ht="19.5" customHeight="1">
+    <row r="37" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="1"/>
       <c r="B37" s="7"/>
       <c r="C37" s="7"/>
@@ -994,7 +1044,7 @@
       <c r="K37" s="7"/>
       <c r="L37" s="1"/>
     </row>
-    <row r="38" ht="19.5" customHeight="1">
+    <row r="38" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="1"/>
       <c r="B38" s="7"/>
       <c r="C38" s="7"/>
@@ -1008,7 +1058,7 @@
       <c r="K38" s="7"/>
       <c r="L38" s="1"/>
     </row>
-    <row r="39" ht="19.5" customHeight="1">
+    <row r="39" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="1"/>
       <c r="B39" s="7"/>
       <c r="C39" s="7"/>
@@ -1022,7 +1072,7 @@
       <c r="K39" s="7"/>
       <c r="L39" s="1"/>
     </row>
-    <row r="40" ht="19.5" customHeight="1">
+    <row r="40" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="1"/>
       <c r="B40" s="7"/>
       <c r="C40" s="7"/>
@@ -1036,7 +1086,7 @@
       <c r="K40" s="7"/>
       <c r="L40" s="1"/>
     </row>
-    <row r="41" ht="19.5" customHeight="1">
+    <row r="41" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="1"/>
       <c r="B41" s="7"/>
       <c r="C41" s="7"/>
@@ -1050,7 +1100,7 @@
       <c r="K41" s="7"/>
       <c r="L41" s="1"/>
     </row>
-    <row r="42" ht="19.5" customHeight="1">
+    <row r="42" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="1"/>
       <c r="B42" s="7"/>
       <c r="C42" s="7"/>
@@ -1064,7 +1114,7 @@
       <c r="K42" s="7"/>
       <c r="L42" s="1"/>
     </row>
-    <row r="43" ht="19.5" customHeight="1">
+    <row r="43" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="1"/>
       <c r="B43" s="7"/>
       <c r="C43" s="7"/>
@@ -1078,7 +1128,7 @@
       <c r="K43" s="7"/>
       <c r="L43" s="1"/>
     </row>
-    <row r="44" ht="19.5" customHeight="1">
+    <row r="44" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="1"/>
       <c r="B44" s="7"/>
       <c r="C44" s="7"/>
@@ -1092,7 +1142,7 @@
       <c r="K44" s="7"/>
       <c r="L44" s="1"/>
     </row>
-    <row r="45" ht="19.5" customHeight="1">
+    <row r="45" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="1"/>
       <c r="B45" s="7"/>
       <c r="C45" s="7"/>
@@ -1106,7 +1156,7 @@
       <c r="K45" s="7"/>
       <c r="L45" s="1"/>
     </row>
-    <row r="46" ht="19.5" customHeight="1">
+    <row r="46" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="1"/>
       <c r="B46" s="7"/>
       <c r="C46" s="7"/>
@@ -1120,7 +1170,7 @@
       <c r="K46" s="7"/>
       <c r="L46" s="1"/>
     </row>
-    <row r="47" ht="19.5" customHeight="1">
+    <row r="47" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="1"/>
       <c r="B47" s="7"/>
       <c r="C47" s="7"/>
@@ -1134,7 +1184,7 @@
       <c r="K47" s="7"/>
       <c r="L47" s="1"/>
     </row>
-    <row r="48" ht="19.5" customHeight="1">
+    <row r="48" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="1"/>
       <c r="B48" s="7"/>
       <c r="C48" s="7"/>
@@ -1148,7 +1198,7 @@
       <c r="K48" s="7"/>
       <c r="L48" s="1"/>
     </row>
-    <row r="49" ht="19.5" customHeight="1">
+    <row r="49" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="1"/>
       <c r="B49" s="7"/>
       <c r="C49" s="7"/>
@@ -1162,7 +1212,7 @@
       <c r="K49" s="7"/>
       <c r="L49" s="1"/>
     </row>
-    <row r="50" ht="19.5" customHeight="1">
+    <row r="50" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="1"/>
       <c r="B50" s="7"/>
       <c r="C50" s="7"/>
@@ -1176,7 +1226,7 @@
       <c r="K50" s="7"/>
       <c r="L50" s="1"/>
     </row>
-    <row r="51" ht="19.5" customHeight="1">
+    <row r="51" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="1"/>
       <c r="B51" s="7"/>
       <c r="C51" s="7"/>
@@ -1190,7 +1240,7 @@
       <c r="K51" s="7"/>
       <c r="L51" s="1"/>
     </row>
-    <row r="52" ht="19.5" customHeight="1">
+    <row r="52" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="1"/>
       <c r="B52" s="7"/>
       <c r="C52" s="7"/>
@@ -1204,7 +1254,7 @@
       <c r="K52" s="7"/>
       <c r="L52" s="1"/>
     </row>
-    <row r="53" ht="19.5" customHeight="1">
+    <row r="53" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="1"/>
       <c r="B53" s="7"/>
       <c r="C53" s="7"/>
@@ -1218,7 +1268,7 @@
       <c r="K53" s="7"/>
       <c r="L53" s="1"/>
     </row>
-    <row r="54" ht="19.5" customHeight="1">
+    <row r="54" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="1"/>
       <c r="B54" s="7"/>
       <c r="C54" s="7"/>
@@ -1232,7 +1282,7 @@
       <c r="K54" s="7"/>
       <c r="L54" s="1"/>
     </row>
-    <row r="55" ht="19.5" customHeight="1">
+    <row r="55" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="1"/>
       <c r="B55" s="7"/>
       <c r="C55" s="7"/>
@@ -1246,7 +1296,7 @@
       <c r="K55" s="7"/>
       <c r="L55" s="1"/>
     </row>
-    <row r="56" ht="19.5" customHeight="1">
+    <row r="56" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="1"/>
       <c r="B56" s="7"/>
       <c r="C56" s="7"/>
@@ -1260,7 +1310,7 @@
       <c r="K56" s="7"/>
       <c r="L56" s="1"/>
     </row>
-    <row r="57" ht="19.5" customHeight="1">
+    <row r="57" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="1"/>
       <c r="B57" s="7"/>
       <c r="C57" s="7"/>
@@ -1274,7 +1324,7 @@
       <c r="K57" s="7"/>
       <c r="L57" s="1"/>
     </row>
-    <row r="58" ht="19.5" customHeight="1">
+    <row r="58" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="1"/>
       <c r="B58" s="7"/>
       <c r="C58" s="7"/>
@@ -1288,7 +1338,7 @@
       <c r="K58" s="7"/>
       <c r="L58" s="1"/>
     </row>
-    <row r="59" ht="19.5" customHeight="1">
+    <row r="59" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="1"/>
       <c r="B59" s="7"/>
       <c r="C59" s="7"/>
@@ -1302,7 +1352,7 @@
       <c r="K59" s="7"/>
       <c r="L59" s="1"/>
     </row>
-    <row r="60" ht="19.5" customHeight="1">
+    <row r="60" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="1"/>
       <c r="B60" s="7"/>
       <c r="C60" s="7"/>
@@ -1316,7 +1366,7 @@
       <c r="K60" s="7"/>
       <c r="L60" s="1"/>
     </row>
-    <row r="61" ht="19.5" customHeight="1">
+    <row r="61" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="1"/>
       <c r="B61" s="7"/>
       <c r="C61" s="7"/>
@@ -1330,7 +1380,7 @@
       <c r="K61" s="7"/>
       <c r="L61" s="1"/>
     </row>
-    <row r="62" ht="19.5" customHeight="1">
+    <row r="62" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="1"/>
       <c r="B62" s="7"/>
       <c r="C62" s="7"/>
@@ -1344,7 +1394,7 @@
       <c r="K62" s="7"/>
       <c r="L62" s="1"/>
     </row>
-    <row r="63" ht="19.5" customHeight="1">
+    <row r="63" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="1"/>
       <c r="B63" s="7"/>
       <c r="C63" s="7"/>
@@ -1358,7 +1408,7 @@
       <c r="K63" s="7"/>
       <c r="L63" s="1"/>
     </row>
-    <row r="64" ht="19.5" customHeight="1">
+    <row r="64" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="1"/>
       <c r="B64" s="7"/>
       <c r="C64" s="7"/>
@@ -1372,7 +1422,7 @@
       <c r="K64" s="7"/>
       <c r="L64" s="1"/>
     </row>
-    <row r="65" ht="19.5" customHeight="1">
+    <row r="65" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="1"/>
       <c r="B65" s="7"/>
       <c r="C65" s="7"/>
@@ -1386,7 +1436,7 @@
       <c r="K65" s="7"/>
       <c r="L65" s="1"/>
     </row>
-    <row r="66" ht="19.5" customHeight="1">
+    <row r="66" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A66" s="1"/>
       <c r="B66" s="7"/>
       <c r="C66" s="7"/>
@@ -1400,7 +1450,7 @@
       <c r="K66" s="7"/>
       <c r="L66" s="1"/>
     </row>
-    <row r="67" ht="19.5" customHeight="1">
+    <row r="67" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A67" s="1"/>
       <c r="B67" s="7"/>
       <c r="C67" s="7"/>
@@ -1414,7 +1464,7 @@
       <c r="K67" s="7"/>
       <c r="L67" s="1"/>
     </row>
-    <row r="68" ht="19.5" customHeight="1">
+    <row r="68" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A68" s="1"/>
       <c r="B68" s="7"/>
       <c r="C68" s="7"/>
@@ -1428,7 +1478,7 @@
       <c r="K68" s="7"/>
       <c r="L68" s="1"/>
     </row>
-    <row r="69" ht="19.5" customHeight="1">
+    <row r="69" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A69" s="1"/>
       <c r="B69" s="7"/>
       <c r="C69" s="7"/>
@@ -1442,7 +1492,7 @@
       <c r="K69" s="7"/>
       <c r="L69" s="1"/>
     </row>
-    <row r="70" ht="19.5" customHeight="1">
+    <row r="70" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A70" s="1"/>
       <c r="B70" s="7"/>
       <c r="C70" s="7"/>
@@ -1456,7 +1506,7 @@
       <c r="K70" s="7"/>
       <c r="L70" s="1"/>
     </row>
-    <row r="71" ht="19.5" customHeight="1">
+    <row r="71" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A71" s="1"/>
       <c r="B71" s="7"/>
       <c r="C71" s="7"/>
@@ -1470,7 +1520,7 @@
       <c r="K71" s="7"/>
       <c r="L71" s="1"/>
     </row>
-    <row r="72" ht="19.5" customHeight="1">
+    <row r="72" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A72" s="1"/>
       <c r="B72" s="7"/>
       <c r="C72" s="7"/>
@@ -1484,7 +1534,7 @@
       <c r="K72" s="7"/>
       <c r="L72" s="1"/>
     </row>
-    <row r="73" ht="19.5" customHeight="1">
+    <row r="73" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A73" s="1"/>
       <c r="B73" s="7"/>
       <c r="C73" s="7"/>
@@ -1498,7 +1548,7 @@
       <c r="K73" s="7"/>
       <c r="L73" s="1"/>
     </row>
-    <row r="74" ht="19.5" customHeight="1">
+    <row r="74" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A74" s="1"/>
       <c r="B74" s="7"/>
       <c r="C74" s="7"/>
@@ -1512,7 +1562,7 @@
       <c r="K74" s="7"/>
       <c r="L74" s="1"/>
     </row>
-    <row r="75" ht="19.5" customHeight="1">
+    <row r="75" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A75" s="1"/>
       <c r="B75" s="7"/>
       <c r="C75" s="7"/>
@@ -1526,7 +1576,7 @@
       <c r="K75" s="7"/>
       <c r="L75" s="1"/>
     </row>
-    <row r="76" ht="19.5" customHeight="1">
+    <row r="76" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A76" s="1"/>
       <c r="B76" s="7"/>
       <c r="C76" s="7"/>
@@ -1540,7 +1590,7 @@
       <c r="K76" s="7"/>
       <c r="L76" s="1"/>
     </row>
-    <row r="77" ht="19.5" customHeight="1">
+    <row r="77" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A77" s="1"/>
       <c r="B77" s="7"/>
       <c r="C77" s="7"/>
@@ -1554,7 +1604,7 @@
       <c r="K77" s="7"/>
       <c r="L77" s="1"/>
     </row>
-    <row r="78" ht="19.5" customHeight="1">
+    <row r="78" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A78" s="1"/>
       <c r="B78" s="7"/>
       <c r="C78" s="7"/>
@@ -1568,7 +1618,7 @@
       <c r="K78" s="7"/>
       <c r="L78" s="1"/>
     </row>
-    <row r="79" ht="19.5" customHeight="1">
+    <row r="79" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A79" s="1"/>
       <c r="B79" s="7"/>
       <c r="C79" s="7"/>
@@ -1582,7 +1632,7 @@
       <c r="K79" s="7"/>
       <c r="L79" s="1"/>
     </row>
-    <row r="80" ht="19.5" customHeight="1">
+    <row r="80" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A80" s="1"/>
       <c r="B80" s="7"/>
       <c r="C80" s="7"/>
@@ -1596,7 +1646,7 @@
       <c r="K80" s="7"/>
       <c r="L80" s="1"/>
     </row>
-    <row r="81" ht="19.5" customHeight="1">
+    <row r="81" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A81" s="1"/>
       <c r="B81" s="7"/>
       <c r="C81" s="7"/>
@@ -1610,7 +1660,7 @@
       <c r="K81" s="7"/>
       <c r="L81" s="1"/>
     </row>
-    <row r="82" ht="19.5" customHeight="1">
+    <row r="82" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A82" s="1"/>
       <c r="B82" s="7"/>
       <c r="C82" s="7"/>
@@ -1624,7 +1674,7 @@
       <c r="K82" s="7"/>
       <c r="L82" s="1"/>
     </row>
-    <row r="83" ht="19.5" customHeight="1">
+    <row r="83" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A83" s="1"/>
       <c r="B83" s="7"/>
       <c r="C83" s="7"/>
@@ -1638,7 +1688,7 @@
       <c r="K83" s="7"/>
       <c r="L83" s="1"/>
     </row>
-    <row r="84" ht="19.5" customHeight="1">
+    <row r="84" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A84" s="1"/>
       <c r="B84" s="7"/>
       <c r="C84" s="7"/>
@@ -1652,7 +1702,7 @@
       <c r="K84" s="7"/>
       <c r="L84" s="1"/>
     </row>
-    <row r="85" ht="19.5" customHeight="1">
+    <row r="85" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A85" s="1"/>
       <c r="B85" s="7"/>
       <c r="C85" s="7"/>
@@ -1666,7 +1716,7 @@
       <c r="K85" s="7"/>
       <c r="L85" s="1"/>
     </row>
-    <row r="86" ht="19.5" customHeight="1">
+    <row r="86" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A86" s="1"/>
       <c r="B86" s="7"/>
       <c r="C86" s="7"/>
@@ -1680,7 +1730,7 @@
       <c r="K86" s="7"/>
       <c r="L86" s="1"/>
     </row>
-    <row r="87" ht="19.5" customHeight="1">
+    <row r="87" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A87" s="1"/>
       <c r="B87" s="7"/>
       <c r="C87" s="7"/>
@@ -1694,7 +1744,7 @@
       <c r="K87" s="7"/>
       <c r="L87" s="1"/>
     </row>
-    <row r="88" ht="19.5" customHeight="1">
+    <row r="88" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A88" s="1"/>
       <c r="B88" s="7"/>
       <c r="C88" s="7"/>
@@ -1708,7 +1758,7 @@
       <c r="K88" s="7"/>
       <c r="L88" s="1"/>
     </row>
-    <row r="89" ht="19.5" customHeight="1">
+    <row r="89" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A89" s="1"/>
       <c r="B89" s="7"/>
       <c r="C89" s="7"/>
@@ -1722,7 +1772,7 @@
       <c r="K89" s="7"/>
       <c r="L89" s="1"/>
     </row>
-    <row r="90" ht="19.5" customHeight="1">
+    <row r="90" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A90" s="1"/>
       <c r="B90" s="7"/>
       <c r="C90" s="7"/>
@@ -1736,7 +1786,7 @@
       <c r="K90" s="7"/>
       <c r="L90" s="1"/>
     </row>
-    <row r="91" ht="19.5" customHeight="1">
+    <row r="91" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A91" s="1"/>
       <c r="B91" s="7"/>
       <c r="C91" s="7"/>
@@ -1750,7 +1800,7 @@
       <c r="K91" s="7"/>
       <c r="L91" s="1"/>
     </row>
-    <row r="92" ht="19.5" customHeight="1">
+    <row r="92" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A92" s="1"/>
       <c r="B92" s="7"/>
       <c r="C92" s="7"/>
@@ -1764,7 +1814,7 @@
       <c r="K92" s="7"/>
       <c r="L92" s="1"/>
     </row>
-    <row r="93" ht="19.5" customHeight="1">
+    <row r="93" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A93" s="1"/>
       <c r="B93" s="7"/>
       <c r="C93" s="7"/>
@@ -1778,7 +1828,7 @@
       <c r="K93" s="7"/>
       <c r="L93" s="1"/>
     </row>
-    <row r="94" ht="19.5" customHeight="1">
+    <row r="94" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A94" s="1"/>
       <c r="B94" s="7"/>
       <c r="C94" s="7"/>
@@ -1792,7 +1842,7 @@
       <c r="K94" s="7"/>
       <c r="L94" s="1"/>
     </row>
-    <row r="95" ht="19.5" customHeight="1">
+    <row r="95" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A95" s="1"/>
       <c r="B95" s="7"/>
       <c r="C95" s="7"/>
@@ -1806,7 +1856,7 @@
       <c r="K95" s="7"/>
       <c r="L95" s="1"/>
     </row>
-    <row r="96" ht="19.5" customHeight="1">
+    <row r="96" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A96" s="1"/>
       <c r="B96" s="7"/>
       <c r="C96" s="7"/>
@@ -1820,7 +1870,7 @@
       <c r="K96" s="7"/>
       <c r="L96" s="1"/>
     </row>
-    <row r="97" ht="19.5" customHeight="1">
+    <row r="97" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A97" s="1"/>
       <c r="B97" s="7"/>
       <c r="C97" s="7"/>
@@ -1834,7 +1884,7 @@
       <c r="K97" s="7"/>
       <c r="L97" s="1"/>
     </row>
-    <row r="98" ht="19.5" customHeight="1">
+    <row r="98" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A98" s="1"/>
       <c r="B98" s="7"/>
       <c r="C98" s="7"/>
@@ -1848,7 +1898,7 @@
       <c r="K98" s="7"/>
       <c r="L98" s="1"/>
     </row>
-    <row r="99" ht="19.5" customHeight="1">
+    <row r="99" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A99" s="1"/>
       <c r="B99" s="7"/>
       <c r="C99" s="7"/>
@@ -1862,7 +1912,7 @@
       <c r="K99" s="7"/>
       <c r="L99" s="1"/>
     </row>
-    <row r="100" ht="19.5" customHeight="1">
+    <row r="100" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A100" s="1"/>
       <c r="B100" s="7"/>
       <c r="C100" s="7"/>
@@ -1876,7 +1926,7 @@
       <c r="K100" s="7"/>
       <c r="L100" s="1"/>
     </row>
-    <row r="101" ht="19.5" customHeight="1">
+    <row r="101" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A101" s="1"/>
       <c r="B101" s="7"/>
       <c r="C101" s="7"/>
@@ -1890,7 +1940,7 @@
       <c r="K101" s="7"/>
       <c r="L101" s="1"/>
     </row>
-    <row r="102" ht="19.5" customHeight="1">
+    <row r="102" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A102" s="1"/>
       <c r="B102" s="7"/>
       <c r="C102" s="7"/>
@@ -1904,7 +1954,7 @@
       <c r="K102" s="7"/>
       <c r="L102" s="1"/>
     </row>
-    <row r="103" ht="19.5" customHeight="1">
+    <row r="103" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A103" s="1"/>
       <c r="B103" s="7"/>
       <c r="C103" s="7"/>
@@ -1918,7 +1968,7 @@
       <c r="K103" s="7"/>
       <c r="L103" s="1"/>
     </row>
-    <row r="104" ht="19.5" customHeight="1">
+    <row r="104" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A104" s="1"/>
       <c r="B104" s="7"/>
       <c r="C104" s="7"/>
@@ -1932,7 +1982,7 @@
       <c r="K104" s="7"/>
       <c r="L104" s="1"/>
     </row>
-    <row r="105" ht="19.5" customHeight="1">
+    <row r="105" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A105" s="1"/>
       <c r="B105" s="7"/>
       <c r="C105" s="7"/>
@@ -1946,7 +1996,7 @@
       <c r="K105" s="7"/>
       <c r="L105" s="1"/>
     </row>
-    <row r="106" ht="19.5" customHeight="1">
+    <row r="106" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A106" s="1"/>
       <c r="B106" s="7"/>
       <c r="C106" s="7"/>
@@ -1960,7 +2010,7 @@
       <c r="K106" s="7"/>
       <c r="L106" s="1"/>
     </row>
-    <row r="107" ht="19.5" customHeight="1">
+    <row r="107" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A107" s="1"/>
       <c r="B107" s="7"/>
       <c r="C107" s="7"/>
@@ -1974,7 +2024,7 @@
       <c r="K107" s="7"/>
       <c r="L107" s="1"/>
     </row>
-    <row r="108" ht="19.5" customHeight="1">
+    <row r="108" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A108" s="1"/>
       <c r="B108" s="7"/>
       <c r="C108" s="7"/>
@@ -1988,7 +2038,7 @@
       <c r="K108" s="7"/>
       <c r="L108" s="1"/>
     </row>
-    <row r="109" ht="19.5" customHeight="1">
+    <row r="109" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A109" s="1"/>
       <c r="B109" s="7"/>
       <c r="C109" s="7"/>
@@ -2002,7 +2052,7 @@
       <c r="K109" s="7"/>
       <c r="L109" s="1"/>
     </row>
-    <row r="110" ht="19.5" customHeight="1">
+    <row r="110" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A110" s="1"/>
       <c r="B110" s="7"/>
       <c r="C110" s="7"/>
@@ -2016,7 +2066,7 @@
       <c r="K110" s="7"/>
       <c r="L110" s="1"/>
     </row>
-    <row r="111" ht="19.5" customHeight="1">
+    <row r="111" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A111" s="1"/>
       <c r="B111" s="7"/>
       <c r="C111" s="7"/>
@@ -2030,7 +2080,7 @@
       <c r="K111" s="7"/>
       <c r="L111" s="1"/>
     </row>
-    <row r="112" ht="19.5" customHeight="1">
+    <row r="112" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A112" s="1"/>
       <c r="B112" s="7"/>
       <c r="C112" s="7"/>
@@ -2044,7 +2094,7 @@
       <c r="K112" s="7"/>
       <c r="L112" s="1"/>
     </row>
-    <row r="113" ht="19.5" customHeight="1">
+    <row r="113" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A113" s="1"/>
       <c r="B113" s="7"/>
       <c r="C113" s="7"/>
@@ -2058,7 +2108,7 @@
       <c r="K113" s="7"/>
       <c r="L113" s="1"/>
     </row>
-    <row r="114" ht="19.5" customHeight="1">
+    <row r="114" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A114" s="1"/>
       <c r="B114" s="7"/>
       <c r="C114" s="7"/>
@@ -2072,7 +2122,7 @@
       <c r="K114" s="7"/>
       <c r="L114" s="1"/>
     </row>
-    <row r="115" ht="19.5" customHeight="1">
+    <row r="115" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A115" s="1"/>
       <c r="B115" s="7"/>
       <c r="C115" s="7"/>
@@ -2086,7 +2136,7 @@
       <c r="K115" s="7"/>
       <c r="L115" s="1"/>
     </row>
-    <row r="116" ht="19.5" customHeight="1">
+    <row r="116" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A116" s="1"/>
       <c r="B116" s="7"/>
       <c r="C116" s="7"/>
@@ -2100,7 +2150,7 @@
       <c r="K116" s="7"/>
       <c r="L116" s="1"/>
     </row>
-    <row r="117" ht="19.5" customHeight="1">
+    <row r="117" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A117" s="1"/>
       <c r="B117" s="7"/>
       <c r="C117" s="7"/>
@@ -2114,7 +2164,7 @@
       <c r="K117" s="7"/>
       <c r="L117" s="1"/>
     </row>
-    <row r="118" ht="19.5" customHeight="1">
+    <row r="118" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A118" s="1"/>
       <c r="B118" s="7"/>
       <c r="C118" s="7"/>
@@ -2128,7 +2178,7 @@
       <c r="K118" s="7"/>
       <c r="L118" s="1"/>
     </row>
-    <row r="119" ht="19.5" customHeight="1">
+    <row r="119" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A119" s="1"/>
       <c r="B119" s="7"/>
       <c r="C119" s="7"/>
@@ -2142,7 +2192,7 @@
       <c r="K119" s="7"/>
       <c r="L119" s="1"/>
     </row>
-    <row r="120" ht="19.5" customHeight="1">
+    <row r="120" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A120" s="1"/>
       <c r="B120" s="7"/>
       <c r="C120" s="7"/>
@@ -2156,7 +2206,7 @@
       <c r="K120" s="7"/>
       <c r="L120" s="1"/>
     </row>
-    <row r="121" ht="19.5" customHeight="1">
+    <row r="121" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A121" s="1"/>
       <c r="B121" s="7"/>
       <c r="C121" s="7"/>
@@ -2170,7 +2220,7 @@
       <c r="K121" s="7"/>
       <c r="L121" s="1"/>
     </row>
-    <row r="122" ht="19.5" customHeight="1">
+    <row r="122" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A122" s="1"/>
       <c r="B122" s="7"/>
       <c r="C122" s="7"/>
@@ -2184,7 +2234,7 @@
       <c r="K122" s="7"/>
       <c r="L122" s="1"/>
     </row>
-    <row r="123" ht="19.5" customHeight="1">
+    <row r="123" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A123" s="1"/>
       <c r="B123" s="7"/>
       <c r="C123" s="7"/>
@@ -2198,7 +2248,7 @@
       <c r="K123" s="7"/>
       <c r="L123" s="1"/>
     </row>
-    <row r="124" ht="19.5" customHeight="1">
+    <row r="124" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A124" s="1"/>
       <c r="B124" s="7"/>
       <c r="C124" s="7"/>
@@ -2212,7 +2262,7 @@
       <c r="K124" s="7"/>
       <c r="L124" s="1"/>
     </row>
-    <row r="125" ht="19.5" customHeight="1">
+    <row r="125" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A125" s="1"/>
       <c r="B125" s="7"/>
       <c r="C125" s="7"/>
@@ -2226,7 +2276,7 @@
       <c r="K125" s="7"/>
       <c r="L125" s="1"/>
     </row>
-    <row r="126" ht="19.5" customHeight="1">
+    <row r="126" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A126" s="1"/>
       <c r="B126" s="7"/>
       <c r="C126" s="7"/>
@@ -2240,7 +2290,7 @@
       <c r="K126" s="7"/>
       <c r="L126" s="1"/>
     </row>
-    <row r="127" ht="19.5" customHeight="1">
+    <row r="127" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A127" s="1"/>
       <c r="B127" s="7"/>
       <c r="C127" s="7"/>
@@ -2254,7 +2304,7 @@
       <c r="K127" s="7"/>
       <c r="L127" s="1"/>
     </row>
-    <row r="128" ht="19.5" customHeight="1">
+    <row r="128" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A128" s="1"/>
       <c r="B128" s="7"/>
       <c r="C128" s="7"/>
@@ -2268,7 +2318,7 @@
       <c r="K128" s="7"/>
       <c r="L128" s="1"/>
     </row>
-    <row r="129" ht="19.5" customHeight="1">
+    <row r="129" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A129" s="1"/>
       <c r="B129" s="7"/>
       <c r="C129" s="7"/>
@@ -2282,7 +2332,7 @@
       <c r="K129" s="7"/>
       <c r="L129" s="1"/>
     </row>
-    <row r="130" ht="19.5" customHeight="1">
+    <row r="130" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A130" s="1"/>
       <c r="B130" s="7"/>
       <c r="C130" s="7"/>
@@ -2296,7 +2346,7 @@
       <c r="K130" s="7"/>
       <c r="L130" s="1"/>
     </row>
-    <row r="131" ht="19.5" customHeight="1">
+    <row r="131" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A131" s="1"/>
       <c r="B131" s="7"/>
       <c r="C131" s="7"/>
@@ -2310,7 +2360,7 @@
       <c r="K131" s="7"/>
       <c r="L131" s="1"/>
     </row>
-    <row r="132" ht="19.5" customHeight="1">
+    <row r="132" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A132" s="1"/>
       <c r="B132" s="7"/>
       <c r="C132" s="7"/>
@@ -2324,7 +2374,7 @@
       <c r="K132" s="7"/>
       <c r="L132" s="1"/>
     </row>
-    <row r="133" ht="19.5" customHeight="1">
+    <row r="133" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A133" s="1"/>
       <c r="B133" s="7"/>
       <c r="C133" s="7"/>
@@ -2338,7 +2388,7 @@
       <c r="K133" s="7"/>
       <c r="L133" s="1"/>
     </row>
-    <row r="134" ht="19.5" customHeight="1">
+    <row r="134" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A134" s="1"/>
       <c r="B134" s="7"/>
       <c r="C134" s="7"/>
@@ -2352,7 +2402,7 @@
       <c r="K134" s="7"/>
       <c r="L134" s="1"/>
     </row>
-    <row r="135" ht="19.5" customHeight="1">
+    <row r="135" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A135" s="1"/>
       <c r="B135" s="7"/>
       <c r="C135" s="7"/>
@@ -2366,7 +2416,7 @@
       <c r="K135" s="7"/>
       <c r="L135" s="1"/>
     </row>
-    <row r="136" ht="19.5" customHeight="1">
+    <row r="136" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A136" s="1"/>
       <c r="B136" s="7"/>
       <c r="C136" s="7"/>
@@ -2380,7 +2430,7 @@
       <c r="K136" s="7"/>
       <c r="L136" s="1"/>
     </row>
-    <row r="137" ht="19.5" customHeight="1">
+    <row r="137" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A137" s="1"/>
       <c r="B137" s="7"/>
       <c r="C137" s="7"/>
@@ -2394,7 +2444,7 @@
       <c r="K137" s="7"/>
       <c r="L137" s="1"/>
     </row>
-    <row r="138" ht="19.5" customHeight="1">
+    <row r="138" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A138" s="1"/>
       <c r="B138" s="7"/>
       <c r="C138" s="7"/>
@@ -2408,7 +2458,7 @@
       <c r="K138" s="7"/>
       <c r="L138" s="1"/>
     </row>
-    <row r="139" ht="19.5" customHeight="1">
+    <row r="139" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A139" s="1"/>
       <c r="B139" s="7"/>
       <c r="C139" s="7"/>
@@ -2422,7 +2472,7 @@
       <c r="K139" s="7"/>
       <c r="L139" s="1"/>
     </row>
-    <row r="140" ht="19.5" customHeight="1">
+    <row r="140" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A140" s="1"/>
       <c r="B140" s="7"/>
       <c r="C140" s="7"/>
@@ -2436,7 +2486,7 @@
       <c r="K140" s="7"/>
       <c r="L140" s="1"/>
     </row>
-    <row r="141" ht="19.5" customHeight="1">
+    <row r="141" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A141" s="1"/>
       <c r="B141" s="7"/>
       <c r="C141" s="7"/>
@@ -2450,7 +2500,7 @@
       <c r="K141" s="7"/>
       <c r="L141" s="1"/>
     </row>
-    <row r="142" ht="19.5" customHeight="1">
+    <row r="142" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A142" s="1"/>
       <c r="B142" s="7"/>
       <c r="C142" s="7"/>
@@ -2464,7 +2514,7 @@
       <c r="K142" s="7"/>
       <c r="L142" s="1"/>
     </row>
-    <row r="143" ht="19.5" customHeight="1">
+    <row r="143" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A143" s="1"/>
       <c r="B143" s="7"/>
       <c r="C143" s="7"/>
@@ -2478,7 +2528,7 @@
       <c r="K143" s="7"/>
       <c r="L143" s="1"/>
     </row>
-    <row r="144" ht="19.5" customHeight="1">
+    <row r="144" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A144" s="1"/>
       <c r="B144" s="7"/>
       <c r="C144" s="7"/>
@@ -2492,7 +2542,7 @@
       <c r="K144" s="7"/>
       <c r="L144" s="1"/>
     </row>
-    <row r="145" ht="19.5" customHeight="1">
+    <row r="145" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A145" s="1"/>
       <c r="B145" s="7"/>
       <c r="C145" s="7"/>
@@ -2506,7 +2556,7 @@
       <c r="K145" s="7"/>
       <c r="L145" s="1"/>
     </row>
-    <row r="146" ht="19.5" customHeight="1">
+    <row r="146" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A146" s="1"/>
       <c r="B146" s="7"/>
       <c r="C146" s="7"/>
@@ -2520,7 +2570,7 @@
       <c r="K146" s="7"/>
       <c r="L146" s="1"/>
     </row>
-    <row r="147" ht="19.5" customHeight="1">
+    <row r="147" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A147" s="1"/>
       <c r="B147" s="7"/>
       <c r="C147" s="7"/>
@@ -2534,7 +2584,7 @@
       <c r="K147" s="7"/>
       <c r="L147" s="1"/>
     </row>
-    <row r="148" ht="19.5" customHeight="1">
+    <row r="148" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A148" s="1"/>
       <c r="B148" s="7"/>
       <c r="C148" s="7"/>
@@ -2548,7 +2598,7 @@
       <c r="K148" s="7"/>
       <c r="L148" s="1"/>
     </row>
-    <row r="149" ht="19.5" customHeight="1">
+    <row r="149" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A149" s="1"/>
       <c r="B149" s="7"/>
       <c r="C149" s="7"/>
@@ -2562,7 +2612,7 @@
       <c r="K149" s="7"/>
       <c r="L149" s="1"/>
     </row>
-    <row r="150" ht="19.5" customHeight="1">
+    <row r="150" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A150" s="1"/>
       <c r="B150" s="7"/>
       <c r="C150" s="7"/>
@@ -2576,7 +2626,7 @@
       <c r="K150" s="7"/>
       <c r="L150" s="1"/>
     </row>
-    <row r="151" ht="19.5" customHeight="1">
+    <row r="151" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A151" s="1"/>
       <c r="B151" s="7"/>
       <c r="C151" s="7"/>
@@ -2590,7 +2640,7 @@
       <c r="K151" s="7"/>
       <c r="L151" s="1"/>
     </row>
-    <row r="152" ht="19.5" customHeight="1">
+    <row r="152" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A152" s="1"/>
       <c r="B152" s="7"/>
       <c r="C152" s="7"/>
@@ -2604,7 +2654,7 @@
       <c r="K152" s="7"/>
       <c r="L152" s="1"/>
     </row>
-    <row r="153" ht="19.5" customHeight="1">
+    <row r="153" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A153" s="1"/>
       <c r="B153" s="7"/>
       <c r="C153" s="7"/>
@@ -2618,7 +2668,7 @@
       <c r="K153" s="7"/>
       <c r="L153" s="1"/>
     </row>
-    <row r="154" ht="19.5" customHeight="1">
+    <row r="154" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A154" s="1"/>
       <c r="B154" s="7"/>
       <c r="C154" s="7"/>
@@ -2632,7 +2682,7 @@
       <c r="K154" s="7"/>
       <c r="L154" s="1"/>
     </row>
-    <row r="155" ht="19.5" customHeight="1">
+    <row r="155" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A155" s="1"/>
       <c r="B155" s="7"/>
       <c r="C155" s="7"/>
@@ -2646,7 +2696,7 @@
       <c r="K155" s="7"/>
       <c r="L155" s="1"/>
     </row>
-    <row r="156" ht="19.5" customHeight="1">
+    <row r="156" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A156" s="1"/>
       <c r="B156" s="7"/>
       <c r="C156" s="7"/>
@@ -2660,7 +2710,7 @@
       <c r="K156" s="7"/>
       <c r="L156" s="1"/>
     </row>
-    <row r="157" ht="19.5" customHeight="1">
+    <row r="157" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A157" s="1"/>
       <c r="B157" s="7"/>
       <c r="C157" s="7"/>
@@ -2674,7 +2724,7 @@
       <c r="K157" s="7"/>
       <c r="L157" s="1"/>
     </row>
-    <row r="158" ht="19.5" customHeight="1">
+    <row r="158" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A158" s="1"/>
       <c r="B158" s="7"/>
       <c r="C158" s="7"/>
@@ -2688,7 +2738,7 @@
       <c r="K158" s="7"/>
       <c r="L158" s="1"/>
     </row>
-    <row r="159" ht="19.5" customHeight="1">
+    <row r="159" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A159" s="1"/>
       <c r="B159" s="7"/>
       <c r="C159" s="7"/>
@@ -2702,7 +2752,7 @@
       <c r="K159" s="7"/>
       <c r="L159" s="1"/>
     </row>
-    <row r="160" ht="19.5" customHeight="1">
+    <row r="160" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A160" s="1"/>
       <c r="B160" s="7"/>
       <c r="C160" s="7"/>
@@ -2716,7 +2766,7 @@
       <c r="K160" s="7"/>
       <c r="L160" s="1"/>
     </row>
-    <row r="161" ht="19.5" customHeight="1">
+    <row r="161" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A161" s="1"/>
       <c r="B161" s="7"/>
       <c r="C161" s="7"/>
@@ -2730,7 +2780,7 @@
       <c r="K161" s="7"/>
       <c r="L161" s="1"/>
     </row>
-    <row r="162" ht="19.5" customHeight="1">
+    <row r="162" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A162" s="1"/>
       <c r="B162" s="7"/>
       <c r="C162" s="7"/>
@@ -2744,7 +2794,7 @@
       <c r="K162" s="7"/>
       <c r="L162" s="1"/>
     </row>
-    <row r="163" ht="19.5" customHeight="1">
+    <row r="163" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A163" s="1"/>
       <c r="B163" s="7"/>
       <c r="C163" s="7"/>
@@ -2758,7 +2808,7 @@
       <c r="K163" s="7"/>
       <c r="L163" s="1"/>
     </row>
-    <row r="164" ht="19.5" customHeight="1">
+    <row r="164" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A164" s="1"/>
       <c r="B164" s="7"/>
       <c r="C164" s="7"/>
@@ -2772,7 +2822,7 @@
       <c r="K164" s="7"/>
       <c r="L164" s="1"/>
     </row>
-    <row r="165" ht="19.5" customHeight="1">
+    <row r="165" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A165" s="1"/>
       <c r="B165" s="7"/>
       <c r="C165" s="7"/>
@@ -2786,7 +2836,7 @@
       <c r="K165" s="7"/>
       <c r="L165" s="1"/>
     </row>
-    <row r="166" ht="19.5" customHeight="1">
+    <row r="166" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A166" s="1"/>
       <c r="B166" s="7"/>
       <c r="C166" s="7"/>
@@ -2800,7 +2850,7 @@
       <c r="K166" s="7"/>
       <c r="L166" s="1"/>
     </row>
-    <row r="167" ht="19.5" customHeight="1">
+    <row r="167" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A167" s="1"/>
       <c r="B167" s="7"/>
       <c r="C167" s="7"/>
@@ -2814,7 +2864,7 @@
       <c r="K167" s="7"/>
       <c r="L167" s="1"/>
     </row>
-    <row r="168" ht="19.5" customHeight="1">
+    <row r="168" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A168" s="1"/>
       <c r="B168" s="7"/>
       <c r="C168" s="7"/>
@@ -2828,7 +2878,7 @@
       <c r="K168" s="7"/>
       <c r="L168" s="1"/>
     </row>
-    <row r="169" ht="19.5" customHeight="1">
+    <row r="169" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A169" s="1"/>
       <c r="B169" s="7"/>
       <c r="C169" s="7"/>
@@ -2842,7 +2892,7 @@
       <c r="K169" s="7"/>
       <c r="L169" s="1"/>
     </row>
-    <row r="170" ht="19.5" customHeight="1">
+    <row r="170" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A170" s="1"/>
       <c r="B170" s="7"/>
       <c r="C170" s="7"/>
@@ -2856,7 +2906,7 @@
       <c r="K170" s="7"/>
       <c r="L170" s="1"/>
     </row>
-    <row r="171" ht="19.5" customHeight="1">
+    <row r="171" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A171" s="1"/>
       <c r="B171" s="7"/>
       <c r="C171" s="7"/>
@@ -2870,7 +2920,7 @@
       <c r="K171" s="7"/>
       <c r="L171" s="1"/>
     </row>
-    <row r="172" ht="19.5" customHeight="1">
+    <row r="172" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A172" s="1"/>
       <c r="B172" s="7"/>
       <c r="C172" s="7"/>
@@ -2884,7 +2934,7 @@
       <c r="K172" s="7"/>
       <c r="L172" s="1"/>
     </row>
-    <row r="173" ht="19.5" customHeight="1">
+    <row r="173" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A173" s="1"/>
       <c r="B173" s="7"/>
       <c r="C173" s="7"/>
@@ -2898,7 +2948,7 @@
       <c r="K173" s="7"/>
       <c r="L173" s="1"/>
     </row>
-    <row r="174" ht="19.5" customHeight="1">
+    <row r="174" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A174" s="1"/>
       <c r="B174" s="7"/>
       <c r="C174" s="7"/>
@@ -2912,7 +2962,7 @@
       <c r="K174" s="7"/>
       <c r="L174" s="1"/>
     </row>
-    <row r="175" ht="19.5" customHeight="1">
+    <row r="175" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A175" s="1"/>
       <c r="B175" s="7"/>
       <c r="C175" s="7"/>
@@ -2926,7 +2976,7 @@
       <c r="K175" s="7"/>
       <c r="L175" s="1"/>
     </row>
-    <row r="176" ht="19.5" customHeight="1">
+    <row r="176" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A176" s="1"/>
       <c r="B176" s="7"/>
       <c r="C176" s="7"/>
@@ -2940,7 +2990,7 @@
       <c r="K176" s="7"/>
       <c r="L176" s="1"/>
     </row>
-    <row r="177" ht="19.5" customHeight="1">
+    <row r="177" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A177" s="1"/>
       <c r="B177" s="7"/>
       <c r="C177" s="7"/>
@@ -2954,7 +3004,7 @@
       <c r="K177" s="7"/>
       <c r="L177" s="1"/>
     </row>
-    <row r="178" ht="19.5" customHeight="1">
+    <row r="178" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A178" s="1"/>
       <c r="B178" s="7"/>
       <c r="C178" s="7"/>
@@ -2968,7 +3018,7 @@
       <c r="K178" s="7"/>
       <c r="L178" s="1"/>
     </row>
-    <row r="179" ht="19.5" customHeight="1">
+    <row r="179" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A179" s="1"/>
       <c r="B179" s="7"/>
       <c r="C179" s="7"/>
@@ -2982,7 +3032,7 @@
       <c r="K179" s="7"/>
       <c r="L179" s="1"/>
     </row>
-    <row r="180" ht="19.5" customHeight="1">
+    <row r="180" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A180" s="1"/>
       <c r="B180" s="7"/>
       <c r="C180" s="7"/>
@@ -2996,7 +3046,7 @@
       <c r="K180" s="7"/>
       <c r="L180" s="1"/>
     </row>
-    <row r="181" ht="19.5" customHeight="1">
+    <row r="181" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A181" s="1"/>
       <c r="B181" s="7"/>
       <c r="C181" s="7"/>
@@ -3010,7 +3060,7 @@
       <c r="K181" s="7"/>
       <c r="L181" s="1"/>
     </row>
-    <row r="182" ht="19.5" customHeight="1">
+    <row r="182" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A182" s="1"/>
       <c r="B182" s="7"/>
       <c r="C182" s="7"/>
@@ -3024,7 +3074,7 @@
       <c r="K182" s="7"/>
       <c r="L182" s="1"/>
     </row>
-    <row r="183" ht="19.5" customHeight="1">
+    <row r="183" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A183" s="1"/>
       <c r="B183" s="7"/>
       <c r="C183" s="7"/>
@@ -3038,7 +3088,7 @@
       <c r="K183" s="7"/>
       <c r="L183" s="1"/>
     </row>
-    <row r="184" ht="19.5" customHeight="1">
+    <row r="184" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A184" s="1"/>
       <c r="B184" s="7"/>
       <c r="C184" s="7"/>
@@ -3052,7 +3102,7 @@
       <c r="K184" s="7"/>
       <c r="L184" s="1"/>
     </row>
-    <row r="185" ht="19.5" customHeight="1">
+    <row r="185" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A185" s="1"/>
       <c r="B185" s="7"/>
       <c r="C185" s="7"/>
@@ -3066,7 +3116,7 @@
       <c r="K185" s="7"/>
       <c r="L185" s="1"/>
     </row>
-    <row r="186" ht="19.5" customHeight="1">
+    <row r="186" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A186" s="1"/>
       <c r="B186" s="7"/>
       <c r="C186" s="7"/>
@@ -3080,7 +3130,7 @@
       <c r="K186" s="7"/>
       <c r="L186" s="1"/>
     </row>
-    <row r="187" ht="19.5" customHeight="1">
+    <row r="187" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A187" s="1"/>
       <c r="B187" s="7"/>
       <c r="C187" s="7"/>
@@ -3094,7 +3144,7 @@
       <c r="K187" s="7"/>
       <c r="L187" s="1"/>
     </row>
-    <row r="188" ht="19.5" customHeight="1">
+    <row r="188" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A188" s="1"/>
       <c r="B188" s="7"/>
       <c r="C188" s="7"/>
@@ -3108,7 +3158,7 @@
       <c r="K188" s="7"/>
       <c r="L188" s="1"/>
     </row>
-    <row r="189" ht="19.5" customHeight="1">
+    <row r="189" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A189" s="1"/>
       <c r="B189" s="7"/>
       <c r="C189" s="7"/>
@@ -3122,7 +3172,7 @@
       <c r="K189" s="7"/>
       <c r="L189" s="1"/>
     </row>
-    <row r="190" ht="19.5" customHeight="1">
+    <row r="190" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A190" s="1"/>
       <c r="B190" s="7"/>
       <c r="C190" s="7"/>
@@ -3136,7 +3186,7 @@
       <c r="K190" s="7"/>
       <c r="L190" s="1"/>
     </row>
-    <row r="191" ht="19.5" customHeight="1">
+    <row r="191" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A191" s="1"/>
       <c r="B191" s="7"/>
       <c r="C191" s="7"/>
@@ -3150,7 +3200,7 @@
       <c r="K191" s="7"/>
       <c r="L191" s="1"/>
     </row>
-    <row r="192" ht="19.5" customHeight="1">
+    <row r="192" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A192" s="1"/>
       <c r="B192" s="7"/>
       <c r="C192" s="7"/>
@@ -3164,7 +3214,7 @@
       <c r="K192" s="7"/>
       <c r="L192" s="1"/>
     </row>
-    <row r="193" ht="19.5" customHeight="1">
+    <row r="193" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A193" s="1"/>
       <c r="B193" s="7"/>
       <c r="C193" s="7"/>
@@ -3178,7 +3228,7 @@
       <c r="K193" s="7"/>
       <c r="L193" s="1"/>
     </row>
-    <row r="194" ht="19.5" customHeight="1">
+    <row r="194" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A194" s="1"/>
       <c r="B194" s="7"/>
       <c r="C194" s="7"/>
@@ -3192,7 +3242,7 @@
       <c r="K194" s="7"/>
       <c r="L194" s="1"/>
     </row>
-    <row r="195" ht="19.5" customHeight="1">
+    <row r="195" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A195" s="1"/>
       <c r="B195" s="7"/>
       <c r="C195" s="7"/>
@@ -3206,7 +3256,7 @@
       <c r="K195" s="7"/>
       <c r="L195" s="1"/>
     </row>
-    <row r="196" ht="19.5" customHeight="1">
+    <row r="196" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A196" s="1"/>
       <c r="B196" s="7"/>
       <c r="C196" s="7"/>
@@ -3220,7 +3270,7 @@
       <c r="K196" s="7"/>
       <c r="L196" s="1"/>
     </row>
-    <row r="197" ht="19.5" customHeight="1">
+    <row r="197" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A197" s="1"/>
       <c r="B197" s="7"/>
       <c r="C197" s="7"/>
@@ -3234,7 +3284,7 @@
       <c r="K197" s="7"/>
       <c r="L197" s="1"/>
     </row>
-    <row r="198" ht="19.5" customHeight="1">
+    <row r="198" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A198" s="1"/>
       <c r="B198" s="7"/>
       <c r="C198" s="7"/>
@@ -3248,7 +3298,7 @@
       <c r="K198" s="7"/>
       <c r="L198" s="1"/>
     </row>
-    <row r="199" ht="19.5" customHeight="1">
+    <row r="199" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A199" s="1"/>
       <c r="B199" s="7"/>
       <c r="C199" s="7"/>
@@ -3262,7 +3312,7 @@
       <c r="K199" s="7"/>
       <c r="L199" s="1"/>
     </row>
-    <row r="200" ht="19.5" customHeight="1">
+    <row r="200" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A200" s="1"/>
       <c r="B200" s="7"/>
       <c r="C200" s="7"/>
@@ -3276,7 +3326,7 @@
       <c r="K200" s="7"/>
       <c r="L200" s="1"/>
     </row>
-    <row r="201" ht="19.5" customHeight="1">
+    <row r="201" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A201" s="1"/>
       <c r="B201" s="7"/>
       <c r="C201" s="7"/>
@@ -3290,7 +3340,7 @@
       <c r="K201" s="7"/>
       <c r="L201" s="1"/>
     </row>
-    <row r="202" ht="19.5" customHeight="1">
+    <row r="202" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A202" s="1"/>
       <c r="B202" s="7"/>
       <c r="C202" s="7"/>
@@ -3304,7 +3354,7 @@
       <c r="K202" s="7"/>
       <c r="L202" s="1"/>
     </row>
-    <row r="203" ht="19.5" customHeight="1">
+    <row r="203" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A203" s="1"/>
       <c r="B203" s="7"/>
       <c r="C203" s="7"/>
@@ -3318,7 +3368,7 @@
       <c r="K203" s="7"/>
       <c r="L203" s="1"/>
     </row>
-    <row r="204" ht="19.5" customHeight="1">
+    <row r="204" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A204" s="1"/>
       <c r="B204" s="7"/>
       <c r="C204" s="7"/>
@@ -3332,7 +3382,7 @@
       <c r="K204" s="7"/>
       <c r="L204" s="1"/>
     </row>
-    <row r="205" ht="19.5" customHeight="1">
+    <row r="205" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A205" s="1"/>
       <c r="B205" s="7"/>
       <c r="C205" s="7"/>
@@ -3346,7 +3396,7 @@
       <c r="K205" s="7"/>
       <c r="L205" s="1"/>
     </row>
-    <row r="206" ht="19.5" customHeight="1">
+    <row r="206" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A206" s="1"/>
       <c r="B206" s="7"/>
       <c r="C206" s="7"/>
@@ -3360,7 +3410,7 @@
       <c r="K206" s="7"/>
       <c r="L206" s="1"/>
     </row>
-    <row r="207" ht="19.5" customHeight="1">
+    <row r="207" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A207" s="1"/>
       <c r="B207" s="7"/>
       <c r="C207" s="7"/>
@@ -3374,7 +3424,7 @@
       <c r="K207" s="7"/>
       <c r="L207" s="1"/>
     </row>
-    <row r="208" ht="19.5" customHeight="1">
+    <row r="208" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A208" s="1"/>
       <c r="B208" s="7"/>
       <c r="C208" s="7"/>
@@ -3388,7 +3438,7 @@
       <c r="K208" s="7"/>
       <c r="L208" s="1"/>
     </row>
-    <row r="209" ht="19.5" customHeight="1">
+    <row r="209" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A209" s="1"/>
       <c r="B209" s="7"/>
       <c r="C209" s="7"/>
@@ -3402,7 +3452,7 @@
       <c r="K209" s="7"/>
       <c r="L209" s="1"/>
     </row>
-    <row r="210" ht="19.5" customHeight="1">
+    <row r="210" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A210" s="1"/>
       <c r="B210" s="7"/>
       <c r="C210" s="7"/>
@@ -3416,7 +3466,7 @@
       <c r="K210" s="7"/>
       <c r="L210" s="1"/>
     </row>
-    <row r="211" ht="19.5" customHeight="1">
+    <row r="211" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A211" s="1"/>
       <c r="B211" s="7"/>
       <c r="C211" s="7"/>
@@ -3430,7 +3480,7 @@
       <c r="K211" s="7"/>
       <c r="L211" s="1"/>
     </row>
-    <row r="212" ht="19.5" customHeight="1">
+    <row r="212" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A212" s="1"/>
       <c r="B212" s="7"/>
       <c r="C212" s="7"/>
@@ -3444,7 +3494,7 @@
       <c r="K212" s="7"/>
       <c r="L212" s="1"/>
     </row>
-    <row r="213" ht="19.5" customHeight="1">
+    <row r="213" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A213" s="1"/>
       <c r="B213" s="7"/>
       <c r="C213" s="7"/>
@@ -3458,7 +3508,7 @@
       <c r="K213" s="7"/>
       <c r="L213" s="1"/>
     </row>
-    <row r="214" ht="19.5" customHeight="1">
+    <row r="214" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A214" s="1"/>
       <c r="B214" s="7"/>
       <c r="C214" s="7"/>
@@ -3472,7 +3522,7 @@
       <c r="K214" s="7"/>
       <c r="L214" s="1"/>
     </row>
-    <row r="215" ht="19.5" customHeight="1">
+    <row r="215" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A215" s="1"/>
       <c r="B215" s="7"/>
       <c r="C215" s="7"/>
@@ -3486,7 +3536,7 @@
       <c r="K215" s="7"/>
       <c r="L215" s="1"/>
     </row>
-    <row r="216" ht="19.5" customHeight="1">
+    <row r="216" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A216" s="1"/>
       <c r="B216" s="7"/>
       <c r="C216" s="7"/>
@@ -3500,7 +3550,7 @@
       <c r="K216" s="7"/>
       <c r="L216" s="1"/>
     </row>
-    <row r="217" ht="19.5" customHeight="1">
+    <row r="217" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A217" s="1"/>
       <c r="B217" s="7"/>
       <c r="C217" s="7"/>
@@ -3514,7 +3564,7 @@
       <c r="K217" s="7"/>
       <c r="L217" s="1"/>
     </row>
-    <row r="218" ht="19.5" customHeight="1">
+    <row r="218" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A218" s="1"/>
       <c r="B218" s="7"/>
       <c r="C218" s="7"/>
@@ -3528,7 +3578,7 @@
       <c r="K218" s="7"/>
       <c r="L218" s="1"/>
     </row>
-    <row r="219" ht="19.5" customHeight="1">
+    <row r="219" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A219" s="1"/>
       <c r="B219" s="7"/>
       <c r="C219" s="7"/>
@@ -3542,7 +3592,7 @@
       <c r="K219" s="7"/>
       <c r="L219" s="1"/>
     </row>
-    <row r="220" ht="19.5" customHeight="1">
+    <row r="220" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A220" s="1"/>
       <c r="B220" s="7"/>
       <c r="C220" s="7"/>
@@ -3556,7 +3606,7 @@
       <c r="K220" s="7"/>
       <c r="L220" s="1"/>
     </row>
-    <row r="221" ht="19.5" customHeight="1">
+    <row r="221" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A221" s="1"/>
       <c r="B221" s="7"/>
       <c r="C221" s="7"/>
@@ -3570,7 +3620,7 @@
       <c r="K221" s="7"/>
       <c r="L221" s="1"/>
     </row>
-    <row r="222" ht="19.5" customHeight="1">
+    <row r="222" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A222" s="1"/>
       <c r="B222" s="7"/>
       <c r="C222" s="7"/>
@@ -3584,7 +3634,7 @@
       <c r="K222" s="7"/>
       <c r="L222" s="1"/>
     </row>
-    <row r="223" ht="19.5" customHeight="1">
+    <row r="223" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A223" s="1"/>
       <c r="B223" s="7"/>
       <c r="C223" s="7"/>
@@ -3598,7 +3648,7 @@
       <c r="K223" s="7"/>
       <c r="L223" s="1"/>
     </row>
-    <row r="224" ht="19.5" customHeight="1">
+    <row r="224" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A224" s="1"/>
       <c r="B224" s="7"/>
       <c r="C224" s="7"/>
@@ -3612,7 +3662,7 @@
       <c r="K224" s="7"/>
       <c r="L224" s="1"/>
     </row>
-    <row r="225" ht="19.5" customHeight="1">
+    <row r="225" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A225" s="1"/>
       <c r="B225" s="7"/>
       <c r="C225" s="7"/>
@@ -3626,7 +3676,7 @@
       <c r="K225" s="7"/>
       <c r="L225" s="1"/>
     </row>
-    <row r="226" ht="19.5" customHeight="1">
+    <row r="226" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A226" s="1"/>
       <c r="B226" s="7"/>
       <c r="C226" s="7"/>
@@ -3640,7 +3690,7 @@
       <c r="K226" s="7"/>
       <c r="L226" s="1"/>
     </row>
-    <row r="227" ht="19.5" customHeight="1">
+    <row r="227" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A227" s="1"/>
       <c r="B227" s="7"/>
       <c r="C227" s="7"/>
@@ -3654,7 +3704,7 @@
       <c r="K227" s="7"/>
       <c r="L227" s="1"/>
     </row>
-    <row r="228" ht="19.5" customHeight="1">
+    <row r="228" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A228" s="1"/>
       <c r="B228" s="7"/>
       <c r="C228" s="7"/>
@@ -3668,7 +3718,7 @@
       <c r="K228" s="7"/>
       <c r="L228" s="1"/>
     </row>
-    <row r="229" ht="19.5" customHeight="1">
+    <row r="229" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A229" s="1"/>
       <c r="B229" s="7"/>
       <c r="C229" s="7"/>
@@ -3682,7 +3732,7 @@
       <c r="K229" s="7"/>
       <c r="L229" s="1"/>
     </row>
-    <row r="230" ht="19.5" customHeight="1">
+    <row r="230" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A230" s="1"/>
       <c r="B230" s="7"/>
       <c r="C230" s="7"/>
@@ -3696,7 +3746,7 @@
       <c r="K230" s="7"/>
       <c r="L230" s="1"/>
     </row>
-    <row r="231" ht="19.5" customHeight="1">
+    <row r="231" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A231" s="1"/>
       <c r="B231" s="7"/>
       <c r="C231" s="7"/>
@@ -3710,7 +3760,7 @@
       <c r="K231" s="7"/>
       <c r="L231" s="1"/>
     </row>
-    <row r="232" ht="19.5" customHeight="1">
+    <row r="232" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A232" s="1"/>
       <c r="B232" s="7"/>
       <c r="C232" s="7"/>
@@ -3724,7 +3774,7 @@
       <c r="K232" s="7"/>
       <c r="L232" s="1"/>
     </row>
-    <row r="233" ht="19.5" customHeight="1">
+    <row r="233" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A233" s="1"/>
       <c r="B233" s="7"/>
       <c r="C233" s="7"/>
@@ -3738,7 +3788,7 @@
       <c r="K233" s="7"/>
       <c r="L233" s="1"/>
     </row>
-    <row r="234" ht="19.5" customHeight="1">
+    <row r="234" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A234" s="1"/>
       <c r="B234" s="7"/>
       <c r="C234" s="7"/>
@@ -3752,7 +3802,7 @@
       <c r="K234" s="7"/>
       <c r="L234" s="1"/>
     </row>
-    <row r="235" ht="19.5" customHeight="1">
+    <row r="235" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A235" s="1"/>
       <c r="B235" s="7"/>
       <c r="C235" s="7"/>
@@ -3766,7 +3816,7 @@
       <c r="K235" s="7"/>
       <c r="L235" s="1"/>
     </row>
-    <row r="236" ht="19.5" customHeight="1">
+    <row r="236" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A236" s="1"/>
       <c r="B236" s="7"/>
       <c r="C236" s="7"/>
@@ -3780,7 +3830,7 @@
       <c r="K236" s="7"/>
       <c r="L236" s="1"/>
     </row>
-    <row r="237" ht="19.5" customHeight="1">
+    <row r="237" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A237" s="1"/>
       <c r="B237" s="7"/>
       <c r="C237" s="7"/>
@@ -3794,7 +3844,7 @@
       <c r="K237" s="7"/>
       <c r="L237" s="1"/>
     </row>
-    <row r="238" ht="19.5" customHeight="1">
+    <row r="238" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A238" s="1"/>
       <c r="B238" s="7"/>
       <c r="C238" s="7"/>
@@ -3808,7 +3858,7 @@
       <c r="K238" s="7"/>
       <c r="L238" s="1"/>
     </row>
-    <row r="239" ht="19.5" customHeight="1">
+    <row r="239" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A239" s="1"/>
       <c r="B239" s="7"/>
       <c r="C239" s="7"/>
@@ -3822,7 +3872,7 @@
       <c r="K239" s="7"/>
       <c r="L239" s="1"/>
     </row>
-    <row r="240" ht="19.5" customHeight="1">
+    <row r="240" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A240" s="1"/>
       <c r="B240" s="7"/>
       <c r="C240" s="7"/>
@@ -3836,7 +3886,7 @@
       <c r="K240" s="7"/>
       <c r="L240" s="1"/>
     </row>
-    <row r="241" ht="19.5" customHeight="1">
+    <row r="241" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A241" s="1"/>
       <c r="B241" s="7"/>
       <c r="C241" s="7"/>
@@ -3850,7 +3900,7 @@
       <c r="K241" s="7"/>
       <c r="L241" s="1"/>
     </row>
-    <row r="242" ht="19.5" customHeight="1">
+    <row r="242" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A242" s="1"/>
       <c r="B242" s="7"/>
       <c r="C242" s="7"/>
@@ -3864,7 +3914,7 @@
       <c r="K242" s="7"/>
       <c r="L242" s="1"/>
     </row>
-    <row r="243" ht="19.5" customHeight="1">
+    <row r="243" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A243" s="1"/>
       <c r="B243" s="7"/>
       <c r="C243" s="7"/>
@@ -3878,7 +3928,7 @@
       <c r="K243" s="7"/>
       <c r="L243" s="1"/>
     </row>
-    <row r="244" ht="19.5" customHeight="1">
+    <row r="244" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A244" s="1"/>
       <c r="B244" s="7"/>
       <c r="C244" s="7"/>
@@ -3892,7 +3942,7 @@
       <c r="K244" s="7"/>
       <c r="L244" s="1"/>
     </row>
-    <row r="245" ht="19.5" customHeight="1">
+    <row r="245" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A245" s="1"/>
       <c r="B245" s="7"/>
       <c r="C245" s="7"/>
@@ -3906,7 +3956,7 @@
       <c r="K245" s="7"/>
       <c r="L245" s="1"/>
     </row>
-    <row r="246" ht="19.5" customHeight="1">
+    <row r="246" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A246" s="1"/>
       <c r="B246" s="7"/>
       <c r="C246" s="7"/>
@@ -3920,7 +3970,7 @@
       <c r="K246" s="7"/>
       <c r="L246" s="1"/>
     </row>
-    <row r="247" ht="19.5" customHeight="1">
+    <row r="247" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A247" s="1"/>
       <c r="B247" s="7"/>
       <c r="C247" s="7"/>
@@ -3934,7 +3984,7 @@
       <c r="K247" s="7"/>
       <c r="L247" s="1"/>
     </row>
-    <row r="248" ht="19.5" customHeight="1">
+    <row r="248" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A248" s="1"/>
       <c r="B248" s="7"/>
       <c r="C248" s="7"/>
@@ -3948,7 +3998,7 @@
       <c r="K248" s="7"/>
       <c r="L248" s="1"/>
     </row>
-    <row r="249" ht="19.5" customHeight="1">
+    <row r="249" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A249" s="1"/>
       <c r="B249" s="7"/>
       <c r="C249" s="7"/>
@@ -3962,7 +4012,7 @@
       <c r="K249" s="7"/>
       <c r="L249" s="1"/>
     </row>
-    <row r="250" ht="19.5" customHeight="1">
+    <row r="250" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A250" s="1"/>
       <c r="B250" s="7"/>
       <c r="C250" s="7"/>
@@ -3976,7 +4026,7 @@
       <c r="K250" s="7"/>
       <c r="L250" s="1"/>
     </row>
-    <row r="251" ht="19.5" customHeight="1">
+    <row r="251" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A251" s="1"/>
       <c r="B251" s="7"/>
       <c r="C251" s="7"/>
@@ -3990,7 +4040,7 @@
       <c r="K251" s="7"/>
       <c r="L251" s="1"/>
     </row>
-    <row r="252" ht="19.5" customHeight="1">
+    <row r="252" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A252" s="1"/>
       <c r="B252" s="7"/>
       <c r="C252" s="7"/>
@@ -4004,7 +4054,7 @@
       <c r="K252" s="7"/>
       <c r="L252" s="1"/>
     </row>
-    <row r="253" ht="19.5" customHeight="1">
+    <row r="253" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A253" s="1"/>
       <c r="B253" s="7"/>
       <c r="C253" s="7"/>
@@ -4018,7 +4068,7 @@
       <c r="K253" s="7"/>
       <c r="L253" s="1"/>
     </row>
-    <row r="254" ht="19.5" customHeight="1">
+    <row r="254" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A254" s="1"/>
       <c r="B254" s="7"/>
       <c r="C254" s="7"/>
@@ -4032,7 +4082,7 @@
       <c r="K254" s="7"/>
       <c r="L254" s="1"/>
     </row>
-    <row r="255" ht="19.5" customHeight="1">
+    <row r="255" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A255" s="1"/>
       <c r="B255" s="7"/>
       <c r="C255" s="7"/>
@@ -4046,7 +4096,7 @@
       <c r="K255" s="7"/>
       <c r="L255" s="1"/>
     </row>
-    <row r="256" ht="19.5" customHeight="1">
+    <row r="256" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A256" s="1"/>
       <c r="B256" s="7"/>
       <c r="C256" s="7"/>
@@ -4060,7 +4110,7 @@
       <c r="K256" s="7"/>
       <c r="L256" s="1"/>
     </row>
-    <row r="257" ht="19.5" customHeight="1">
+    <row r="257" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A257" s="1"/>
       <c r="B257" s="7"/>
       <c r="C257" s="7"/>
@@ -4074,7 +4124,7 @@
       <c r="K257" s="7"/>
       <c r="L257" s="1"/>
     </row>
-    <row r="258" ht="19.5" customHeight="1">
+    <row r="258" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A258" s="1"/>
       <c r="B258" s="7"/>
       <c r="C258" s="7"/>
@@ -4088,7 +4138,7 @@
       <c r="K258" s="7"/>
       <c r="L258" s="1"/>
     </row>
-    <row r="259" ht="19.5" customHeight="1">
+    <row r="259" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A259" s="1"/>
       <c r="B259" s="7"/>
       <c r="C259" s="7"/>
@@ -4102,7 +4152,7 @@
       <c r="K259" s="7"/>
       <c r="L259" s="1"/>
     </row>
-    <row r="260" ht="19.5" customHeight="1">
+    <row r="260" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A260" s="1"/>
       <c r="B260" s="7"/>
       <c r="C260" s="7"/>
@@ -4116,7 +4166,7 @@
       <c r="K260" s="7"/>
       <c r="L260" s="1"/>
     </row>
-    <row r="261" ht="19.5" customHeight="1">
+    <row r="261" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A261" s="1"/>
       <c r="B261" s="7"/>
       <c r="C261" s="7"/>
@@ -4130,7 +4180,7 @@
       <c r="K261" s="7"/>
       <c r="L261" s="1"/>
     </row>
-    <row r="262" ht="19.5" customHeight="1">
+    <row r="262" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A262" s="1"/>
       <c r="B262" s="7"/>
       <c r="C262" s="7"/>
@@ -4144,7 +4194,7 @@
       <c r="K262" s="7"/>
       <c r="L262" s="1"/>
     </row>
-    <row r="263" ht="19.5" customHeight="1">
+    <row r="263" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A263" s="1"/>
       <c r="B263" s="7"/>
       <c r="C263" s="7"/>
@@ -4158,7 +4208,7 @@
       <c r="K263" s="7"/>
       <c r="L263" s="1"/>
     </row>
-    <row r="264" ht="19.5" customHeight="1">
+    <row r="264" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A264" s="1"/>
       <c r="B264" s="7"/>
       <c r="C264" s="7"/>
@@ -4172,7 +4222,7 @@
       <c r="K264" s="7"/>
       <c r="L264" s="1"/>
     </row>
-    <row r="265" ht="19.5" customHeight="1">
+    <row r="265" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A265" s="1"/>
       <c r="B265" s="7"/>
       <c r="C265" s="7"/>
@@ -4186,7 +4236,7 @@
       <c r="K265" s="7"/>
       <c r="L265" s="1"/>
     </row>
-    <row r="266" ht="19.5" customHeight="1">
+    <row r="266" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A266" s="1"/>
       <c r="B266" s="7"/>
       <c r="C266" s="7"/>
@@ -4200,7 +4250,7 @@
       <c r="K266" s="7"/>
       <c r="L266" s="1"/>
     </row>
-    <row r="267" ht="19.5" customHeight="1">
+    <row r="267" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A267" s="1"/>
       <c r="B267" s="7"/>
       <c r="C267" s="7"/>
@@ -4214,7 +4264,7 @@
       <c r="K267" s="7"/>
       <c r="L267" s="1"/>
     </row>
-    <row r="268" ht="19.5" customHeight="1">
+    <row r="268" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A268" s="1"/>
       <c r="B268" s="7"/>
       <c r="C268" s="7"/>
@@ -4228,7 +4278,7 @@
       <c r="K268" s="7"/>
       <c r="L268" s="1"/>
     </row>
-    <row r="269" ht="19.5" customHeight="1">
+    <row r="269" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A269" s="1"/>
       <c r="B269" s="7"/>
       <c r="C269" s="7"/>
@@ -4242,7 +4292,7 @@
       <c r="K269" s="7"/>
       <c r="L269" s="1"/>
     </row>
-    <row r="270" ht="19.5" customHeight="1">
+    <row r="270" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A270" s="1"/>
       <c r="B270" s="7"/>
       <c r="C270" s="7"/>
@@ -4256,7 +4306,7 @@
       <c r="K270" s="7"/>
       <c r="L270" s="1"/>
     </row>
-    <row r="271" ht="19.5" customHeight="1">
+    <row r="271" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A271" s="1"/>
       <c r="B271" s="7"/>
       <c r="C271" s="7"/>
@@ -4270,7 +4320,7 @@
       <c r="K271" s="7"/>
       <c r="L271" s="1"/>
     </row>
-    <row r="272" ht="19.5" customHeight="1">
+    <row r="272" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A272" s="1"/>
       <c r="B272" s="7"/>
       <c r="C272" s="7"/>
@@ -4284,7 +4334,7 @@
       <c r="K272" s="7"/>
       <c r="L272" s="1"/>
     </row>
-    <row r="273" ht="19.5" customHeight="1">
+    <row r="273" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A273" s="1"/>
       <c r="B273" s="7"/>
       <c r="C273" s="7"/>
@@ -4298,7 +4348,7 @@
       <c r="K273" s="7"/>
       <c r="L273" s="1"/>
     </row>
-    <row r="274" ht="19.5" customHeight="1">
+    <row r="274" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A274" s="1"/>
       <c r="B274" s="7"/>
       <c r="C274" s="7"/>
@@ -4312,7 +4362,7 @@
       <c r="K274" s="7"/>
       <c r="L274" s="1"/>
     </row>
-    <row r="275" ht="19.5" customHeight="1">
+    <row r="275" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A275" s="1"/>
       <c r="B275" s="7"/>
       <c r="C275" s="7"/>
@@ -4326,7 +4376,7 @@
       <c r="K275" s="7"/>
       <c r="L275" s="1"/>
     </row>
-    <row r="276" ht="19.5" customHeight="1">
+    <row r="276" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A276" s="1"/>
       <c r="B276" s="7"/>
       <c r="C276" s="7"/>
@@ -4340,7 +4390,7 @@
       <c r="K276" s="7"/>
       <c r="L276" s="1"/>
     </row>
-    <row r="277" ht="19.5" customHeight="1">
+    <row r="277" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A277" s="1"/>
       <c r="B277" s="7"/>
       <c r="C277" s="7"/>
@@ -4354,7 +4404,7 @@
       <c r="K277" s="7"/>
       <c r="L277" s="1"/>
     </row>
-    <row r="278" ht="19.5" customHeight="1">
+    <row r="278" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A278" s="1"/>
       <c r="B278" s="7"/>
       <c r="C278" s="7"/>
@@ -4368,7 +4418,7 @@
       <c r="K278" s="7"/>
       <c r="L278" s="1"/>
     </row>
-    <row r="279" ht="19.5" customHeight="1">
+    <row r="279" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A279" s="1"/>
       <c r="B279" s="7"/>
       <c r="C279" s="7"/>
@@ -4382,7 +4432,7 @@
       <c r="K279" s="7"/>
       <c r="L279" s="1"/>
     </row>
-    <row r="280" ht="19.5" customHeight="1">
+    <row r="280" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A280" s="1"/>
       <c r="B280" s="7"/>
       <c r="C280" s="7"/>
@@ -4396,7 +4446,7 @@
       <c r="K280" s="7"/>
       <c r="L280" s="1"/>
     </row>
-    <row r="281" ht="19.5" customHeight="1">
+    <row r="281" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A281" s="1"/>
       <c r="B281" s="7"/>
       <c r="C281" s="7"/>
@@ -4410,7 +4460,7 @@
       <c r="K281" s="7"/>
       <c r="L281" s="1"/>
     </row>
-    <row r="282" ht="19.5" customHeight="1">
+    <row r="282" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A282" s="1"/>
       <c r="B282" s="7"/>
       <c r="C282" s="7"/>
@@ -4424,7 +4474,7 @@
       <c r="K282" s="7"/>
       <c r="L282" s="1"/>
     </row>
-    <row r="283" ht="19.5" customHeight="1">
+    <row r="283" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A283" s="1"/>
       <c r="B283" s="7"/>
       <c r="C283" s="7"/>
@@ -4438,7 +4488,7 @@
       <c r="K283" s="7"/>
       <c r="L283" s="1"/>
     </row>
-    <row r="284" ht="19.5" customHeight="1">
+    <row r="284" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A284" s="1"/>
       <c r="B284" s="7"/>
       <c r="C284" s="7"/>
@@ -4452,7 +4502,7 @@
       <c r="K284" s="7"/>
       <c r="L284" s="1"/>
     </row>
-    <row r="285" ht="19.5" customHeight="1">
+    <row r="285" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A285" s="1"/>
       <c r="B285" s="7"/>
       <c r="C285" s="7"/>
@@ -4466,7 +4516,7 @@
       <c r="K285" s="7"/>
       <c r="L285" s="1"/>
     </row>
-    <row r="286" ht="19.5" customHeight="1">
+    <row r="286" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A286" s="1"/>
       <c r="B286" s="7"/>
       <c r="C286" s="7"/>
@@ -4480,7 +4530,7 @@
       <c r="K286" s="7"/>
       <c r="L286" s="1"/>
     </row>
-    <row r="287" ht="19.5" customHeight="1">
+    <row r="287" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A287" s="1"/>
       <c r="B287" s="7"/>
       <c r="C287" s="7"/>
@@ -4494,7 +4544,7 @@
       <c r="K287" s="7"/>
       <c r="L287" s="1"/>
     </row>
-    <row r="288" ht="19.5" customHeight="1">
+    <row r="288" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A288" s="1"/>
       <c r="B288" s="7"/>
       <c r="C288" s="7"/>
@@ -4508,7 +4558,7 @@
       <c r="K288" s="7"/>
       <c r="L288" s="1"/>
     </row>
-    <row r="289" ht="19.5" customHeight="1">
+    <row r="289" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A289" s="1"/>
       <c r="B289" s="7"/>
       <c r="C289" s="7"/>
@@ -4522,7 +4572,7 @@
       <c r="K289" s="7"/>
       <c r="L289" s="1"/>
     </row>
-    <row r="290" ht="19.5" customHeight="1">
+    <row r="290" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A290" s="1"/>
       <c r="B290" s="7"/>
       <c r="C290" s="7"/>
@@ -4536,7 +4586,7 @@
       <c r="K290" s="7"/>
       <c r="L290" s="1"/>
     </row>
-    <row r="291" ht="19.5" customHeight="1">
+    <row r="291" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A291" s="1"/>
       <c r="B291" s="7"/>
       <c r="C291" s="7"/>
@@ -4550,7 +4600,7 @@
       <c r="K291" s="7"/>
       <c r="L291" s="1"/>
     </row>
-    <row r="292" ht="19.5" customHeight="1">
+    <row r="292" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A292" s="1"/>
       <c r="B292" s="7"/>
       <c r="C292" s="7"/>
@@ -4564,7 +4614,7 @@
       <c r="K292" s="7"/>
       <c r="L292" s="1"/>
     </row>
-    <row r="293" ht="19.5" customHeight="1">
+    <row r="293" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A293" s="1"/>
       <c r="B293" s="7"/>
       <c r="C293" s="7"/>
@@ -4578,7 +4628,7 @@
       <c r="K293" s="7"/>
       <c r="L293" s="1"/>
     </row>
-    <row r="294" ht="19.5" customHeight="1">
+    <row r="294" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A294" s="1"/>
       <c r="B294" s="7"/>
       <c r="C294" s="7"/>
@@ -4592,7 +4642,7 @@
       <c r="K294" s="7"/>
       <c r="L294" s="1"/>
     </row>
-    <row r="295" ht="19.5" customHeight="1">
+    <row r="295" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A295" s="1"/>
       <c r="B295" s="7"/>
       <c r="C295" s="7"/>
@@ -4606,7 +4656,7 @@
       <c r="K295" s="7"/>
       <c r="L295" s="1"/>
     </row>
-    <row r="296" ht="19.5" customHeight="1">
+    <row r="296" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A296" s="1"/>
       <c r="B296" s="7"/>
       <c r="C296" s="7"/>
@@ -4620,7 +4670,7 @@
       <c r="K296" s="7"/>
       <c r="L296" s="1"/>
     </row>
-    <row r="297" ht="19.5" customHeight="1">
+    <row r="297" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A297" s="1"/>
       <c r="B297" s="7"/>
       <c r="C297" s="7"/>
@@ -4634,7 +4684,7 @@
       <c r="K297" s="7"/>
       <c r="L297" s="1"/>
     </row>
-    <row r="298" ht="19.5" customHeight="1">
+    <row r="298" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A298" s="1"/>
       <c r="B298" s="7"/>
       <c r="C298" s="7"/>
@@ -4648,7 +4698,7 @@
       <c r="K298" s="7"/>
       <c r="L298" s="1"/>
     </row>
-    <row r="299" ht="19.5" customHeight="1">
+    <row r="299" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A299" s="1"/>
       <c r="B299" s="7"/>
       <c r="C299" s="7"/>
@@ -4662,7 +4712,7 @@
       <c r="K299" s="7"/>
       <c r="L299" s="1"/>
     </row>
-    <row r="300" ht="19.5" customHeight="1">
+    <row r="300" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A300" s="1"/>
       <c r="B300" s="7"/>
       <c r="C300" s="7"/>
@@ -4676,7 +4726,7 @@
       <c r="K300" s="7"/>
       <c r="L300" s="1"/>
     </row>
-    <row r="301" ht="19.5" customHeight="1">
+    <row r="301" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A301" s="1"/>
       <c r="B301" s="7"/>
       <c r="C301" s="7"/>
@@ -4690,7 +4740,7 @@
       <c r="K301" s="7"/>
       <c r="L301" s="1"/>
     </row>
-    <row r="302" ht="19.5" customHeight="1">
+    <row r="302" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A302" s="1"/>
       <c r="B302" s="7"/>
       <c r="C302" s="7"/>
@@ -4704,7 +4754,7 @@
       <c r="K302" s="7"/>
       <c r="L302" s="1"/>
     </row>
-    <row r="303" ht="19.5" customHeight="1">
+    <row r="303" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A303" s="1"/>
       <c r="B303" s="7"/>
       <c r="C303" s="7"/>
@@ -4718,7 +4768,7 @@
       <c r="K303" s="7"/>
       <c r="L303" s="1"/>
     </row>
-    <row r="304" ht="19.5" customHeight="1">
+    <row r="304" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A304" s="1"/>
       <c r="B304" s="7"/>
       <c r="C304" s="7"/>
@@ -4732,7 +4782,7 @@
       <c r="K304" s="7"/>
       <c r="L304" s="1"/>
     </row>
-    <row r="305" ht="19.5" customHeight="1">
+    <row r="305" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A305" s="1"/>
       <c r="B305" s="7"/>
       <c r="C305" s="7"/>
@@ -4746,7 +4796,7 @@
       <c r="K305" s="7"/>
       <c r="L305" s="1"/>
     </row>
-    <row r="306" ht="19.5" customHeight="1">
+    <row r="306" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A306" s="1"/>
       <c r="B306" s="7"/>
       <c r="C306" s="7"/>
@@ -4760,7 +4810,7 @@
       <c r="K306" s="7"/>
       <c r="L306" s="1"/>
     </row>
-    <row r="307" ht="19.5" customHeight="1">
+    <row r="307" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A307" s="1"/>
       <c r="B307" s="7"/>
       <c r="C307" s="7"/>
@@ -4774,7 +4824,7 @@
       <c r="K307" s="7"/>
       <c r="L307" s="1"/>
     </row>
-    <row r="308" ht="19.5" customHeight="1">
+    <row r="308" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A308" s="1"/>
       <c r="B308" s="7"/>
       <c r="C308" s="7"/>
@@ -4788,7 +4838,7 @@
       <c r="K308" s="7"/>
       <c r="L308" s="1"/>
     </row>
-    <row r="309" ht="19.5" customHeight="1">
+    <row r="309" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A309" s="1"/>
       <c r="B309" s="7"/>
       <c r="C309" s="7"/>
@@ -4802,7 +4852,7 @@
       <c r="K309" s="7"/>
       <c r="L309" s="1"/>
     </row>
-    <row r="310" ht="19.5" customHeight="1">
+    <row r="310" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A310" s="1"/>
       <c r="B310" s="7"/>
       <c r="C310" s="7"/>
@@ -4816,7 +4866,7 @@
       <c r="K310" s="7"/>
       <c r="L310" s="1"/>
     </row>
-    <row r="311" ht="19.5" customHeight="1">
+    <row r="311" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A311" s="1"/>
       <c r="B311" s="7"/>
       <c r="C311" s="7"/>
@@ -4830,7 +4880,7 @@
       <c r="K311" s="7"/>
       <c r="L311" s="1"/>
     </row>
-    <row r="312" ht="19.5" customHeight="1">
+    <row r="312" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A312" s="1"/>
       <c r="B312" s="7"/>
       <c r="C312" s="7"/>
@@ -4844,7 +4894,7 @@
       <c r="K312" s="7"/>
       <c r="L312" s="1"/>
     </row>
-    <row r="313" ht="19.5" customHeight="1">
+    <row r="313" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A313" s="1"/>
       <c r="B313" s="7"/>
       <c r="C313" s="7"/>
@@ -4858,7 +4908,7 @@
       <c r="K313" s="7"/>
       <c r="L313" s="1"/>
     </row>
-    <row r="314" ht="19.5" customHeight="1">
+    <row r="314" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A314" s="1"/>
       <c r="B314" s="7"/>
       <c r="C314" s="7"/>
@@ -4872,7 +4922,7 @@
       <c r="K314" s="7"/>
       <c r="L314" s="1"/>
     </row>
-    <row r="315" ht="19.5" customHeight="1">
+    <row r="315" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A315" s="1"/>
       <c r="B315" s="7"/>
       <c r="C315" s="7"/>
@@ -4886,7 +4936,7 @@
       <c r="K315" s="7"/>
       <c r="L315" s="1"/>
     </row>
-    <row r="316" ht="19.5" customHeight="1">
+    <row r="316" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A316" s="1"/>
       <c r="B316" s="7"/>
       <c r="C316" s="7"/>
@@ -4900,7 +4950,7 @@
       <c r="K316" s="7"/>
       <c r="L316" s="1"/>
     </row>
-    <row r="317" ht="19.5" customHeight="1">
+    <row r="317" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A317" s="1"/>
       <c r="B317" s="7"/>
       <c r="C317" s="7"/>
@@ -4914,7 +4964,7 @@
       <c r="K317" s="7"/>
       <c r="L317" s="1"/>
     </row>
-    <row r="318" ht="19.5" customHeight="1">
+    <row r="318" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A318" s="1"/>
       <c r="B318" s="7"/>
       <c r="C318" s="7"/>
@@ -4928,7 +4978,7 @@
       <c r="K318" s="7"/>
       <c r="L318" s="1"/>
     </row>
-    <row r="319" ht="19.5" customHeight="1">
+    <row r="319" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A319" s="1"/>
       <c r="B319" s="7"/>
       <c r="C319" s="7"/>
@@ -4942,7 +4992,7 @@
       <c r="K319" s="7"/>
       <c r="L319" s="1"/>
     </row>
-    <row r="320" ht="19.5" customHeight="1">
+    <row r="320" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A320" s="1"/>
       <c r="B320" s="7"/>
       <c r="C320" s="7"/>
@@ -4956,7 +5006,7 @@
       <c r="K320" s="7"/>
       <c r="L320" s="1"/>
     </row>
-    <row r="321" ht="19.5" customHeight="1">
+    <row r="321" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A321" s="1"/>
       <c r="B321" s="7"/>
       <c r="C321" s="7"/>
@@ -4970,7 +5020,7 @@
       <c r="K321" s="7"/>
       <c r="L321" s="1"/>
     </row>
-    <row r="322" ht="19.5" customHeight="1">
+    <row r="322" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A322" s="1"/>
       <c r="B322" s="7"/>
       <c r="C322" s="7"/>
@@ -4984,7 +5034,7 @@
       <c r="K322" s="7"/>
       <c r="L322" s="1"/>
     </row>
-    <row r="323" ht="19.5" customHeight="1">
+    <row r="323" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A323" s="1"/>
       <c r="B323" s="7"/>
       <c r="C323" s="7"/>
@@ -4998,7 +5048,7 @@
       <c r="K323" s="7"/>
       <c r="L323" s="1"/>
     </row>
-    <row r="324" ht="19.5" customHeight="1">
+    <row r="324" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A324" s="1"/>
       <c r="B324" s="7"/>
       <c r="C324" s="7"/>
@@ -5012,7 +5062,7 @@
       <c r="K324" s="7"/>
       <c r="L324" s="1"/>
     </row>
-    <row r="325" ht="19.5" customHeight="1">
+    <row r="325" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A325" s="1"/>
       <c r="B325" s="7"/>
       <c r="C325" s="7"/>
@@ -5026,7 +5076,7 @@
       <c r="K325" s="7"/>
       <c r="L325" s="1"/>
     </row>
-    <row r="326" ht="19.5" customHeight="1">
+    <row r="326" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A326" s="1"/>
       <c r="B326" s="7"/>
       <c r="C326" s="7"/>
@@ -5040,7 +5090,7 @@
       <c r="K326" s="7"/>
       <c r="L326" s="1"/>
     </row>
-    <row r="327" ht="19.5" customHeight="1">
+    <row r="327" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A327" s="1"/>
       <c r="B327" s="7"/>
       <c r="C327" s="7"/>
@@ -5054,7 +5104,7 @@
       <c r="K327" s="7"/>
       <c r="L327" s="1"/>
     </row>
-    <row r="328" ht="19.5" customHeight="1">
+    <row r="328" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A328" s="1"/>
       <c r="B328" s="7"/>
       <c r="C328" s="7"/>
@@ -5068,7 +5118,7 @@
       <c r="K328" s="7"/>
       <c r="L328" s="1"/>
     </row>
-    <row r="329" ht="19.5" customHeight="1">
+    <row r="329" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A329" s="1"/>
       <c r="B329" s="7"/>
       <c r="C329" s="7"/>
@@ -5082,7 +5132,7 @@
       <c r="K329" s="7"/>
       <c r="L329" s="1"/>
     </row>
-    <row r="330" ht="19.5" customHeight="1">
+    <row r="330" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A330" s="1"/>
       <c r="B330" s="7"/>
       <c r="C330" s="7"/>
@@ -5096,7 +5146,7 @@
       <c r="K330" s="7"/>
       <c r="L330" s="1"/>
     </row>
-    <row r="331" ht="19.5" customHeight="1">
+    <row r="331" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A331" s="1"/>
       <c r="B331" s="7"/>
       <c r="C331" s="7"/>
@@ -5110,7 +5160,7 @@
       <c r="K331" s="7"/>
       <c r="L331" s="1"/>
     </row>
-    <row r="332" ht="19.5" customHeight="1">
+    <row r="332" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A332" s="1"/>
       <c r="B332" s="7"/>
       <c r="C332" s="7"/>
@@ -5124,7 +5174,7 @@
       <c r="K332" s="7"/>
       <c r="L332" s="1"/>
     </row>
-    <row r="333" ht="19.5" customHeight="1">
+    <row r="333" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A333" s="1"/>
       <c r="B333" s="7"/>
       <c r="C333" s="7"/>
@@ -5138,7 +5188,7 @@
       <c r="K333" s="7"/>
       <c r="L333" s="1"/>
     </row>
-    <row r="334" ht="19.5" customHeight="1">
+    <row r="334" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A334" s="1"/>
       <c r="B334" s="7"/>
       <c r="C334" s="7"/>
@@ -5152,7 +5202,7 @@
       <c r="K334" s="7"/>
       <c r="L334" s="1"/>
     </row>
-    <row r="335" ht="19.5" customHeight="1">
+    <row r="335" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A335" s="1"/>
       <c r="B335" s="7"/>
       <c r="C335" s="7"/>
@@ -5166,7 +5216,7 @@
       <c r="K335" s="7"/>
       <c r="L335" s="1"/>
     </row>
-    <row r="336" ht="19.5" customHeight="1">
+    <row r="336" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A336" s="1"/>
       <c r="B336" s="7"/>
       <c r="C336" s="7"/>
@@ -5180,7 +5230,7 @@
       <c r="K336" s="7"/>
       <c r="L336" s="1"/>
     </row>
-    <row r="337" ht="19.5" customHeight="1">
+    <row r="337" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A337" s="1"/>
       <c r="B337" s="7"/>
       <c r="C337" s="7"/>
@@ -5194,7 +5244,7 @@
       <c r="K337" s="7"/>
       <c r="L337" s="1"/>
     </row>
-    <row r="338" ht="19.5" customHeight="1">
+    <row r="338" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A338" s="1"/>
       <c r="B338" s="7"/>
       <c r="C338" s="7"/>
@@ -5208,7 +5258,7 @@
       <c r="K338" s="7"/>
       <c r="L338" s="1"/>
     </row>
-    <row r="339" ht="19.5" customHeight="1">
+    <row r="339" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A339" s="1"/>
       <c r="B339" s="7"/>
       <c r="C339" s="7"/>
@@ -5222,7 +5272,7 @@
       <c r="K339" s="7"/>
       <c r="L339" s="1"/>
     </row>
-    <row r="340" ht="19.5" customHeight="1">
+    <row r="340" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A340" s="1"/>
       <c r="B340" s="7"/>
       <c r="C340" s="7"/>
@@ -5236,7 +5286,7 @@
       <c r="K340" s="7"/>
       <c r="L340" s="1"/>
     </row>
-    <row r="341" ht="19.5" customHeight="1">
+    <row r="341" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A341" s="1"/>
       <c r="B341" s="7"/>
       <c r="C341" s="7"/>
@@ -5250,7 +5300,7 @@
       <c r="K341" s="7"/>
       <c r="L341" s="1"/>
     </row>
-    <row r="342" ht="19.5" customHeight="1">
+    <row r="342" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A342" s="1"/>
       <c r="B342" s="7"/>
       <c r="C342" s="7"/>
@@ -5264,7 +5314,7 @@
       <c r="K342" s="7"/>
       <c r="L342" s="1"/>
     </row>
-    <row r="343" ht="19.5" customHeight="1">
+    <row r="343" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A343" s="1"/>
       <c r="B343" s="7"/>
       <c r="C343" s="7"/>
@@ -5278,7 +5328,7 @@
       <c r="K343" s="7"/>
       <c r="L343" s="1"/>
     </row>
-    <row r="344" ht="19.5" customHeight="1">
+    <row r="344" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A344" s="1"/>
       <c r="B344" s="7"/>
       <c r="C344" s="7"/>
@@ -5292,7 +5342,7 @@
       <c r="K344" s="7"/>
       <c r="L344" s="1"/>
     </row>
-    <row r="345" ht="19.5" customHeight="1">
+    <row r="345" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A345" s="1"/>
       <c r="B345" s="7"/>
       <c r="C345" s="7"/>
@@ -5306,7 +5356,7 @@
       <c r="K345" s="7"/>
       <c r="L345" s="1"/>
     </row>
-    <row r="346" ht="19.5" customHeight="1">
+    <row r="346" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A346" s="1"/>
       <c r="B346" s="7"/>
       <c r="C346" s="7"/>
@@ -5320,7 +5370,7 @@
       <c r="K346" s="7"/>
       <c r="L346" s="1"/>
     </row>
-    <row r="347" ht="19.5" customHeight="1">
+    <row r="347" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A347" s="1"/>
       <c r="B347" s="7"/>
       <c r="C347" s="7"/>
@@ -5334,7 +5384,7 @@
       <c r="K347" s="7"/>
       <c r="L347" s="1"/>
     </row>
-    <row r="348" ht="19.5" customHeight="1">
+    <row r="348" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A348" s="1"/>
       <c r="B348" s="7"/>
       <c r="C348" s="7"/>
@@ -5348,7 +5398,7 @@
       <c r="K348" s="7"/>
       <c r="L348" s="1"/>
     </row>
-    <row r="349" ht="19.5" customHeight="1">
+    <row r="349" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A349" s="1"/>
       <c r="B349" s="7"/>
       <c r="C349" s="7"/>
@@ -5362,7 +5412,7 @@
       <c r="K349" s="7"/>
       <c r="L349" s="1"/>
     </row>
-    <row r="350" ht="19.5" customHeight="1">
+    <row r="350" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A350" s="1"/>
       <c r="B350" s="7"/>
       <c r="C350" s="7"/>
@@ -5376,7 +5426,7 @@
       <c r="K350" s="7"/>
       <c r="L350" s="1"/>
     </row>
-    <row r="351" ht="19.5" customHeight="1">
+    <row r="351" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A351" s="1"/>
       <c r="B351" s="7"/>
       <c r="C351" s="7"/>
@@ -5390,7 +5440,7 @@
       <c r="K351" s="7"/>
       <c r="L351" s="1"/>
     </row>
-    <row r="352" ht="19.5" customHeight="1">
+    <row r="352" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A352" s="1"/>
       <c r="B352" s="7"/>
       <c r="C352" s="7"/>
@@ -5404,7 +5454,7 @@
       <c r="K352" s="7"/>
       <c r="L352" s="1"/>
     </row>
-    <row r="353" ht="19.5" customHeight="1">
+    <row r="353" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A353" s="1"/>
       <c r="B353" s="7"/>
       <c r="C353" s="7"/>
@@ -5418,7 +5468,7 @@
       <c r="K353" s="7"/>
       <c r="L353" s="1"/>
     </row>
-    <row r="354" ht="19.5" customHeight="1">
+    <row r="354" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A354" s="1"/>
       <c r="B354" s="7"/>
       <c r="C354" s="7"/>
@@ -5432,7 +5482,7 @@
       <c r="K354" s="7"/>
       <c r="L354" s="1"/>
     </row>
-    <row r="355" ht="19.5" customHeight="1">
+    <row r="355" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A355" s="1"/>
       <c r="B355" s="7"/>
       <c r="C355" s="7"/>
@@ -5446,7 +5496,7 @@
       <c r="K355" s="7"/>
       <c r="L355" s="1"/>
     </row>
-    <row r="356" ht="19.5" customHeight="1">
+    <row r="356" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A356" s="1"/>
       <c r="B356" s="7"/>
       <c r="C356" s="7"/>
@@ -5460,7 +5510,7 @@
       <c r="K356" s="7"/>
       <c r="L356" s="1"/>
     </row>
-    <row r="357" ht="19.5" customHeight="1">
+    <row r="357" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A357" s="1"/>
       <c r="B357" s="7"/>
       <c r="C357" s="7"/>
@@ -5474,7 +5524,7 @@
       <c r="K357" s="7"/>
       <c r="L357" s="1"/>
     </row>
-    <row r="358" ht="19.5" customHeight="1">
+    <row r="358" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A358" s="1"/>
       <c r="B358" s="7"/>
       <c r="C358" s="7"/>
@@ -5488,7 +5538,7 @@
       <c r="K358" s="7"/>
       <c r="L358" s="1"/>
     </row>
-    <row r="359" ht="19.5" customHeight="1">
+    <row r="359" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A359" s="1"/>
       <c r="B359" s="7"/>
       <c r="C359" s="7"/>
@@ -5502,7 +5552,7 @@
       <c r="K359" s="7"/>
       <c r="L359" s="1"/>
     </row>
-    <row r="360" ht="19.5" customHeight="1">
+    <row r="360" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A360" s="1"/>
       <c r="B360" s="7"/>
       <c r="C360" s="7"/>
@@ -5516,7 +5566,7 @@
       <c r="K360" s="7"/>
       <c r="L360" s="1"/>
     </row>
-    <row r="361" ht="19.5" customHeight="1">
+    <row r="361" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A361" s="1"/>
       <c r="B361" s="7"/>
       <c r="C361" s="7"/>
@@ -5530,7 +5580,7 @@
       <c r="K361" s="7"/>
       <c r="L361" s="1"/>
     </row>
-    <row r="362" ht="19.5" customHeight="1">
+    <row r="362" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A362" s="1"/>
       <c r="B362" s="7"/>
       <c r="C362" s="7"/>
@@ -5544,7 +5594,7 @@
       <c r="K362" s="7"/>
       <c r="L362" s="1"/>
     </row>
-    <row r="363" ht="19.5" customHeight="1">
+    <row r="363" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A363" s="1"/>
       <c r="B363" s="7"/>
       <c r="C363" s="7"/>
@@ -5558,7 +5608,7 @@
       <c r="K363" s="7"/>
       <c r="L363" s="1"/>
     </row>
-    <row r="364" ht="19.5" customHeight="1">
+    <row r="364" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A364" s="1"/>
       <c r="B364" s="7"/>
       <c r="C364" s="7"/>
@@ -5572,7 +5622,7 @@
       <c r="K364" s="7"/>
       <c r="L364" s="1"/>
     </row>
-    <row r="365" ht="19.5" customHeight="1">
+    <row r="365" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A365" s="1"/>
       <c r="B365" s="7"/>
       <c r="C365" s="7"/>
@@ -5586,7 +5636,7 @@
       <c r="K365" s="7"/>
       <c r="L365" s="1"/>
     </row>
-    <row r="366" ht="19.5" customHeight="1">
+    <row r="366" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A366" s="1"/>
       <c r="B366" s="7"/>
       <c r="C366" s="7"/>
@@ -5600,7 +5650,7 @@
       <c r="K366" s="7"/>
       <c r="L366" s="1"/>
     </row>
-    <row r="367" ht="19.5" customHeight="1">
+    <row r="367" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A367" s="1"/>
       <c r="B367" s="7"/>
       <c r="C367" s="7"/>
@@ -5614,7 +5664,7 @@
       <c r="K367" s="7"/>
       <c r="L367" s="1"/>
     </row>
-    <row r="368" ht="19.5" customHeight="1">
+    <row r="368" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A368" s="1"/>
       <c r="B368" s="7"/>
       <c r="C368" s="7"/>
@@ -5628,7 +5678,7 @@
       <c r="K368" s="7"/>
       <c r="L368" s="1"/>
     </row>
-    <row r="369" ht="19.5" customHeight="1">
+    <row r="369" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A369" s="1"/>
       <c r="B369" s="7"/>
       <c r="C369" s="7"/>
@@ -5642,7 +5692,7 @@
       <c r="K369" s="7"/>
       <c r="L369" s="1"/>
     </row>
-    <row r="370" ht="19.5" customHeight="1">
+    <row r="370" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A370" s="1"/>
       <c r="B370" s="7"/>
       <c r="C370" s="7"/>
@@ -5656,7 +5706,7 @@
       <c r="K370" s="7"/>
       <c r="L370" s="1"/>
     </row>
-    <row r="371" ht="19.5" customHeight="1">
+    <row r="371" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A371" s="1"/>
       <c r="B371" s="7"/>
       <c r="C371" s="7"/>
@@ -5670,7 +5720,7 @@
       <c r="K371" s="7"/>
       <c r="L371" s="1"/>
     </row>
-    <row r="372" ht="19.5" customHeight="1">
+    <row r="372" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A372" s="1"/>
       <c r="B372" s="7"/>
       <c r="C372" s="7"/>
@@ -5684,7 +5734,7 @@
       <c r="K372" s="7"/>
       <c r="L372" s="1"/>
     </row>
-    <row r="373" ht="19.5" customHeight="1">
+    <row r="373" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A373" s="1"/>
       <c r="B373" s="7"/>
       <c r="C373" s="7"/>
@@ -5698,7 +5748,7 @@
       <c r="K373" s="7"/>
       <c r="L373" s="1"/>
     </row>
-    <row r="374" ht="19.5" customHeight="1">
+    <row r="374" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A374" s="1"/>
       <c r="B374" s="7"/>
       <c r="C374" s="7"/>
@@ -5712,7 +5762,7 @@
       <c r="K374" s="7"/>
       <c r="L374" s="1"/>
     </row>
-    <row r="375" ht="19.5" customHeight="1">
+    <row r="375" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A375" s="1"/>
       <c r="B375" s="7"/>
       <c r="C375" s="7"/>
@@ -5726,7 +5776,7 @@
       <c r="K375" s="7"/>
       <c r="L375" s="1"/>
     </row>
-    <row r="376" ht="19.5" customHeight="1">
+    <row r="376" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A376" s="1"/>
       <c r="B376" s="7"/>
       <c r="C376" s="7"/>
@@ -5740,7 +5790,7 @@
       <c r="K376" s="7"/>
       <c r="L376" s="1"/>
     </row>
-    <row r="377" ht="19.5" customHeight="1">
+    <row r="377" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A377" s="1"/>
       <c r="B377" s="7"/>
       <c r="C377" s="7"/>
@@ -5754,7 +5804,7 @@
       <c r="K377" s="7"/>
       <c r="L377" s="1"/>
     </row>
-    <row r="378" ht="19.5" customHeight="1">
+    <row r="378" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A378" s="1"/>
       <c r="B378" s="7"/>
       <c r="C378" s="7"/>
@@ -5768,7 +5818,7 @@
       <c r="K378" s="7"/>
       <c r="L378" s="1"/>
     </row>
-    <row r="379" ht="19.5" customHeight="1">
+    <row r="379" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A379" s="1"/>
       <c r="B379" s="7"/>
       <c r="C379" s="7"/>
@@ -5782,7 +5832,7 @@
       <c r="K379" s="7"/>
       <c r="L379" s="1"/>
     </row>
-    <row r="380" ht="19.5" customHeight="1">
+    <row r="380" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A380" s="1"/>
       <c r="B380" s="7"/>
       <c r="C380" s="7"/>
@@ -5796,7 +5846,7 @@
       <c r="K380" s="7"/>
       <c r="L380" s="1"/>
     </row>
-    <row r="381" ht="19.5" customHeight="1">
+    <row r="381" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A381" s="1"/>
       <c r="B381" s="7"/>
       <c r="C381" s="7"/>
@@ -5810,7 +5860,7 @@
       <c r="K381" s="7"/>
       <c r="L381" s="1"/>
     </row>
-    <row r="382" ht="19.5" customHeight="1">
+    <row r="382" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A382" s="1"/>
       <c r="B382" s="7"/>
       <c r="C382" s="7"/>
@@ -5824,7 +5874,7 @@
       <c r="K382" s="7"/>
       <c r="L382" s="1"/>
     </row>
-    <row r="383" ht="19.5" customHeight="1">
+    <row r="383" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A383" s="1"/>
       <c r="B383" s="7"/>
       <c r="C383" s="7"/>
@@ -5838,7 +5888,7 @@
       <c r="K383" s="7"/>
       <c r="L383" s="1"/>
     </row>
-    <row r="384" ht="19.5" customHeight="1">
+    <row r="384" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A384" s="1"/>
       <c r="B384" s="7"/>
       <c r="C384" s="7"/>
@@ -5852,7 +5902,7 @@
       <c r="K384" s="7"/>
       <c r="L384" s="1"/>
     </row>
-    <row r="385" ht="19.5" customHeight="1">
+    <row r="385" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A385" s="1"/>
       <c r="B385" s="7"/>
       <c r="C385" s="7"/>
@@ -5866,7 +5916,7 @@
       <c r="K385" s="7"/>
       <c r="L385" s="1"/>
     </row>
-    <row r="386" ht="19.5" customHeight="1">
+    <row r="386" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A386" s="1"/>
       <c r="B386" s="7"/>
       <c r="C386" s="7"/>
@@ -5880,7 +5930,7 @@
       <c r="K386" s="7"/>
       <c r="L386" s="1"/>
     </row>
-    <row r="387" ht="19.5" customHeight="1">
+    <row r="387" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A387" s="1"/>
       <c r="B387" s="7"/>
       <c r="C387" s="7"/>
@@ -5894,7 +5944,7 @@
       <c r="K387" s="7"/>
       <c r="L387" s="1"/>
     </row>
-    <row r="388" ht="19.5" customHeight="1">
+    <row r="388" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A388" s="1"/>
       <c r="B388" s="7"/>
       <c r="C388" s="7"/>
@@ -5908,7 +5958,7 @@
       <c r="K388" s="7"/>
       <c r="L388" s="1"/>
     </row>
-    <row r="389" ht="19.5" customHeight="1">
+    <row r="389" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A389" s="1"/>
       <c r="B389" s="7"/>
       <c r="C389" s="7"/>
@@ -5922,7 +5972,7 @@
       <c r="K389" s="7"/>
       <c r="L389" s="1"/>
     </row>
-    <row r="390" ht="19.5" customHeight="1">
+    <row r="390" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A390" s="1"/>
       <c r="B390" s="7"/>
       <c r="C390" s="7"/>
@@ -5936,7 +5986,7 @@
       <c r="K390" s="7"/>
       <c r="L390" s="1"/>
     </row>
-    <row r="391" ht="19.5" customHeight="1">
+    <row r="391" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A391" s="1"/>
       <c r="B391" s="7"/>
       <c r="C391" s="7"/>
@@ -5950,7 +6000,7 @@
       <c r="K391" s="7"/>
       <c r="L391" s="1"/>
     </row>
-    <row r="392" ht="19.5" customHeight="1">
+    <row r="392" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A392" s="1"/>
       <c r="B392" s="7"/>
       <c r="C392" s="7"/>
@@ -5964,7 +6014,7 @@
       <c r="K392" s="7"/>
       <c r="L392" s="1"/>
     </row>
-    <row r="393" ht="19.5" customHeight="1">
+    <row r="393" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A393" s="1"/>
       <c r="B393" s="7"/>
       <c r="C393" s="7"/>
@@ -5978,7 +6028,7 @@
       <c r="K393" s="7"/>
       <c r="L393" s="1"/>
     </row>
-    <row r="394" ht="19.5" customHeight="1">
+    <row r="394" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A394" s="1"/>
       <c r="B394" s="7"/>
       <c r="C394" s="7"/>
@@ -5992,7 +6042,7 @@
       <c r="K394" s="7"/>
       <c r="L394" s="1"/>
     </row>
-    <row r="395" ht="19.5" customHeight="1">
+    <row r="395" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A395" s="1"/>
       <c r="B395" s="7"/>
       <c r="C395" s="7"/>
@@ -6006,7 +6056,7 @@
       <c r="K395" s="7"/>
       <c r="L395" s="1"/>
     </row>
-    <row r="396" ht="19.5" customHeight="1">
+    <row r="396" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A396" s="1"/>
       <c r="B396" s="7"/>
       <c r="C396" s="7"/>
@@ -6020,7 +6070,7 @@
       <c r="K396" s="7"/>
       <c r="L396" s="1"/>
     </row>
-    <row r="397" ht="19.5" customHeight="1">
+    <row r="397" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A397" s="1"/>
       <c r="B397" s="7"/>
       <c r="C397" s="7"/>
@@ -6034,7 +6084,7 @@
       <c r="K397" s="7"/>
       <c r="L397" s="1"/>
     </row>
-    <row r="398" ht="19.5" customHeight="1">
+    <row r="398" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A398" s="1"/>
       <c r="B398" s="7"/>
       <c r="C398" s="7"/>
@@ -6048,7 +6098,7 @@
       <c r="K398" s="7"/>
       <c r="L398" s="1"/>
     </row>
-    <row r="399" ht="19.5" customHeight="1">
+    <row r="399" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A399" s="1"/>
       <c r="B399" s="7"/>
       <c r="C399" s="7"/>
@@ -6062,7 +6112,7 @@
       <c r="K399" s="7"/>
       <c r="L399" s="1"/>
     </row>
-    <row r="400" ht="19.5" customHeight="1">
+    <row r="400" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A400" s="1"/>
       <c r="B400" s="7"/>
       <c r="C400" s="7"/>
@@ -6076,7 +6126,7 @@
       <c r="K400" s="7"/>
       <c r="L400" s="1"/>
     </row>
-    <row r="401" ht="19.5" customHeight="1">
+    <row r="401" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A401" s="1"/>
       <c r="B401" s="7"/>
       <c r="C401" s="7"/>
@@ -6090,7 +6140,7 @@
       <c r="K401" s="7"/>
       <c r="L401" s="1"/>
     </row>
-    <row r="402" ht="19.5" customHeight="1">
+    <row r="402" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A402" s="1"/>
       <c r="B402" s="7"/>
       <c r="C402" s="7"/>
@@ -6104,7 +6154,7 @@
       <c r="K402" s="7"/>
       <c r="L402" s="1"/>
     </row>
-    <row r="403" ht="19.5" customHeight="1">
+    <row r="403" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A403" s="1"/>
       <c r="B403" s="7"/>
       <c r="C403" s="7"/>
@@ -6118,7 +6168,7 @@
       <c r="K403" s="7"/>
       <c r="L403" s="1"/>
     </row>
-    <row r="404" ht="19.5" customHeight="1">
+    <row r="404" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A404" s="1"/>
       <c r="B404" s="7"/>
       <c r="C404" s="7"/>
@@ -6132,7 +6182,7 @@
       <c r="K404" s="7"/>
       <c r="L404" s="1"/>
     </row>
-    <row r="405" ht="19.5" customHeight="1">
+    <row r="405" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A405" s="1"/>
       <c r="B405" s="7"/>
       <c r="C405" s="7"/>
@@ -6146,7 +6196,7 @@
       <c r="K405" s="7"/>
       <c r="L405" s="1"/>
     </row>
-    <row r="406" ht="19.5" customHeight="1">
+    <row r="406" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A406" s="1"/>
       <c r="B406" s="7"/>
       <c r="C406" s="7"/>
@@ -6160,7 +6210,7 @@
       <c r="K406" s="7"/>
       <c r="L406" s="1"/>
     </row>
-    <row r="407" ht="19.5" customHeight="1">
+    <row r="407" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A407" s="1"/>
       <c r="B407" s="7"/>
       <c r="C407" s="7"/>
@@ -6174,7 +6224,7 @@
       <c r="K407" s="7"/>
       <c r="L407" s="1"/>
     </row>
-    <row r="408" ht="19.5" customHeight="1">
+    <row r="408" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A408" s="1"/>
       <c r="B408" s="7"/>
       <c r="C408" s="7"/>
@@ -6188,7 +6238,7 @@
       <c r="K408" s="7"/>
       <c r="L408" s="1"/>
     </row>
-    <row r="409" ht="19.5" customHeight="1">
+    <row r="409" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A409" s="1"/>
       <c r="B409" s="7"/>
       <c r="C409" s="7"/>
@@ -6202,7 +6252,7 @@
       <c r="K409" s="7"/>
       <c r="L409" s="1"/>
     </row>
-    <row r="410" ht="19.5" customHeight="1">
+    <row r="410" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A410" s="1"/>
       <c r="B410" s="7"/>
       <c r="C410" s="7"/>
@@ -6216,7 +6266,7 @@
       <c r="K410" s="7"/>
       <c r="L410" s="1"/>
     </row>
-    <row r="411" ht="19.5" customHeight="1">
+    <row r="411" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A411" s="1"/>
       <c r="B411" s="7"/>
       <c r="C411" s="7"/>
@@ -6230,7 +6280,7 @@
       <c r="K411" s="7"/>
       <c r="L411" s="1"/>
     </row>
-    <row r="412" ht="19.5" customHeight="1">
+    <row r="412" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A412" s="1"/>
       <c r="B412" s="7"/>
       <c r="C412" s="7"/>
@@ -6244,7 +6294,7 @@
       <c r="K412" s="7"/>
       <c r="L412" s="1"/>
     </row>
-    <row r="413" ht="19.5" customHeight="1">
+    <row r="413" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A413" s="1"/>
       <c r="B413" s="7"/>
       <c r="C413" s="7"/>
@@ -6258,7 +6308,7 @@
       <c r="K413" s="7"/>
       <c r="L413" s="1"/>
     </row>
-    <row r="414" ht="19.5" customHeight="1">
+    <row r="414" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A414" s="1"/>
       <c r="B414" s="7"/>
       <c r="C414" s="7"/>
@@ -6272,7 +6322,7 @@
       <c r="K414" s="7"/>
       <c r="L414" s="1"/>
     </row>
-    <row r="415" ht="19.5" customHeight="1">
+    <row r="415" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A415" s="1"/>
       <c r="B415" s="7"/>
       <c r="C415" s="7"/>
@@ -6286,7 +6336,7 @@
       <c r="K415" s="7"/>
       <c r="L415" s="1"/>
     </row>
-    <row r="416" ht="19.5" customHeight="1">
+    <row r="416" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A416" s="1"/>
       <c r="B416" s="7"/>
       <c r="C416" s="7"/>
@@ -6300,7 +6350,7 @@
       <c r="K416" s="7"/>
       <c r="L416" s="1"/>
     </row>
-    <row r="417" ht="19.5" customHeight="1">
+    <row r="417" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A417" s="1"/>
       <c r="B417" s="7"/>
       <c r="C417" s="7"/>
@@ -6314,7 +6364,7 @@
       <c r="K417" s="7"/>
       <c r="L417" s="1"/>
     </row>
-    <row r="418" ht="19.5" customHeight="1">
+    <row r="418" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A418" s="1"/>
       <c r="B418" s="7"/>
       <c r="C418" s="7"/>
@@ -6328,7 +6378,7 @@
       <c r="K418" s="7"/>
       <c r="L418" s="1"/>
     </row>
-    <row r="419" ht="19.5" customHeight="1">
+    <row r="419" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A419" s="1"/>
       <c r="B419" s="7"/>
       <c r="C419" s="7"/>
@@ -6342,7 +6392,7 @@
       <c r="K419" s="7"/>
       <c r="L419" s="1"/>
     </row>
-    <row r="420" ht="19.5" customHeight="1">
+    <row r="420" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A420" s="1"/>
       <c r="B420" s="7"/>
       <c r="C420" s="7"/>
@@ -6356,7 +6406,7 @@
       <c r="K420" s="7"/>
       <c r="L420" s="1"/>
     </row>
-    <row r="421" ht="19.5" customHeight="1">
+    <row r="421" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A421" s="1"/>
       <c r="B421" s="7"/>
       <c r="C421" s="7"/>
@@ -6370,7 +6420,7 @@
       <c r="K421" s="7"/>
       <c r="L421" s="1"/>
     </row>
-    <row r="422" ht="19.5" customHeight="1">
+    <row r="422" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A422" s="1"/>
       <c r="B422" s="7"/>
       <c r="C422" s="7"/>
@@ -6384,7 +6434,7 @@
       <c r="K422" s="7"/>
       <c r="L422" s="1"/>
     </row>
-    <row r="423" ht="19.5" customHeight="1">
+    <row r="423" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A423" s="1"/>
       <c r="B423" s="7"/>
       <c r="C423" s="7"/>
@@ -6398,7 +6448,7 @@
       <c r="K423" s="7"/>
       <c r="L423" s="1"/>
     </row>
-    <row r="424" ht="19.5" customHeight="1">
+    <row r="424" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A424" s="1"/>
       <c r="B424" s="7"/>
       <c r="C424" s="7"/>
@@ -6412,7 +6462,7 @@
       <c r="K424" s="7"/>
       <c r="L424" s="1"/>
     </row>
-    <row r="425" ht="19.5" customHeight="1">
+    <row r="425" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A425" s="1"/>
       <c r="B425" s="7"/>
       <c r="C425" s="7"/>
@@ -6426,7 +6476,7 @@
       <c r="K425" s="7"/>
       <c r="L425" s="1"/>
     </row>
-    <row r="426" ht="19.5" customHeight="1">
+    <row r="426" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A426" s="1"/>
       <c r="B426" s="7"/>
       <c r="C426" s="7"/>
@@ -6440,7 +6490,7 @@
       <c r="K426" s="7"/>
       <c r="L426" s="1"/>
     </row>
-    <row r="427" ht="19.5" customHeight="1">
+    <row r="427" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A427" s="1"/>
       <c r="B427" s="7"/>
       <c r="C427" s="7"/>
@@ -6454,7 +6504,7 @@
       <c r="K427" s="7"/>
       <c r="L427" s="1"/>
     </row>
-    <row r="428" ht="19.5" customHeight="1">
+    <row r="428" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A428" s="1"/>
       <c r="B428" s="7"/>
       <c r="C428" s="7"/>
@@ -6468,7 +6518,7 @@
       <c r="K428" s="7"/>
       <c r="L428" s="1"/>
     </row>
-    <row r="429" ht="19.5" customHeight="1">
+    <row r="429" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A429" s="1"/>
       <c r="B429" s="7"/>
       <c r="C429" s="7"/>
@@ -6482,7 +6532,7 @@
       <c r="K429" s="7"/>
       <c r="L429" s="1"/>
     </row>
-    <row r="430" ht="19.5" customHeight="1">
+    <row r="430" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A430" s="1"/>
       <c r="B430" s="7"/>
       <c r="C430" s="7"/>
@@ -6496,7 +6546,7 @@
       <c r="K430" s="7"/>
       <c r="L430" s="1"/>
     </row>
-    <row r="431" ht="19.5" customHeight="1">
+    <row r="431" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A431" s="1"/>
       <c r="B431" s="7"/>
       <c r="C431" s="7"/>
@@ -6510,7 +6560,7 @@
       <c r="K431" s="7"/>
       <c r="L431" s="1"/>
     </row>
-    <row r="432" ht="19.5" customHeight="1">
+    <row r="432" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A432" s="1"/>
       <c r="B432" s="7"/>
       <c r="C432" s="7"/>
@@ -6524,7 +6574,7 @@
       <c r="K432" s="7"/>
       <c r="L432" s="1"/>
     </row>
-    <row r="433" ht="19.5" customHeight="1">
+    <row r="433" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A433" s="1"/>
       <c r="B433" s="7"/>
       <c r="C433" s="7"/>
@@ -6538,7 +6588,7 @@
       <c r="K433" s="7"/>
       <c r="L433" s="1"/>
     </row>
-    <row r="434" ht="19.5" customHeight="1">
+    <row r="434" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A434" s="1"/>
       <c r="B434" s="7"/>
       <c r="C434" s="7"/>
@@ -6552,7 +6602,7 @@
       <c r="K434" s="7"/>
       <c r="L434" s="1"/>
     </row>
-    <row r="435" ht="19.5" customHeight="1">
+    <row r="435" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A435" s="1"/>
       <c r="B435" s="7"/>
       <c r="C435" s="7"/>
@@ -6566,7 +6616,7 @@
       <c r="K435" s="7"/>
       <c r="L435" s="1"/>
     </row>
-    <row r="436" ht="19.5" customHeight="1">
+    <row r="436" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A436" s="1"/>
       <c r="B436" s="7"/>
       <c r="C436" s="7"/>
@@ -6580,7 +6630,7 @@
       <c r="K436" s="7"/>
       <c r="L436" s="1"/>
     </row>
-    <row r="437" ht="19.5" customHeight="1">
+    <row r="437" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A437" s="1"/>
       <c r="B437" s="7"/>
       <c r="C437" s="7"/>
@@ -6594,7 +6644,7 @@
       <c r="K437" s="7"/>
       <c r="L437" s="1"/>
     </row>
-    <row r="438" ht="19.5" customHeight="1">
+    <row r="438" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A438" s="1"/>
       <c r="B438" s="7"/>
       <c r="C438" s="7"/>
@@ -6608,7 +6658,7 @@
       <c r="K438" s="7"/>
       <c r="L438" s="1"/>
     </row>
-    <row r="439" ht="19.5" customHeight="1">
+    <row r="439" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A439" s="1"/>
       <c r="B439" s="7"/>
       <c r="C439" s="7"/>
@@ -6622,7 +6672,7 @@
       <c r="K439" s="7"/>
       <c r="L439" s="1"/>
     </row>
-    <row r="440" ht="19.5" customHeight="1">
+    <row r="440" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A440" s="1"/>
       <c r="B440" s="7"/>
       <c r="C440" s="7"/>
@@ -6636,7 +6686,7 @@
       <c r="K440" s="7"/>
       <c r="L440" s="1"/>
     </row>
-    <row r="441" ht="19.5" customHeight="1">
+    <row r="441" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A441" s="1"/>
       <c r="B441" s="7"/>
       <c r="C441" s="7"/>
@@ -6650,7 +6700,7 @@
       <c r="K441" s="7"/>
       <c r="L441" s="1"/>
     </row>
-    <row r="442" ht="19.5" customHeight="1">
+    <row r="442" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A442" s="1"/>
       <c r="B442" s="7"/>
       <c r="C442" s="7"/>
@@ -6664,7 +6714,7 @@
       <c r="K442" s="7"/>
       <c r="L442" s="1"/>
     </row>
-    <row r="443" ht="19.5" customHeight="1">
+    <row r="443" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A443" s="1"/>
       <c r="B443" s="7"/>
       <c r="C443" s="7"/>
@@ -6678,7 +6728,7 @@
       <c r="K443" s="7"/>
       <c r="L443" s="1"/>
     </row>
-    <row r="444" ht="19.5" customHeight="1">
+    <row r="444" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A444" s="1"/>
       <c r="B444" s="7"/>
       <c r="C444" s="7"/>
@@ -6692,7 +6742,7 @@
       <c r="K444" s="7"/>
       <c r="L444" s="1"/>
     </row>
-    <row r="445" ht="19.5" customHeight="1">
+    <row r="445" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A445" s="1"/>
       <c r="B445" s="7"/>
       <c r="C445" s="7"/>
@@ -6706,7 +6756,7 @@
       <c r="K445" s="7"/>
       <c r="L445" s="1"/>
     </row>
-    <row r="446" ht="19.5" customHeight="1">
+    <row r="446" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A446" s="1"/>
       <c r="B446" s="7"/>
       <c r="C446" s="7"/>
@@ -6720,7 +6770,7 @@
       <c r="K446" s="7"/>
       <c r="L446" s="1"/>
     </row>
-    <row r="447" ht="19.5" customHeight="1">
+    <row r="447" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A447" s="1"/>
       <c r="B447" s="7"/>
       <c r="C447" s="7"/>
@@ -6734,7 +6784,7 @@
       <c r="K447" s="7"/>
       <c r="L447" s="1"/>
     </row>
-    <row r="448" ht="19.5" customHeight="1">
+    <row r="448" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A448" s="1"/>
       <c r="B448" s="7"/>
       <c r="C448" s="7"/>
@@ -6748,7 +6798,7 @@
       <c r="K448" s="7"/>
       <c r="L448" s="1"/>
     </row>
-    <row r="449" ht="19.5" customHeight="1">
+    <row r="449" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A449" s="1"/>
       <c r="B449" s="7"/>
       <c r="C449" s="7"/>
@@ -6762,7 +6812,7 @@
       <c r="K449" s="7"/>
       <c r="L449" s="1"/>
     </row>
-    <row r="450" ht="19.5" customHeight="1">
+    <row r="450" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A450" s="1"/>
       <c r="B450" s="7"/>
       <c r="C450" s="7"/>
@@ -6776,7 +6826,7 @@
       <c r="K450" s="7"/>
       <c r="L450" s="1"/>
     </row>
-    <row r="451" ht="19.5" customHeight="1">
+    <row r="451" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A451" s="1"/>
       <c r="B451" s="7"/>
       <c r="C451" s="7"/>
@@ -6790,7 +6840,7 @@
       <c r="K451" s="7"/>
       <c r="L451" s="1"/>
     </row>
-    <row r="452" ht="19.5" customHeight="1">
+    <row r="452" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A452" s="1"/>
       <c r="B452" s="7"/>
       <c r="C452" s="7"/>
@@ -6804,7 +6854,7 @@
       <c r="K452" s="7"/>
       <c r="L452" s="1"/>
     </row>
-    <row r="453" ht="19.5" customHeight="1">
+    <row r="453" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A453" s="1"/>
       <c r="B453" s="7"/>
       <c r="C453" s="7"/>
@@ -6818,7 +6868,7 @@
       <c r="K453" s="7"/>
       <c r="L453" s="1"/>
     </row>
-    <row r="454" ht="19.5" customHeight="1">
+    <row r="454" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A454" s="1"/>
       <c r="B454" s="7"/>
       <c r="C454" s="7"/>
@@ -6832,7 +6882,7 @@
       <c r="K454" s="7"/>
       <c r="L454" s="1"/>
     </row>
-    <row r="455" ht="19.5" customHeight="1">
+    <row r="455" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A455" s="1"/>
       <c r="B455" s="7"/>
       <c r="C455" s="7"/>
@@ -6846,7 +6896,7 @@
       <c r="K455" s="7"/>
       <c r="L455" s="1"/>
     </row>
-    <row r="456" ht="19.5" customHeight="1">
+    <row r="456" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A456" s="1"/>
       <c r="B456" s="7"/>
       <c r="C456" s="7"/>
@@ -6860,7 +6910,7 @@
       <c r="K456" s="7"/>
       <c r="L456" s="1"/>
     </row>
-    <row r="457" ht="19.5" customHeight="1">
+    <row r="457" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A457" s="1"/>
       <c r="B457" s="7"/>
       <c r="C457" s="7"/>
@@ -6874,7 +6924,7 @@
       <c r="K457" s="7"/>
       <c r="L457" s="1"/>
     </row>
-    <row r="458" ht="19.5" customHeight="1">
+    <row r="458" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A458" s="1"/>
       <c r="B458" s="7"/>
       <c r="C458" s="7"/>
@@ -6888,7 +6938,7 @@
       <c r="K458" s="7"/>
       <c r="L458" s="1"/>
     </row>
-    <row r="459" ht="19.5" customHeight="1">
+    <row r="459" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A459" s="1"/>
       <c r="B459" s="7"/>
       <c r="C459" s="7"/>
@@ -6902,7 +6952,7 @@
       <c r="K459" s="7"/>
       <c r="L459" s="1"/>
     </row>
-    <row r="460" ht="19.5" customHeight="1">
+    <row r="460" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A460" s="1"/>
       <c r="B460" s="7"/>
       <c r="C460" s="7"/>
@@ -6916,7 +6966,7 @@
       <c r="K460" s="7"/>
       <c r="L460" s="1"/>
     </row>
-    <row r="461" ht="19.5" customHeight="1">
+    <row r="461" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A461" s="1"/>
       <c r="B461" s="7"/>
       <c r="C461" s="7"/>
@@ -6930,7 +6980,7 @@
       <c r="K461" s="7"/>
       <c r="L461" s="1"/>
     </row>
-    <row r="462" ht="19.5" customHeight="1">
+    <row r="462" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A462" s="1"/>
       <c r="B462" s="7"/>
       <c r="C462" s="7"/>
@@ -6944,7 +6994,7 @@
       <c r="K462" s="7"/>
       <c r="L462" s="1"/>
     </row>
-    <row r="463" ht="19.5" customHeight="1">
+    <row r="463" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A463" s="1"/>
       <c r="B463" s="7"/>
       <c r="C463" s="7"/>
@@ -6958,7 +7008,7 @@
       <c r="K463" s="7"/>
       <c r="L463" s="1"/>
     </row>
-    <row r="464" ht="19.5" customHeight="1">
+    <row r="464" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A464" s="1"/>
       <c r="B464" s="7"/>
       <c r="C464" s="7"/>
@@ -6972,7 +7022,7 @@
       <c r="K464" s="7"/>
       <c r="L464" s="1"/>
     </row>
-    <row r="465" ht="19.5" customHeight="1">
+    <row r="465" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A465" s="1"/>
       <c r="B465" s="7"/>
       <c r="C465" s="7"/>
@@ -6986,7 +7036,7 @@
       <c r="K465" s="7"/>
       <c r="L465" s="1"/>
     </row>
-    <row r="466" ht="19.5" customHeight="1">
+    <row r="466" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A466" s="1"/>
       <c r="B466" s="7"/>
       <c r="C466" s="7"/>
@@ -7000,7 +7050,7 @@
       <c r="K466" s="7"/>
       <c r="L466" s="1"/>
     </row>
-    <row r="467" ht="19.5" customHeight="1">
+    <row r="467" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A467" s="1"/>
       <c r="B467" s="7"/>
       <c r="C467" s="7"/>
@@ -7014,7 +7064,7 @@
       <c r="K467" s="7"/>
       <c r="L467" s="1"/>
     </row>
-    <row r="468" ht="19.5" customHeight="1">
+    <row r="468" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A468" s="1"/>
       <c r="B468" s="7"/>
       <c r="C468" s="7"/>
@@ -7028,7 +7078,7 @@
       <c r="K468" s="7"/>
       <c r="L468" s="1"/>
     </row>
-    <row r="469" ht="19.5" customHeight="1">
+    <row r="469" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A469" s="1"/>
       <c r="B469" s="7"/>
       <c r="C469" s="7"/>
@@ -7042,7 +7092,7 @@
       <c r="K469" s="7"/>
       <c r="L469" s="1"/>
     </row>
-    <row r="470" ht="19.5" customHeight="1">
+    <row r="470" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A470" s="1"/>
       <c r="B470" s="7"/>
       <c r="C470" s="7"/>
@@ -7056,7 +7106,7 @@
       <c r="K470" s="7"/>
       <c r="L470" s="1"/>
     </row>
-    <row r="471" ht="19.5" customHeight="1">
+    <row r="471" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A471" s="1"/>
       <c r="B471" s="7"/>
       <c r="C471" s="7"/>
@@ -7070,7 +7120,7 @@
       <c r="K471" s="7"/>
       <c r="L471" s="1"/>
     </row>
-    <row r="472" ht="19.5" customHeight="1">
+    <row r="472" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A472" s="1"/>
       <c r="B472" s="7"/>
       <c r="C472" s="7"/>
@@ -7084,7 +7134,7 @@
       <c r="K472" s="7"/>
       <c r="L472" s="1"/>
     </row>
-    <row r="473" ht="19.5" customHeight="1">
+    <row r="473" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A473" s="1"/>
       <c r="B473" s="7"/>
       <c r="C473" s="7"/>
@@ -7098,7 +7148,7 @@
       <c r="K473" s="7"/>
       <c r="L473" s="1"/>
     </row>
-    <row r="474" ht="19.5" customHeight="1">
+    <row r="474" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A474" s="1"/>
       <c r="B474" s="7"/>
       <c r="C474" s="7"/>
@@ -7112,7 +7162,7 @@
       <c r="K474" s="7"/>
       <c r="L474" s="1"/>
     </row>
-    <row r="475" ht="19.5" customHeight="1">
+    <row r="475" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A475" s="1"/>
       <c r="B475" s="7"/>
       <c r="C475" s="7"/>
@@ -7126,7 +7176,7 @@
       <c r="K475" s="7"/>
       <c r="L475" s="1"/>
     </row>
-    <row r="476" ht="19.5" customHeight="1">
+    <row r="476" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A476" s="1"/>
       <c r="B476" s="7"/>
       <c r="C476" s="7"/>
@@ -7140,7 +7190,7 @@
       <c r="K476" s="7"/>
       <c r="L476" s="1"/>
     </row>
-    <row r="477" ht="19.5" customHeight="1">
+    <row r="477" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A477" s="1"/>
       <c r="B477" s="7"/>
       <c r="C477" s="7"/>
@@ -7154,7 +7204,7 @@
       <c r="K477" s="7"/>
       <c r="L477" s="1"/>
     </row>
-    <row r="478" ht="19.5" customHeight="1">
+    <row r="478" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A478" s="1"/>
       <c r="B478" s="7"/>
       <c r="C478" s="7"/>
@@ -7168,7 +7218,7 @@
       <c r="K478" s="7"/>
       <c r="L478" s="1"/>
     </row>
-    <row r="479" ht="19.5" customHeight="1">
+    <row r="479" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A479" s="1"/>
       <c r="B479" s="7"/>
       <c r="C479" s="7"/>
@@ -7182,7 +7232,7 @@
       <c r="K479" s="7"/>
       <c r="L479" s="1"/>
     </row>
-    <row r="480" ht="19.5" customHeight="1">
+    <row r="480" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A480" s="1"/>
       <c r="B480" s="7"/>
       <c r="C480" s="7"/>
@@ -7196,7 +7246,7 @@
       <c r="K480" s="7"/>
       <c r="L480" s="1"/>
     </row>
-    <row r="481" ht="19.5" customHeight="1">
+    <row r="481" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A481" s="1"/>
       <c r="B481" s="7"/>
       <c r="C481" s="7"/>
@@ -7210,7 +7260,7 @@
       <c r="K481" s="7"/>
       <c r="L481" s="1"/>
     </row>
-    <row r="482" ht="19.5" customHeight="1">
+    <row r="482" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A482" s="1"/>
       <c r="B482" s="7"/>
       <c r="C482" s="7"/>
@@ -7224,7 +7274,7 @@
       <c r="K482" s="7"/>
       <c r="L482" s="1"/>
     </row>
-    <row r="483" ht="19.5" customHeight="1">
+    <row r="483" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A483" s="1"/>
       <c r="B483" s="7"/>
       <c r="C483" s="7"/>
@@ -7238,7 +7288,7 @@
       <c r="K483" s="7"/>
       <c r="L483" s="1"/>
     </row>
-    <row r="484" ht="19.5" customHeight="1">
+    <row r="484" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A484" s="1"/>
       <c r="B484" s="7"/>
       <c r="C484" s="7"/>
@@ -7252,7 +7302,7 @@
       <c r="K484" s="7"/>
       <c r="L484" s="1"/>
     </row>
-    <row r="485" ht="19.5" customHeight="1">
+    <row r="485" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A485" s="1"/>
       <c r="B485" s="7"/>
       <c r="C485" s="7"/>
@@ -7266,7 +7316,7 @@
       <c r="K485" s="7"/>
       <c r="L485" s="1"/>
     </row>
-    <row r="486" ht="19.5" customHeight="1">
+    <row r="486" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A486" s="1"/>
       <c r="B486" s="7"/>
       <c r="C486" s="7"/>
@@ -7280,7 +7330,7 @@
       <c r="K486" s="7"/>
       <c r="L486" s="1"/>
     </row>
-    <row r="487" ht="19.5" customHeight="1">
+    <row r="487" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A487" s="1"/>
       <c r="B487" s="7"/>
       <c r="C487" s="7"/>
@@ -7294,7 +7344,7 @@
       <c r="K487" s="7"/>
       <c r="L487" s="1"/>
     </row>
-    <row r="488" ht="19.5" customHeight="1">
+    <row r="488" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A488" s="1"/>
       <c r="B488" s="7"/>
       <c r="C488" s="7"/>
@@ -7308,7 +7358,7 @@
       <c r="K488" s="7"/>
       <c r="L488" s="1"/>
     </row>
-    <row r="489" ht="19.5" customHeight="1">
+    <row r="489" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A489" s="1"/>
       <c r="B489" s="7"/>
       <c r="C489" s="7"/>
@@ -7322,7 +7372,7 @@
       <c r="K489" s="7"/>
       <c r="L489" s="1"/>
     </row>
-    <row r="490" ht="19.5" customHeight="1">
+    <row r="490" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A490" s="1"/>
       <c r="B490" s="7"/>
       <c r="C490" s="7"/>
@@ -7336,7 +7386,7 @@
       <c r="K490" s="7"/>
       <c r="L490" s="1"/>
     </row>
-    <row r="491" ht="19.5" customHeight="1">
+    <row r="491" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A491" s="1"/>
       <c r="B491" s="7"/>
       <c r="C491" s="7"/>
@@ -7350,7 +7400,7 @@
       <c r="K491" s="7"/>
       <c r="L491" s="1"/>
     </row>
-    <row r="492" ht="19.5" customHeight="1">
+    <row r="492" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A492" s="1"/>
       <c r="B492" s="7"/>
       <c r="C492" s="7"/>
@@ -7364,7 +7414,7 @@
       <c r="K492" s="7"/>
       <c r="L492" s="1"/>
     </row>
-    <row r="493" ht="19.5" customHeight="1">
+    <row r="493" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A493" s="1"/>
       <c r="B493" s="7"/>
       <c r="C493" s="7"/>
@@ -7378,7 +7428,7 @@
       <c r="K493" s="7"/>
       <c r="L493" s="1"/>
     </row>
-    <row r="494" ht="19.5" customHeight="1">
+    <row r="494" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A494" s="1"/>
       <c r="B494" s="7"/>
       <c r="C494" s="7"/>
@@ -7392,7 +7442,7 @@
       <c r="K494" s="7"/>
       <c r="L494" s="1"/>
     </row>
-    <row r="495" ht="19.5" customHeight="1">
+    <row r="495" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A495" s="1"/>
       <c r="B495" s="7"/>
       <c r="C495" s="7"/>
@@ -7406,7 +7456,7 @@
       <c r="K495" s="7"/>
       <c r="L495" s="1"/>
     </row>
-    <row r="496" ht="19.5" customHeight="1">
+    <row r="496" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A496" s="1"/>
       <c r="B496" s="7"/>
       <c r="C496" s="7"/>
@@ -7420,7 +7470,7 @@
       <c r="K496" s="7"/>
       <c r="L496" s="1"/>
     </row>
-    <row r="497" ht="19.5" customHeight="1">
+    <row r="497" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A497" s="1"/>
       <c r="B497" s="7"/>
       <c r="C497" s="7"/>
@@ -7434,7 +7484,7 @@
       <c r="K497" s="7"/>
       <c r="L497" s="1"/>
     </row>
-    <row r="498" ht="19.5" customHeight="1">
+    <row r="498" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A498" s="1"/>
       <c r="B498" s="7"/>
       <c r="C498" s="7"/>
@@ -7448,7 +7498,7 @@
       <c r="K498" s="7"/>
       <c r="L498" s="1"/>
     </row>
-    <row r="499" ht="19.5" customHeight="1">
+    <row r="499" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A499" s="1"/>
       <c r="B499" s="7"/>
       <c r="C499" s="7"/>
@@ -7462,7 +7512,7 @@
       <c r="K499" s="7"/>
       <c r="L499" s="1"/>
     </row>
-    <row r="500" ht="19.5" customHeight="1">
+    <row r="500" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A500" s="1"/>
       <c r="B500" s="7"/>
       <c r="C500" s="7"/>
@@ -7476,7 +7526,7 @@
       <c r="K500" s="7"/>
       <c r="L500" s="1"/>
     </row>
-    <row r="501" ht="19.5" customHeight="1">
+    <row r="501" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A501" s="1"/>
       <c r="B501" s="7"/>
       <c r="C501" s="7"/>
@@ -7490,7 +7540,7 @@
       <c r="K501" s="7"/>
       <c r="L501" s="1"/>
     </row>
-    <row r="502" ht="19.5" customHeight="1">
+    <row r="502" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A502" s="1"/>
       <c r="B502" s="7"/>
       <c r="C502" s="7"/>
@@ -7504,7 +7554,7 @@
       <c r="K502" s="7"/>
       <c r="L502" s="1"/>
     </row>
-    <row r="503" ht="19.5" customHeight="1">
+    <row r="503" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A503" s="1"/>
       <c r="B503" s="7"/>
       <c r="C503" s="7"/>
@@ -7518,7 +7568,7 @@
       <c r="K503" s="7"/>
       <c r="L503" s="1"/>
     </row>
-    <row r="504" ht="19.5" customHeight="1">
+    <row r="504" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A504" s="1"/>
       <c r="B504" s="7"/>
       <c r="C504" s="7"/>
@@ -7532,7 +7582,7 @@
       <c r="K504" s="7"/>
       <c r="L504" s="1"/>
     </row>
-    <row r="505" ht="19.5" customHeight="1">
+    <row r="505" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A505" s="1"/>
       <c r="B505" s="7"/>
       <c r="C505" s="7"/>
@@ -7546,7 +7596,7 @@
       <c r="K505" s="7"/>
       <c r="L505" s="1"/>
     </row>
-    <row r="506" ht="19.5" customHeight="1">
+    <row r="506" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A506" s="1"/>
       <c r="B506" s="7"/>
       <c r="C506" s="7"/>
@@ -7560,7 +7610,7 @@
       <c r="K506" s="7"/>
       <c r="L506" s="1"/>
     </row>
-    <row r="507" ht="19.5" customHeight="1">
+    <row r="507" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A507" s="1"/>
       <c r="B507" s="7"/>
       <c r="C507" s="7"/>
@@ -7574,7 +7624,7 @@
       <c r="K507" s="7"/>
       <c r="L507" s="1"/>
     </row>
-    <row r="508" ht="19.5" customHeight="1">
+    <row r="508" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A508" s="1"/>
       <c r="B508" s="7"/>
       <c r="C508" s="7"/>
@@ -7588,7 +7638,7 @@
       <c r="K508" s="7"/>
       <c r="L508" s="1"/>
     </row>
-    <row r="509" ht="19.5" customHeight="1">
+    <row r="509" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A509" s="1"/>
       <c r="B509" s="7"/>
       <c r="C509" s="7"/>
@@ -7602,7 +7652,7 @@
       <c r="K509" s="7"/>
       <c r="L509" s="1"/>
     </row>
-    <row r="510" ht="19.5" customHeight="1">
+    <row r="510" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A510" s="1"/>
       <c r="B510" s="7"/>
       <c r="C510" s="7"/>
@@ -7616,7 +7666,7 @@
       <c r="K510" s="7"/>
       <c r="L510" s="1"/>
     </row>
-    <row r="511" ht="19.5" customHeight="1">
+    <row r="511" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A511" s="1"/>
       <c r="B511" s="7"/>
       <c r="C511" s="7"/>
@@ -7630,7 +7680,7 @@
       <c r="K511" s="7"/>
       <c r="L511" s="1"/>
     </row>
-    <row r="512" ht="19.5" customHeight="1">
+    <row r="512" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A512" s="1"/>
       <c r="B512" s="7"/>
       <c r="C512" s="7"/>
@@ -7644,7 +7694,7 @@
       <c r="K512" s="7"/>
       <c r="L512" s="1"/>
     </row>
-    <row r="513" ht="19.5" customHeight="1">
+    <row r="513" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A513" s="1"/>
       <c r="B513" s="7"/>
       <c r="C513" s="7"/>
@@ -7658,7 +7708,7 @@
       <c r="K513" s="7"/>
       <c r="L513" s="1"/>
     </row>
-    <row r="514" ht="19.5" customHeight="1">
+    <row r="514" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A514" s="1"/>
       <c r="B514" s="7"/>
       <c r="C514" s="7"/>
@@ -7672,7 +7722,7 @@
       <c r="K514" s="7"/>
       <c r="L514" s="1"/>
     </row>
-    <row r="515" ht="19.5" customHeight="1">
+    <row r="515" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A515" s="1"/>
       <c r="B515" s="7"/>
       <c r="C515" s="7"/>
@@ -7686,7 +7736,7 @@
       <c r="K515" s="7"/>
       <c r="L515" s="1"/>
     </row>
-    <row r="516" ht="19.5" customHeight="1">
+    <row r="516" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A516" s="1"/>
       <c r="B516" s="7"/>
       <c r="C516" s="7"/>
@@ -7700,7 +7750,7 @@
       <c r="K516" s="7"/>
       <c r="L516" s="1"/>
     </row>
-    <row r="517" ht="19.5" customHeight="1">
+    <row r="517" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A517" s="1"/>
       <c r="B517" s="7"/>
       <c r="C517" s="7"/>
@@ -7714,7 +7764,7 @@
       <c r="K517" s="7"/>
       <c r="L517" s="1"/>
     </row>
-    <row r="518" ht="19.5" customHeight="1">
+    <row r="518" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A518" s="1"/>
       <c r="B518" s="7"/>
       <c r="C518" s="7"/>
@@ -7728,7 +7778,7 @@
       <c r="K518" s="7"/>
       <c r="L518" s="1"/>
     </row>
-    <row r="519" ht="19.5" customHeight="1">
+    <row r="519" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A519" s="1"/>
       <c r="B519" s="7"/>
       <c r="C519" s="7"/>
@@ -7742,7 +7792,7 @@
       <c r="K519" s="7"/>
       <c r="L519" s="1"/>
     </row>
-    <row r="520" ht="19.5" customHeight="1">
+    <row r="520" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A520" s="1"/>
       <c r="B520" s="7"/>
       <c r="C520" s="7"/>
@@ -7756,7 +7806,7 @@
       <c r="K520" s="7"/>
       <c r="L520" s="1"/>
     </row>
-    <row r="521" ht="19.5" customHeight="1">
+    <row r="521" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A521" s="1"/>
       <c r="B521" s="7"/>
       <c r="C521" s="7"/>
@@ -7770,7 +7820,7 @@
       <c r="K521" s="7"/>
       <c r="L521" s="1"/>
     </row>
-    <row r="522" ht="19.5" customHeight="1">
+    <row r="522" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A522" s="1"/>
       <c r="B522" s="7"/>
       <c r="C522" s="7"/>
@@ -7784,7 +7834,7 @@
       <c r="K522" s="7"/>
       <c r="L522" s="1"/>
     </row>
-    <row r="523" ht="19.5" customHeight="1">
+    <row r="523" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A523" s="1"/>
       <c r="B523" s="7"/>
       <c r="C523" s="7"/>
@@ -7798,7 +7848,7 @@
       <c r="K523" s="7"/>
       <c r="L523" s="1"/>
     </row>
-    <row r="524" ht="19.5" customHeight="1">
+    <row r="524" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A524" s="1"/>
       <c r="B524" s="7"/>
       <c r="C524" s="7"/>
@@ -7812,7 +7862,7 @@
       <c r="K524" s="7"/>
       <c r="L524" s="1"/>
     </row>
-    <row r="525" ht="19.5" customHeight="1">
+    <row r="525" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A525" s="1"/>
       <c r="B525" s="7"/>
       <c r="C525" s="7"/>
@@ -7826,7 +7876,7 @@
       <c r="K525" s="7"/>
       <c r="L525" s="1"/>
     </row>
-    <row r="526" ht="19.5" customHeight="1">
+    <row r="526" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A526" s="1"/>
       <c r="B526" s="7"/>
       <c r="C526" s="7"/>
@@ -7840,7 +7890,7 @@
       <c r="K526" s="7"/>
       <c r="L526" s="1"/>
     </row>
-    <row r="527" ht="19.5" customHeight="1">
+    <row r="527" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A527" s="1"/>
       <c r="B527" s="7"/>
       <c r="C527" s="7"/>
@@ -7854,7 +7904,7 @@
       <c r="K527" s="7"/>
       <c r="L527" s="1"/>
     </row>
-    <row r="528" ht="19.5" customHeight="1">
+    <row r="528" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A528" s="1"/>
       <c r="B528" s="7"/>
       <c r="C528" s="7"/>
@@ -7868,7 +7918,7 @@
       <c r="K528" s="7"/>
       <c r="L528" s="1"/>
     </row>
-    <row r="529" ht="19.5" customHeight="1">
+    <row r="529" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A529" s="1"/>
       <c r="B529" s="7"/>
       <c r="C529" s="7"/>
@@ -7882,7 +7932,7 @@
       <c r="K529" s="7"/>
       <c r="L529" s="1"/>
     </row>
-    <row r="530" ht="19.5" customHeight="1">
+    <row r="530" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A530" s="1"/>
       <c r="B530" s="7"/>
       <c r="C530" s="7"/>
@@ -7896,7 +7946,7 @@
       <c r="K530" s="7"/>
       <c r="L530" s="1"/>
     </row>
-    <row r="531" ht="19.5" customHeight="1">
+    <row r="531" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A531" s="1"/>
       <c r="B531" s="7"/>
       <c r="C531" s="7"/>
@@ -7910,7 +7960,7 @@
       <c r="K531" s="7"/>
       <c r="L531" s="1"/>
     </row>
-    <row r="532" ht="19.5" customHeight="1">
+    <row r="532" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A532" s="1"/>
       <c r="B532" s="7"/>
       <c r="C532" s="7"/>
@@ -7924,7 +7974,7 @@
       <c r="K532" s="7"/>
       <c r="L532" s="1"/>
     </row>
-    <row r="533" ht="19.5" customHeight="1">
+    <row r="533" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A533" s="1"/>
       <c r="B533" s="7"/>
       <c r="C533" s="7"/>
@@ -7938,7 +7988,7 @@
       <c r="K533" s="7"/>
       <c r="L533" s="1"/>
     </row>
-    <row r="534" ht="19.5" customHeight="1">
+    <row r="534" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A534" s="1"/>
       <c r="B534" s="7"/>
       <c r="C534" s="7"/>
@@ -7952,7 +8002,7 @@
       <c r="K534" s="7"/>
       <c r="L534" s="1"/>
     </row>
-    <row r="535" ht="19.5" customHeight="1">
+    <row r="535" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A535" s="1"/>
       <c r="B535" s="7"/>
       <c r="C535" s="7"/>
@@ -7966,7 +8016,7 @@
       <c r="K535" s="7"/>
       <c r="L535" s="1"/>
     </row>
-    <row r="536" ht="19.5" customHeight="1">
+    <row r="536" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A536" s="1"/>
       <c r="B536" s="7"/>
       <c r="C536" s="7"/>
@@ -7980,7 +8030,7 @@
       <c r="K536" s="7"/>
       <c r="L536" s="1"/>
     </row>
-    <row r="537" ht="19.5" customHeight="1">
+    <row r="537" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A537" s="1"/>
       <c r="B537" s="7"/>
       <c r="C537" s="7"/>
@@ -7994,7 +8044,7 @@
       <c r="K537" s="7"/>
       <c r="L537" s="1"/>
     </row>
-    <row r="538" ht="19.5" customHeight="1">
+    <row r="538" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A538" s="1"/>
       <c r="B538" s="7"/>
       <c r="C538" s="7"/>
@@ -8008,7 +8058,7 @@
       <c r="K538" s="7"/>
       <c r="L538" s="1"/>
     </row>
-    <row r="539" ht="19.5" customHeight="1">
+    <row r="539" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A539" s="1"/>
       <c r="B539" s="7"/>
       <c r="C539" s="7"/>
@@ -8022,7 +8072,7 @@
       <c r="K539" s="7"/>
       <c r="L539" s="1"/>
     </row>
-    <row r="540" ht="19.5" customHeight="1">
+    <row r="540" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A540" s="1"/>
       <c r="B540" s="7"/>
       <c r="C540" s="7"/>
@@ -8036,7 +8086,7 @@
       <c r="K540" s="7"/>
       <c r="L540" s="1"/>
     </row>
-    <row r="541" ht="19.5" customHeight="1">
+    <row r="541" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A541" s="1"/>
       <c r="B541" s="7"/>
       <c r="C541" s="7"/>
@@ -8050,7 +8100,7 @@
       <c r="K541" s="7"/>
       <c r="L541" s="1"/>
     </row>
-    <row r="542" ht="19.5" customHeight="1">
+    <row r="542" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A542" s="1"/>
       <c r="B542" s="7"/>
       <c r="C542" s="7"/>
@@ -8064,7 +8114,7 @@
       <c r="K542" s="7"/>
       <c r="L542" s="1"/>
     </row>
-    <row r="543" ht="19.5" customHeight="1">
+    <row r="543" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A543" s="1"/>
       <c r="B543" s="7"/>
       <c r="C543" s="7"/>
@@ -8078,7 +8128,7 @@
       <c r="K543" s="7"/>
       <c r="L543" s="1"/>
     </row>
-    <row r="544" ht="19.5" customHeight="1">
+    <row r="544" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A544" s="1"/>
       <c r="B544" s="7"/>
       <c r="C544" s="7"/>
@@ -8092,7 +8142,7 @@
       <c r="K544" s="7"/>
       <c r="L544" s="1"/>
     </row>
-    <row r="545" ht="19.5" customHeight="1">
+    <row r="545" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A545" s="1"/>
       <c r="B545" s="7"/>
       <c r="C545" s="7"/>
@@ -8106,7 +8156,7 @@
       <c r="K545" s="7"/>
       <c r="L545" s="1"/>
     </row>
-    <row r="546" ht="19.5" customHeight="1">
+    <row r="546" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A546" s="1"/>
       <c r="B546" s="7"/>
       <c r="C546" s="7"/>
@@ -8120,7 +8170,7 @@
       <c r="K546" s="7"/>
       <c r="L546" s="1"/>
     </row>
-    <row r="547" ht="19.5" customHeight="1">
+    <row r="547" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A547" s="1"/>
       <c r="B547" s="7"/>
       <c r="C547" s="7"/>
@@ -8134,7 +8184,7 @@
       <c r="K547" s="7"/>
       <c r="L547" s="1"/>
     </row>
-    <row r="548" ht="19.5" customHeight="1">
+    <row r="548" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A548" s="1"/>
       <c r="B548" s="7"/>
       <c r="C548" s="7"/>
@@ -8148,7 +8198,7 @@
       <c r="K548" s="7"/>
       <c r="L548" s="1"/>
     </row>
-    <row r="549" ht="19.5" customHeight="1">
+    <row r="549" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A549" s="1"/>
       <c r="B549" s="7"/>
       <c r="C549" s="7"/>
@@ -8162,7 +8212,7 @@
       <c r="K549" s="7"/>
       <c r="L549" s="1"/>
     </row>
-    <row r="550" ht="19.5" customHeight="1">
+    <row r="550" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A550" s="1"/>
       <c r="B550" s="7"/>
       <c r="C550" s="7"/>
@@ -8176,7 +8226,7 @@
       <c r="K550" s="7"/>
       <c r="L550" s="1"/>
     </row>
-    <row r="551" ht="19.5" customHeight="1">
+    <row r="551" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A551" s="1"/>
       <c r="B551" s="7"/>
       <c r="C551" s="7"/>
@@ -8190,7 +8240,7 @@
       <c r="K551" s="7"/>
       <c r="L551" s="1"/>
     </row>
-    <row r="552" ht="19.5" customHeight="1">
+    <row r="552" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A552" s="1"/>
       <c r="B552" s="7"/>
       <c r="C552" s="7"/>
@@ -8204,7 +8254,7 @@
       <c r="K552" s="7"/>
       <c r="L552" s="1"/>
     </row>
-    <row r="553" ht="19.5" customHeight="1">
+    <row r="553" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A553" s="1"/>
       <c r="B553" s="7"/>
       <c r="C553" s="7"/>
@@ -8218,7 +8268,7 @@
       <c r="K553" s="7"/>
       <c r="L553" s="1"/>
     </row>
-    <row r="554" ht="19.5" customHeight="1">
+    <row r="554" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A554" s="1"/>
       <c r="B554" s="7"/>
       <c r="C554" s="7"/>
@@ -8232,7 +8282,7 @@
       <c r="K554" s="7"/>
       <c r="L554" s="1"/>
     </row>
-    <row r="555" ht="19.5" customHeight="1">
+    <row r="555" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A555" s="1"/>
       <c r="B555" s="7"/>
       <c r="C555" s="7"/>
@@ -8246,7 +8296,7 @@
       <c r="K555" s="7"/>
       <c r="L555" s="1"/>
     </row>
-    <row r="556" ht="19.5" customHeight="1">
+    <row r="556" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A556" s="1"/>
       <c r="B556" s="7"/>
       <c r="C556" s="7"/>
@@ -8260,7 +8310,7 @@
       <c r="K556" s="7"/>
       <c r="L556" s="1"/>
     </row>
-    <row r="557" ht="19.5" customHeight="1">
+    <row r="557" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A557" s="1"/>
       <c r="B557" s="7"/>
       <c r="C557" s="7"/>
@@ -8274,7 +8324,7 @@
       <c r="K557" s="7"/>
       <c r="L557" s="1"/>
     </row>
-    <row r="558" ht="19.5" customHeight="1">
+    <row r="558" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A558" s="1"/>
       <c r="B558" s="7"/>
       <c r="C558" s="7"/>
@@ -8288,7 +8338,7 @@
       <c r="K558" s="7"/>
       <c r="L558" s="1"/>
     </row>
-    <row r="559" ht="19.5" customHeight="1">
+    <row r="559" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A559" s="1"/>
       <c r="B559" s="7"/>
       <c r="C559" s="7"/>
@@ -8302,7 +8352,7 @@
       <c r="K559" s="7"/>
       <c r="L559" s="1"/>
     </row>
-    <row r="560" ht="19.5" customHeight="1">
+    <row r="560" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A560" s="1"/>
       <c r="B560" s="7"/>
       <c r="C560" s="7"/>
@@ -8316,7 +8366,7 @@
       <c r="K560" s="7"/>
       <c r="L560" s="1"/>
     </row>
-    <row r="561" ht="19.5" customHeight="1">
+    <row r="561" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A561" s="1"/>
       <c r="B561" s="7"/>
       <c r="C561" s="7"/>
@@ -8330,7 +8380,7 @@
       <c r="K561" s="7"/>
       <c r="L561" s="1"/>
     </row>
-    <row r="562" ht="19.5" customHeight="1">
+    <row r="562" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A562" s="1"/>
       <c r="B562" s="7"/>
       <c r="C562" s="7"/>
@@ -8344,7 +8394,7 @@
       <c r="K562" s="7"/>
       <c r="L562" s="1"/>
     </row>
-    <row r="563" ht="19.5" customHeight="1">
+    <row r="563" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A563" s="1"/>
       <c r="B563" s="7"/>
       <c r="C563" s="7"/>
@@ -8358,7 +8408,7 @@
       <c r="K563" s="7"/>
       <c r="L563" s="1"/>
     </row>
-    <row r="564" ht="19.5" customHeight="1">
+    <row r="564" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A564" s="1"/>
       <c r="B564" s="7"/>
       <c r="C564" s="7"/>
@@ -8372,7 +8422,7 @@
       <c r="K564" s="7"/>
       <c r="L564" s="1"/>
     </row>
-    <row r="565" ht="19.5" customHeight="1">
+    <row r="565" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A565" s="1"/>
       <c r="B565" s="7"/>
       <c r="C565" s="7"/>
@@ -8386,7 +8436,7 @@
       <c r="K565" s="7"/>
       <c r="L565" s="1"/>
     </row>
-    <row r="566" ht="19.5" customHeight="1">
+    <row r="566" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A566" s="1"/>
       <c r="B566" s="7"/>
       <c r="C566" s="7"/>
@@ -8400,7 +8450,7 @@
       <c r="K566" s="7"/>
       <c r="L566" s="1"/>
     </row>
-    <row r="567" ht="19.5" customHeight="1">
+    <row r="567" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A567" s="1"/>
       <c r="B567" s="7"/>
       <c r="C567" s="7"/>
@@ -8414,7 +8464,7 @@
       <c r="K567" s="7"/>
       <c r="L567" s="1"/>
     </row>
-    <row r="568" ht="19.5" customHeight="1">
+    <row r="568" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A568" s="1"/>
       <c r="B568" s="7"/>
       <c r="C568" s="7"/>
@@ -8428,7 +8478,7 @@
       <c r="K568" s="7"/>
       <c r="L568" s="1"/>
     </row>
-    <row r="569" ht="19.5" customHeight="1">
+    <row r="569" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A569" s="1"/>
       <c r="B569" s="7"/>
       <c r="C569" s="7"/>
@@ -8442,7 +8492,7 @@
       <c r="K569" s="7"/>
       <c r="L569" s="1"/>
     </row>
-    <row r="570" ht="19.5" customHeight="1">
+    <row r="570" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A570" s="1"/>
       <c r="B570" s="7"/>
       <c r="C570" s="7"/>
@@ -8456,7 +8506,7 @@
       <c r="K570" s="7"/>
       <c r="L570" s="1"/>
     </row>
-    <row r="571" ht="19.5" customHeight="1">
+    <row r="571" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A571" s="1"/>
       <c r="B571" s="7"/>
       <c r="C571" s="7"/>
@@ -8470,7 +8520,7 @@
       <c r="K571" s="7"/>
       <c r="L571" s="1"/>
     </row>
-    <row r="572" ht="19.5" customHeight="1">
+    <row r="572" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A572" s="1"/>
       <c r="B572" s="7"/>
       <c r="C572" s="7"/>
@@ -8484,7 +8534,7 @@
       <c r="K572" s="7"/>
       <c r="L572" s="1"/>
     </row>
-    <row r="573" ht="19.5" customHeight="1">
+    <row r="573" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A573" s="1"/>
       <c r="B573" s="7"/>
       <c r="C573" s="7"/>
@@ -8498,7 +8548,7 @@
       <c r="K573" s="7"/>
       <c r="L573" s="1"/>
     </row>
-    <row r="574" ht="19.5" customHeight="1">
+    <row r="574" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A574" s="1"/>
       <c r="B574" s="7"/>
       <c r="C574" s="7"/>
@@ -8512,7 +8562,7 @@
       <c r="K574" s="7"/>
       <c r="L574" s="1"/>
     </row>
-    <row r="575" ht="19.5" customHeight="1">
+    <row r="575" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A575" s="1"/>
       <c r="B575" s="7"/>
       <c r="C575" s="7"/>
@@ -8526,7 +8576,7 @@
       <c r="K575" s="7"/>
       <c r="L575" s="1"/>
     </row>
-    <row r="576" ht="19.5" customHeight="1">
+    <row r="576" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A576" s="1"/>
       <c r="B576" s="7"/>
       <c r="C576" s="7"/>
@@ -8540,7 +8590,7 @@
       <c r="K576" s="7"/>
       <c r="L576" s="1"/>
     </row>
-    <row r="577" ht="19.5" customHeight="1">
+    <row r="577" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A577" s="1"/>
       <c r="B577" s="7"/>
       <c r="C577" s="7"/>
@@ -8554,7 +8604,7 @@
       <c r="K577" s="7"/>
       <c r="L577" s="1"/>
     </row>
-    <row r="578" ht="19.5" customHeight="1">
+    <row r="578" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A578" s="1"/>
       <c r="B578" s="7"/>
       <c r="C578" s="7"/>
@@ -8568,7 +8618,7 @@
       <c r="K578" s="7"/>
       <c r="L578" s="1"/>
     </row>
-    <row r="579" ht="19.5" customHeight="1">
+    <row r="579" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A579" s="1"/>
       <c r="B579" s="7"/>
       <c r="C579" s="7"/>
@@ -8582,7 +8632,7 @@
       <c r="K579" s="7"/>
       <c r="L579" s="1"/>
     </row>
-    <row r="580" ht="19.5" customHeight="1">
+    <row r="580" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A580" s="1"/>
       <c r="B580" s="7"/>
       <c r="C580" s="7"/>
@@ -8596,7 +8646,7 @@
       <c r="K580" s="7"/>
       <c r="L580" s="1"/>
     </row>
-    <row r="581" ht="19.5" customHeight="1">
+    <row r="581" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A581" s="1"/>
       <c r="B581" s="7"/>
       <c r="C581" s="7"/>
@@ -8610,7 +8660,7 @@
       <c r="K581" s="7"/>
       <c r="L581" s="1"/>
     </row>
-    <row r="582" ht="19.5" customHeight="1">
+    <row r="582" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A582" s="1"/>
       <c r="B582" s="7"/>
       <c r="C582" s="7"/>
@@ -8624,7 +8674,7 @@
       <c r="K582" s="7"/>
       <c r="L582" s="1"/>
     </row>
-    <row r="583" ht="19.5" customHeight="1">
+    <row r="583" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A583" s="1"/>
       <c r="B583" s="7"/>
       <c r="C583" s="7"/>
@@ -8638,7 +8688,7 @@
       <c r="K583" s="7"/>
       <c r="L583" s="1"/>
     </row>
-    <row r="584" ht="19.5" customHeight="1">
+    <row r="584" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A584" s="1"/>
       <c r="B584" s="7"/>
       <c r="C584" s="7"/>
@@ -8652,7 +8702,7 @@
       <c r="K584" s="7"/>
       <c r="L584" s="1"/>
     </row>
-    <row r="585" ht="19.5" customHeight="1">
+    <row r="585" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A585" s="1"/>
       <c r="B585" s="7"/>
       <c r="C585" s="7"/>
@@ -8666,7 +8716,7 @@
       <c r="K585" s="7"/>
       <c r="L585" s="1"/>
     </row>
-    <row r="586" ht="19.5" customHeight="1">
+    <row r="586" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A586" s="1"/>
       <c r="B586" s="7"/>
       <c r="C586" s="7"/>
@@ -8680,7 +8730,7 @@
       <c r="K586" s="7"/>
       <c r="L586" s="1"/>
     </row>
-    <row r="587" ht="19.5" customHeight="1">
+    <row r="587" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A587" s="1"/>
       <c r="B587" s="7"/>
       <c r="C587" s="7"/>
@@ -8694,7 +8744,7 @@
       <c r="K587" s="7"/>
       <c r="L587" s="1"/>
     </row>
-    <row r="588" ht="19.5" customHeight="1">
+    <row r="588" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A588" s="1"/>
       <c r="B588" s="7"/>
       <c r="C588" s="7"/>
@@ -8708,7 +8758,7 @@
       <c r="K588" s="7"/>
       <c r="L588" s="1"/>
     </row>
-    <row r="589" ht="19.5" customHeight="1">
+    <row r="589" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A589" s="1"/>
       <c r="B589" s="7"/>
       <c r="C589" s="7"/>
@@ -8722,7 +8772,7 @@
       <c r="K589" s="7"/>
       <c r="L589" s="1"/>
     </row>
-    <row r="590" ht="19.5" customHeight="1">
+    <row r="590" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A590" s="1"/>
       <c r="B590" s="7"/>
       <c r="C590" s="7"/>
@@ -8736,7 +8786,7 @@
       <c r="K590" s="7"/>
       <c r="L590" s="1"/>
     </row>
-    <row r="591" ht="19.5" customHeight="1">
+    <row r="591" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A591" s="1"/>
       <c r="B591" s="7"/>
       <c r="C591" s="7"/>
@@ -8750,7 +8800,7 @@
       <c r="K591" s="7"/>
       <c r="L591" s="1"/>
     </row>
-    <row r="592" ht="19.5" customHeight="1">
+    <row r="592" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A592" s="1"/>
       <c r="B592" s="7"/>
       <c r="C592" s="7"/>
@@ -8764,7 +8814,7 @@
       <c r="K592" s="7"/>
       <c r="L592" s="1"/>
     </row>
-    <row r="593" ht="19.5" customHeight="1">
+    <row r="593" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A593" s="1"/>
       <c r="B593" s="7"/>
       <c r="C593" s="7"/>
@@ -8778,7 +8828,7 @@
       <c r="K593" s="7"/>
       <c r="L593" s="1"/>
     </row>
-    <row r="594" ht="19.5" customHeight="1">
+    <row r="594" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A594" s="1"/>
       <c r="B594" s="7"/>
       <c r="C594" s="7"/>
@@ -8792,7 +8842,7 @@
       <c r="K594" s="7"/>
       <c r="L594" s="1"/>
     </row>
-    <row r="595" ht="19.5" customHeight="1">
+    <row r="595" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A595" s="1"/>
       <c r="B595" s="7"/>
       <c r="C595" s="7"/>
@@ -8806,7 +8856,7 @@
       <c r="K595" s="7"/>
       <c r="L595" s="1"/>
     </row>
-    <row r="596" ht="19.5" customHeight="1">
+    <row r="596" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A596" s="1"/>
       <c r="B596" s="7"/>
       <c r="C596" s="7"/>
@@ -8820,7 +8870,7 @@
       <c r="K596" s="7"/>
       <c r="L596" s="1"/>
     </row>
-    <row r="597" ht="19.5" customHeight="1">
+    <row r="597" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A597" s="1"/>
       <c r="B597" s="7"/>
       <c r="C597" s="7"/>
@@ -8834,7 +8884,7 @@
       <c r="K597" s="7"/>
       <c r="L597" s="1"/>
     </row>
-    <row r="598" ht="19.5" customHeight="1">
+    <row r="598" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A598" s="1"/>
       <c r="B598" s="7"/>
       <c r="C598" s="7"/>
@@ -8848,7 +8898,7 @@
       <c r="K598" s="7"/>
       <c r="L598" s="1"/>
     </row>
-    <row r="599" ht="19.5" customHeight="1">
+    <row r="599" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A599" s="1"/>
       <c r="B599" s="7"/>
       <c r="C599" s="7"/>
@@ -8862,7 +8912,7 @@
       <c r="K599" s="7"/>
       <c r="L599" s="1"/>
     </row>
-    <row r="600" ht="19.5" customHeight="1">
+    <row r="600" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A600" s="1"/>
       <c r="B600" s="7"/>
       <c r="C600" s="7"/>
@@ -8876,7 +8926,7 @@
       <c r="K600" s="7"/>
       <c r="L600" s="1"/>
     </row>
-    <row r="601" ht="19.5" customHeight="1">
+    <row r="601" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A601" s="1"/>
       <c r="B601" s="7"/>
       <c r="C601" s="7"/>
@@ -8890,7 +8940,7 @@
       <c r="K601" s="7"/>
       <c r="L601" s="1"/>
     </row>
-    <row r="602" ht="19.5" customHeight="1">
+    <row r="602" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A602" s="1"/>
       <c r="B602" s="7"/>
       <c r="C602" s="7"/>
@@ -8904,7 +8954,7 @@
       <c r="K602" s="7"/>
       <c r="L602" s="1"/>
     </row>
-    <row r="603" ht="19.5" customHeight="1">
+    <row r="603" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A603" s="1"/>
       <c r="B603" s="7"/>
       <c r="C603" s="7"/>
@@ -8918,7 +8968,7 @@
       <c r="K603" s="7"/>
       <c r="L603" s="1"/>
     </row>
-    <row r="604" ht="19.5" customHeight="1">
+    <row r="604" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A604" s="1"/>
       <c r="B604" s="7"/>
       <c r="C604" s="7"/>
@@ -8932,7 +8982,7 @@
       <c r="K604" s="7"/>
       <c r="L604" s="1"/>
     </row>
-    <row r="605" ht="19.5" customHeight="1">
+    <row r="605" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A605" s="1"/>
       <c r="B605" s="7"/>
       <c r="C605" s="7"/>
@@ -8946,7 +8996,7 @@
       <c r="K605" s="7"/>
       <c r="L605" s="1"/>
     </row>
-    <row r="606" ht="19.5" customHeight="1">
+    <row r="606" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A606" s="1"/>
       <c r="B606" s="7"/>
       <c r="C606" s="7"/>
@@ -8960,7 +9010,7 @@
       <c r="K606" s="7"/>
       <c r="L606" s="1"/>
     </row>
-    <row r="607" ht="19.5" customHeight="1">
+    <row r="607" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A607" s="1"/>
       <c r="B607" s="7"/>
       <c r="C607" s="7"/>
@@ -8974,7 +9024,7 @@
       <c r="K607" s="7"/>
       <c r="L607" s="1"/>
     </row>
-    <row r="608" ht="19.5" customHeight="1">
+    <row r="608" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A608" s="1"/>
       <c r="B608" s="7"/>
       <c r="C608" s="7"/>
@@ -8988,7 +9038,7 @@
       <c r="K608" s="7"/>
       <c r="L608" s="1"/>
     </row>
-    <row r="609" ht="19.5" customHeight="1">
+    <row r="609" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A609" s="1"/>
       <c r="B609" s="7"/>
       <c r="C609" s="7"/>
@@ -9002,7 +9052,7 @@
       <c r="K609" s="7"/>
       <c r="L609" s="1"/>
     </row>
-    <row r="610" ht="19.5" customHeight="1">
+    <row r="610" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A610" s="1"/>
       <c r="B610" s="7"/>
       <c r="C610" s="7"/>
@@ -9016,7 +9066,7 @@
       <c r="K610" s="7"/>
       <c r="L610" s="1"/>
     </row>
-    <row r="611" ht="19.5" customHeight="1">
+    <row r="611" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A611" s="1"/>
       <c r="B611" s="7"/>
       <c r="C611" s="7"/>
@@ -9030,7 +9080,7 @@
       <c r="K611" s="7"/>
       <c r="L611" s="1"/>
     </row>
-    <row r="612" ht="19.5" customHeight="1">
+    <row r="612" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A612" s="1"/>
       <c r="B612" s="7"/>
       <c r="C612" s="7"/>
@@ -9044,7 +9094,7 @@
       <c r="K612" s="7"/>
       <c r="L612" s="1"/>
     </row>
-    <row r="613" ht="19.5" customHeight="1">
+    <row r="613" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A613" s="1"/>
       <c r="B613" s="7"/>
       <c r="C613" s="7"/>
@@ -9058,7 +9108,7 @@
       <c r="K613" s="7"/>
       <c r="L613" s="1"/>
     </row>
-    <row r="614" ht="19.5" customHeight="1">
+    <row r="614" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A614" s="1"/>
       <c r="B614" s="7"/>
       <c r="C614" s="7"/>
@@ -9072,7 +9122,7 @@
       <c r="K614" s="7"/>
       <c r="L614" s="1"/>
     </row>
-    <row r="615" ht="19.5" customHeight="1">
+    <row r="615" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A615" s="1"/>
       <c r="B615" s="7"/>
       <c r="C615" s="7"/>
@@ -9086,7 +9136,7 @@
       <c r="K615" s="7"/>
       <c r="L615" s="1"/>
     </row>
-    <row r="616" ht="19.5" customHeight="1">
+    <row r="616" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A616" s="1"/>
       <c r="B616" s="7"/>
       <c r="C616" s="7"/>
@@ -9100,7 +9150,7 @@
       <c r="K616" s="7"/>
       <c r="L616" s="1"/>
     </row>
-    <row r="617" ht="19.5" customHeight="1">
+    <row r="617" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A617" s="1"/>
       <c r="B617" s="7"/>
       <c r="C617" s="7"/>
@@ -9114,7 +9164,7 @@
       <c r="K617" s="7"/>
       <c r="L617" s="1"/>
     </row>
-    <row r="618" ht="19.5" customHeight="1">
+    <row r="618" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A618" s="1"/>
       <c r="B618" s="7"/>
       <c r="C618" s="7"/>
@@ -9128,7 +9178,7 @@
       <c r="K618" s="7"/>
       <c r="L618" s="1"/>
     </row>
-    <row r="619" ht="19.5" customHeight="1">
+    <row r="619" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A619" s="1"/>
       <c r="B619" s="7"/>
       <c r="C619" s="7"/>
@@ -9142,7 +9192,7 @@
       <c r="K619" s="7"/>
       <c r="L619" s="1"/>
     </row>
-    <row r="620" ht="19.5" customHeight="1">
+    <row r="620" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A620" s="1"/>
       <c r="B620" s="7"/>
       <c r="C620" s="7"/>
@@ -9156,7 +9206,7 @@
       <c r="K620" s="7"/>
       <c r="L620" s="1"/>
     </row>
-    <row r="621" ht="19.5" customHeight="1">
+    <row r="621" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A621" s="1"/>
       <c r="B621" s="7"/>
       <c r="C621" s="7"/>
@@ -9170,7 +9220,7 @@
       <c r="K621" s="7"/>
       <c r="L621" s="1"/>
     </row>
-    <row r="622" ht="19.5" customHeight="1">
+    <row r="622" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A622" s="1"/>
       <c r="B622" s="7"/>
       <c r="C622" s="7"/>
@@ -9184,7 +9234,7 @@
       <c r="K622" s="7"/>
       <c r="L622" s="1"/>
     </row>
-    <row r="623" ht="19.5" customHeight="1">
+    <row r="623" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A623" s="1"/>
       <c r="B623" s="7"/>
       <c r="C623" s="7"/>
@@ -9198,7 +9248,7 @@
       <c r="K623" s="7"/>
       <c r="L623" s="1"/>
     </row>
-    <row r="624" ht="19.5" customHeight="1">
+    <row r="624" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A624" s="1"/>
       <c r="B624" s="7"/>
       <c r="C624" s="7"/>
@@ -9212,7 +9262,7 @@
       <c r="K624" s="7"/>
       <c r="L624" s="1"/>
     </row>
-    <row r="625" ht="19.5" customHeight="1">
+    <row r="625" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A625" s="1"/>
       <c r="B625" s="7"/>
       <c r="C625" s="7"/>
@@ -9226,7 +9276,7 @@
       <c r="K625" s="7"/>
       <c r="L625" s="1"/>
     </row>
-    <row r="626" ht="19.5" customHeight="1">
+    <row r="626" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A626" s="1"/>
       <c r="B626" s="7"/>
       <c r="C626" s="7"/>
@@ -9240,7 +9290,7 @@
       <c r="K626" s="7"/>
       <c r="L626" s="1"/>
     </row>
-    <row r="627" ht="19.5" customHeight="1">
+    <row r="627" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A627" s="1"/>
       <c r="B627" s="7"/>
       <c r="C627" s="7"/>
@@ -9254,7 +9304,7 @@
       <c r="K627" s="7"/>
       <c r="L627" s="1"/>
     </row>
-    <row r="628" ht="19.5" customHeight="1">
+    <row r="628" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A628" s="1"/>
       <c r="B628" s="7"/>
       <c r="C628" s="7"/>
@@ -9268,7 +9318,7 @@
       <c r="K628" s="7"/>
       <c r="L628" s="1"/>
     </row>
-    <row r="629" ht="19.5" customHeight="1">
+    <row r="629" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A629" s="1"/>
       <c r="B629" s="7"/>
       <c r="C629" s="7"/>
@@ -9282,7 +9332,7 @@
       <c r="K629" s="7"/>
       <c r="L629" s="1"/>
     </row>
-    <row r="630" ht="19.5" customHeight="1">
+    <row r="630" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A630" s="1"/>
       <c r="B630" s="7"/>
       <c r="C630" s="7"/>
@@ -9296,7 +9346,7 @@
       <c r="K630" s="7"/>
       <c r="L630" s="1"/>
     </row>
-    <row r="631" ht="19.5" customHeight="1">
+    <row r="631" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A631" s="1"/>
       <c r="B631" s="7"/>
       <c r="C631" s="7"/>
@@ -9310,7 +9360,7 @@
       <c r="K631" s="7"/>
       <c r="L631" s="1"/>
     </row>
-    <row r="632" ht="19.5" customHeight="1">
+    <row r="632" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A632" s="1"/>
       <c r="B632" s="7"/>
       <c r="C632" s="7"/>
@@ -9324,7 +9374,7 @@
       <c r="K632" s="7"/>
       <c r="L632" s="1"/>
     </row>
-    <row r="633" ht="19.5" customHeight="1">
+    <row r="633" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A633" s="1"/>
       <c r="B633" s="7"/>
       <c r="C633" s="7"/>
@@ -9338,7 +9388,7 @@
       <c r="K633" s="7"/>
       <c r="L633" s="1"/>
     </row>
-    <row r="634" ht="19.5" customHeight="1">
+    <row r="634" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A634" s="1"/>
       <c r="B634" s="7"/>
       <c r="C634" s="7"/>
@@ -9352,7 +9402,7 @@
       <c r="K634" s="7"/>
       <c r="L634" s="1"/>
     </row>
-    <row r="635" ht="19.5" customHeight="1">
+    <row r="635" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A635" s="1"/>
       <c r="B635" s="7"/>
       <c r="C635" s="7"/>
@@ -9366,7 +9416,7 @@
       <c r="K635" s="7"/>
       <c r="L635" s="1"/>
     </row>
-    <row r="636" ht="19.5" customHeight="1">
+    <row r="636" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A636" s="1"/>
       <c r="B636" s="7"/>
       <c r="C636" s="7"/>
@@ -9380,7 +9430,7 @@
       <c r="K636" s="7"/>
       <c r="L636" s="1"/>
     </row>
-    <row r="637" ht="19.5" customHeight="1">
+    <row r="637" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A637" s="1"/>
       <c r="B637" s="7"/>
       <c r="C637" s="7"/>
@@ -9394,7 +9444,7 @@
       <c r="K637" s="7"/>
       <c r="L637" s="1"/>
     </row>
-    <row r="638" ht="19.5" customHeight="1">
+    <row r="638" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A638" s="1"/>
       <c r="B638" s="7"/>
       <c r="C638" s="7"/>
@@ -9408,7 +9458,7 @@
       <c r="K638" s="7"/>
       <c r="L638" s="1"/>
     </row>
-    <row r="639" ht="19.5" customHeight="1">
+    <row r="639" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A639" s="1"/>
       <c r="B639" s="7"/>
       <c r="C639" s="7"/>
@@ -9422,7 +9472,7 @@
       <c r="K639" s="7"/>
       <c r="L639" s="1"/>
     </row>
-    <row r="640" ht="19.5" customHeight="1">
+    <row r="640" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A640" s="1"/>
       <c r="B640" s="7"/>
       <c r="C640" s="7"/>
@@ -9436,7 +9486,7 @@
       <c r="K640" s="7"/>
       <c r="L640" s="1"/>
     </row>
-    <row r="641" ht="19.5" customHeight="1">
+    <row r="641" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A641" s="1"/>
       <c r="B641" s="7"/>
       <c r="C641" s="7"/>
@@ -9450,7 +9500,7 @@
       <c r="K641" s="7"/>
       <c r="L641" s="1"/>
     </row>
-    <row r="642" ht="19.5" customHeight="1">
+    <row r="642" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A642" s="1"/>
       <c r="B642" s="7"/>
       <c r="C642" s="7"/>
@@ -9464,7 +9514,7 @@
       <c r="K642" s="7"/>
       <c r="L642" s="1"/>
     </row>
-    <row r="643" ht="19.5" customHeight="1">
+    <row r="643" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A643" s="1"/>
       <c r="B643" s="7"/>
       <c r="C643" s="7"/>
@@ -9478,7 +9528,7 @@
       <c r="K643" s="7"/>
       <c r="L643" s="1"/>
     </row>
-    <row r="644" ht="19.5" customHeight="1">
+    <row r="644" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A644" s="1"/>
       <c r="B644" s="7"/>
       <c r="C644" s="7"/>
@@ -9492,7 +9542,7 @@
       <c r="K644" s="7"/>
       <c r="L644" s="1"/>
     </row>
-    <row r="645" ht="19.5" customHeight="1">
+    <row r="645" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A645" s="1"/>
       <c r="B645" s="7"/>
       <c r="C645" s="7"/>
@@ -9506,7 +9556,7 @@
       <c r="K645" s="7"/>
       <c r="L645" s="1"/>
     </row>
-    <row r="646" ht="19.5" customHeight="1">
+    <row r="646" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A646" s="1"/>
       <c r="B646" s="7"/>
       <c r="C646" s="7"/>
@@ -9520,7 +9570,7 @@
       <c r="K646" s="7"/>
       <c r="L646" s="1"/>
     </row>
-    <row r="647" ht="19.5" customHeight="1">
+    <row r="647" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A647" s="1"/>
       <c r="B647" s="7"/>
       <c r="C647" s="7"/>
@@ -9534,7 +9584,7 @@
       <c r="K647" s="7"/>
       <c r="L647" s="1"/>
     </row>
-    <row r="648" ht="19.5" customHeight="1">
+    <row r="648" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A648" s="1"/>
       <c r="B648" s="7"/>
       <c r="C648" s="7"/>
@@ -9548,7 +9598,7 @@
       <c r="K648" s="7"/>
       <c r="L648" s="1"/>
     </row>
-    <row r="649" ht="19.5" customHeight="1">
+    <row r="649" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A649" s="1"/>
       <c r="B649" s="7"/>
       <c r="C649" s="7"/>
@@ -9562,7 +9612,7 @@
       <c r="K649" s="7"/>
       <c r="L649" s="1"/>
     </row>
-    <row r="650" ht="19.5" customHeight="1">
+    <row r="650" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A650" s="1"/>
       <c r="B650" s="7"/>
       <c r="C650" s="7"/>
@@ -9576,7 +9626,7 @@
       <c r="K650" s="7"/>
       <c r="L650" s="1"/>
     </row>
-    <row r="651" ht="19.5" customHeight="1">
+    <row r="651" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A651" s="1"/>
       <c r="B651" s="7"/>
       <c r="C651" s="7"/>
@@ -9590,7 +9640,7 @@
       <c r="K651" s="7"/>
       <c r="L651" s="1"/>
     </row>
-    <row r="652" ht="19.5" customHeight="1">
+    <row r="652" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A652" s="1"/>
       <c r="B652" s="7"/>
       <c r="C652" s="7"/>
@@ -9604,7 +9654,7 @@
       <c r="K652" s="7"/>
       <c r="L652" s="1"/>
     </row>
-    <row r="653" ht="19.5" customHeight="1">
+    <row r="653" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A653" s="1"/>
       <c r="B653" s="7"/>
       <c r="C653" s="7"/>
@@ -9618,7 +9668,7 @@
       <c r="K653" s="7"/>
       <c r="L653" s="1"/>
     </row>
-    <row r="654" ht="19.5" customHeight="1">
+    <row r="654" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A654" s="1"/>
       <c r="B654" s="7"/>
       <c r="C654" s="7"/>
@@ -9632,7 +9682,7 @@
       <c r="K654" s="7"/>
       <c r="L654" s="1"/>
     </row>
-    <row r="655" ht="19.5" customHeight="1">
+    <row r="655" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A655" s="1"/>
       <c r="B655" s="7"/>
       <c r="C655" s="7"/>
@@ -9646,7 +9696,7 @@
       <c r="K655" s="7"/>
       <c r="L655" s="1"/>
     </row>
-    <row r="656" ht="19.5" customHeight="1">
+    <row r="656" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A656" s="1"/>
       <c r="B656" s="7"/>
       <c r="C656" s="7"/>
@@ -9660,7 +9710,7 @@
       <c r="K656" s="7"/>
       <c r="L656" s="1"/>
     </row>
-    <row r="657" ht="19.5" customHeight="1">
+    <row r="657" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A657" s="1"/>
       <c r="B657" s="7"/>
       <c r="C657" s="7"/>
@@ -9674,7 +9724,7 @@
       <c r="K657" s="7"/>
       <c r="L657" s="1"/>
     </row>
-    <row r="658" ht="19.5" customHeight="1">
+    <row r="658" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A658" s="1"/>
       <c r="B658" s="7"/>
       <c r="C658" s="7"/>
@@ -9688,7 +9738,7 @@
       <c r="K658" s="7"/>
       <c r="L658" s="1"/>
     </row>
-    <row r="659" ht="19.5" customHeight="1">
+    <row r="659" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A659" s="1"/>
       <c r="B659" s="7"/>
       <c r="C659" s="7"/>
@@ -9702,7 +9752,7 @@
       <c r="K659" s="7"/>
       <c r="L659" s="1"/>
     </row>
-    <row r="660" ht="19.5" customHeight="1">
+    <row r="660" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A660" s="1"/>
       <c r="B660" s="7"/>
       <c r="C660" s="7"/>
@@ -9716,7 +9766,7 @@
       <c r="K660" s="7"/>
       <c r="L660" s="1"/>
     </row>
-    <row r="661" ht="19.5" customHeight="1">
+    <row r="661" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A661" s="1"/>
       <c r="B661" s="7"/>
       <c r="C661" s="7"/>
@@ -9730,7 +9780,7 @@
       <c r="K661" s="7"/>
       <c r="L661" s="1"/>
     </row>
-    <row r="662" ht="19.5" customHeight="1">
+    <row r="662" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A662" s="1"/>
       <c r="B662" s="7"/>
       <c r="C662" s="7"/>
@@ -9744,7 +9794,7 @@
       <c r="K662" s="7"/>
       <c r="L662" s="1"/>
     </row>
-    <row r="663" ht="19.5" customHeight="1">
+    <row r="663" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A663" s="1"/>
       <c r="B663" s="7"/>
       <c r="C663" s="7"/>
@@ -9758,7 +9808,7 @@
       <c r="K663" s="7"/>
       <c r="L663" s="1"/>
     </row>
-    <row r="664" ht="19.5" customHeight="1">
+    <row r="664" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A664" s="1"/>
       <c r="B664" s="7"/>
       <c r="C664" s="7"/>
@@ -9772,7 +9822,7 @@
       <c r="K664" s="7"/>
       <c r="L664" s="1"/>
     </row>
-    <row r="665" ht="19.5" customHeight="1">
+    <row r="665" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A665" s="1"/>
       <c r="B665" s="7"/>
       <c r="C665" s="7"/>
@@ -9786,7 +9836,7 @@
       <c r="K665" s="7"/>
       <c r="L665" s="1"/>
     </row>
-    <row r="666" ht="19.5" customHeight="1">
+    <row r="666" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A666" s="1"/>
       <c r="B666" s="7"/>
       <c r="C666" s="7"/>
@@ -9800,7 +9850,7 @@
       <c r="K666" s="7"/>
       <c r="L666" s="1"/>
     </row>
-    <row r="667" ht="19.5" customHeight="1">
+    <row r="667" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A667" s="1"/>
       <c r="B667" s="7"/>
       <c r="C667" s="7"/>
@@ -9814,7 +9864,7 @@
       <c r="K667" s="7"/>
       <c r="L667" s="1"/>
     </row>
-    <row r="668" ht="19.5" customHeight="1">
+    <row r="668" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A668" s="1"/>
       <c r="B668" s="7"/>
       <c r="C668" s="7"/>
@@ -9828,7 +9878,7 @@
       <c r="K668" s="7"/>
       <c r="L668" s="1"/>
     </row>
-    <row r="669" ht="19.5" customHeight="1">
+    <row r="669" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A669" s="1"/>
       <c r="B669" s="7"/>
       <c r="C669" s="7"/>
@@ -9842,7 +9892,7 @@
       <c r="K669" s="7"/>
       <c r="L669" s="1"/>
     </row>
-    <row r="670" ht="19.5" customHeight="1">
+    <row r="670" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A670" s="1"/>
       <c r="B670" s="7"/>
       <c r="C670" s="7"/>
@@ -9856,7 +9906,7 @@
       <c r="K670" s="7"/>
       <c r="L670" s="1"/>
     </row>
-    <row r="671" ht="19.5" customHeight="1">
+    <row r="671" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A671" s="1"/>
       <c r="B671" s="7"/>
       <c r="C671" s="7"/>
@@ -9870,7 +9920,7 @@
       <c r="K671" s="7"/>
       <c r="L671" s="1"/>
     </row>
-    <row r="672" ht="19.5" customHeight="1">
+    <row r="672" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A672" s="1"/>
       <c r="B672" s="7"/>
       <c r="C672" s="7"/>
@@ -9884,7 +9934,7 @@
       <c r="K672" s="7"/>
       <c r="L672" s="1"/>
     </row>
-    <row r="673" ht="19.5" customHeight="1">
+    <row r="673" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A673" s="1"/>
       <c r="B673" s="7"/>
       <c r="C673" s="7"/>
@@ -9898,7 +9948,7 @@
       <c r="K673" s="7"/>
       <c r="L673" s="1"/>
     </row>
-    <row r="674" ht="19.5" customHeight="1">
+    <row r="674" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A674" s="1"/>
       <c r="B674" s="7"/>
       <c r="C674" s="7"/>
@@ -9912,7 +9962,7 @@
       <c r="K674" s="7"/>
       <c r="L674" s="1"/>
     </row>
-    <row r="675" ht="19.5" customHeight="1">
+    <row r="675" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A675" s="1"/>
       <c r="B675" s="7"/>
       <c r="C675" s="7"/>
@@ -9926,7 +9976,7 @@
       <c r="K675" s="7"/>
       <c r="L675" s="1"/>
     </row>
-    <row r="676" ht="19.5" customHeight="1">
+    <row r="676" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A676" s="1"/>
       <c r="B676" s="7"/>
       <c r="C676" s="7"/>
@@ -9940,7 +9990,7 @@
       <c r="K676" s="7"/>
       <c r="L676" s="1"/>
     </row>
-    <row r="677" ht="19.5" customHeight="1">
+    <row r="677" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A677" s="1"/>
       <c r="B677" s="7"/>
       <c r="C677" s="7"/>
@@ -9954,7 +10004,7 @@
       <c r="K677" s="7"/>
       <c r="L677" s="1"/>
     </row>
-    <row r="678" ht="19.5" customHeight="1">
+    <row r="678" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A678" s="1"/>
       <c r="B678" s="7"/>
       <c r="C678" s="7"/>
@@ -9968,7 +10018,7 @@
       <c r="K678" s="7"/>
       <c r="L678" s="1"/>
     </row>
-    <row r="679" ht="19.5" customHeight="1">
+    <row r="679" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A679" s="1"/>
       <c r="B679" s="7"/>
       <c r="C679" s="7"/>
@@ -9982,7 +10032,7 @@
       <c r="K679" s="7"/>
       <c r="L679" s="1"/>
     </row>
-    <row r="680" ht="19.5" customHeight="1">
+    <row r="680" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A680" s="1"/>
       <c r="B680" s="7"/>
       <c r="C680" s="7"/>
@@ -9996,7 +10046,7 @@
       <c r="K680" s="7"/>
       <c r="L680" s="1"/>
     </row>
-    <row r="681" ht="19.5" customHeight="1">
+    <row r="681" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A681" s="1"/>
       <c r="B681" s="7"/>
       <c r="C681" s="7"/>
@@ -10010,7 +10060,7 @@
       <c r="K681" s="7"/>
       <c r="L681" s="1"/>
     </row>
-    <row r="682" ht="19.5" customHeight="1">
+    <row r="682" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A682" s="1"/>
       <c r="B682" s="7"/>
       <c r="C682" s="7"/>
@@ -10024,7 +10074,7 @@
       <c r="K682" s="7"/>
       <c r="L682" s="1"/>
     </row>
-    <row r="683" ht="19.5" customHeight="1">
+    <row r="683" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A683" s="1"/>
       <c r="B683" s="7"/>
       <c r="C683" s="7"/>
@@ -10038,7 +10088,7 @@
       <c r="K683" s="7"/>
       <c r="L683" s="1"/>
     </row>
-    <row r="684" ht="19.5" customHeight="1">
+    <row r="684" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A684" s="1"/>
       <c r="B684" s="7"/>
       <c r="C684" s="7"/>
@@ -10052,7 +10102,7 @@
       <c r="K684" s="7"/>
       <c r="L684" s="1"/>
     </row>
-    <row r="685" ht="19.5" customHeight="1">
+    <row r="685" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A685" s="1"/>
       <c r="B685" s="7"/>
       <c r="C685" s="7"/>
@@ -10066,7 +10116,7 @@
       <c r="K685" s="7"/>
       <c r="L685" s="1"/>
     </row>
-    <row r="686" ht="19.5" customHeight="1">
+    <row r="686" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A686" s="1"/>
       <c r="B686" s="7"/>
       <c r="C686" s="7"/>
@@ -10080,7 +10130,7 @@
       <c r="K686" s="7"/>
       <c r="L686" s="1"/>
     </row>
-    <row r="687" ht="19.5" customHeight="1">
+    <row r="687" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A687" s="1"/>
       <c r="B687" s="7"/>
       <c r="C687" s="7"/>
@@ -10094,7 +10144,7 @@
       <c r="K687" s="7"/>
       <c r="L687" s="1"/>
     </row>
-    <row r="688" ht="19.5" customHeight="1">
+    <row r="688" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A688" s="1"/>
       <c r="B688" s="7"/>
       <c r="C688" s="7"/>
@@ -10108,7 +10158,7 @@
       <c r="K688" s="7"/>
       <c r="L688" s="1"/>
     </row>
-    <row r="689" ht="19.5" customHeight="1">
+    <row r="689" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A689" s="1"/>
       <c r="B689" s="7"/>
       <c r="C689" s="7"/>
@@ -10122,7 +10172,7 @@
       <c r="K689" s="7"/>
       <c r="L689" s="1"/>
     </row>
-    <row r="690" ht="19.5" customHeight="1">
+    <row r="690" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A690" s="1"/>
       <c r="B690" s="7"/>
       <c r="C690" s="7"/>
@@ -10136,7 +10186,7 @@
       <c r="K690" s="7"/>
       <c r="L690" s="1"/>
     </row>
-    <row r="691" ht="19.5" customHeight="1">
+    <row r="691" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A691" s="1"/>
       <c r="B691" s="7"/>
       <c r="C691" s="7"/>
@@ -10150,7 +10200,7 @@
       <c r="K691" s="7"/>
       <c r="L691" s="1"/>
     </row>
-    <row r="692" ht="19.5" customHeight="1">
+    <row r="692" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A692" s="1"/>
       <c r="B692" s="7"/>
       <c r="C692" s="7"/>
@@ -10164,7 +10214,7 @@
       <c r="K692" s="7"/>
       <c r="L692" s="1"/>
     </row>
-    <row r="693" ht="19.5" customHeight="1">
+    <row r="693" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A693" s="1"/>
       <c r="B693" s="7"/>
       <c r="C693" s="7"/>
@@ -10178,7 +10228,7 @@
       <c r="K693" s="7"/>
       <c r="L693" s="1"/>
     </row>
-    <row r="694" ht="19.5" customHeight="1">
+    <row r="694" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A694" s="1"/>
       <c r="B694" s="7"/>
       <c r="C694" s="7"/>
@@ -10192,7 +10242,7 @@
       <c r="K694" s="7"/>
       <c r="L694" s="1"/>
     </row>
-    <row r="695" ht="19.5" customHeight="1">
+    <row r="695" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A695" s="1"/>
       <c r="B695" s="7"/>
       <c r="C695" s="7"/>
@@ -10206,7 +10256,7 @@
       <c r="K695" s="7"/>
       <c r="L695" s="1"/>
     </row>
-    <row r="696" ht="19.5" customHeight="1">
+    <row r="696" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A696" s="1"/>
       <c r="B696" s="7"/>
       <c r="C696" s="7"/>
@@ -10220,7 +10270,7 @@
       <c r="K696" s="7"/>
       <c r="L696" s="1"/>
     </row>
-    <row r="697" ht="19.5" customHeight="1">
+    <row r="697" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A697" s="1"/>
       <c r="B697" s="7"/>
       <c r="C697" s="7"/>
@@ -10234,7 +10284,7 @@
       <c r="K697" s="7"/>
       <c r="L697" s="1"/>
     </row>
-    <row r="698" ht="19.5" customHeight="1">
+    <row r="698" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A698" s="1"/>
       <c r="B698" s="7"/>
       <c r="C698" s="7"/>
@@ -10248,7 +10298,7 @@
       <c r="K698" s="7"/>
       <c r="L698" s="1"/>
     </row>
-    <row r="699" ht="19.5" customHeight="1">
+    <row r="699" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A699" s="1"/>
       <c r="B699" s="7"/>
       <c r="C699" s="7"/>
@@ -10262,7 +10312,7 @@
       <c r="K699" s="7"/>
       <c r="L699" s="1"/>
     </row>
-    <row r="700" ht="19.5" customHeight="1">
+    <row r="700" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A700" s="1"/>
       <c r="B700" s="7"/>
       <c r="C700" s="7"/>
@@ -10276,7 +10326,7 @@
       <c r="K700" s="7"/>
       <c r="L700" s="1"/>
     </row>
-    <row r="701" ht="19.5" customHeight="1">
+    <row r="701" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A701" s="1"/>
       <c r="B701" s="7"/>
       <c r="C701" s="7"/>
@@ -10290,7 +10340,7 @@
       <c r="K701" s="7"/>
       <c r="L701" s="1"/>
     </row>
-    <row r="702" ht="19.5" customHeight="1">
+    <row r="702" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A702" s="1"/>
       <c r="B702" s="7"/>
       <c r="C702" s="7"/>
@@ -10304,7 +10354,7 @@
       <c r="K702" s="7"/>
       <c r="L702" s="1"/>
     </row>
-    <row r="703" ht="19.5" customHeight="1">
+    <row r="703" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A703" s="1"/>
       <c r="B703" s="7"/>
       <c r="C703" s="7"/>
@@ -10318,7 +10368,7 @@
       <c r="K703" s="7"/>
       <c r="L703" s="1"/>
     </row>
-    <row r="704" ht="19.5" customHeight="1">
+    <row r="704" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A704" s="1"/>
       <c r="B704" s="7"/>
       <c r="C704" s="7"/>
@@ -10332,7 +10382,7 @@
       <c r="K704" s="7"/>
       <c r="L704" s="1"/>
     </row>
-    <row r="705" ht="19.5" customHeight="1">
+    <row r="705" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A705" s="1"/>
       <c r="B705" s="7"/>
       <c r="C705" s="7"/>
@@ -10346,7 +10396,7 @@
       <c r="K705" s="7"/>
       <c r="L705" s="1"/>
     </row>
-    <row r="706" ht="19.5" customHeight="1">
+    <row r="706" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A706" s="1"/>
       <c r="B706" s="7"/>
       <c r="C706" s="7"/>
@@ -10360,7 +10410,7 @@
       <c r="K706" s="7"/>
       <c r="L706" s="1"/>
     </row>
-    <row r="707" ht="19.5" customHeight="1">
+    <row r="707" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A707" s="1"/>
       <c r="B707" s="7"/>
       <c r="C707" s="7"/>
@@ -10374,7 +10424,7 @@
       <c r="K707" s="7"/>
       <c r="L707" s="1"/>
     </row>
-    <row r="708" ht="19.5" customHeight="1">
+    <row r="708" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A708" s="1"/>
       <c r="B708" s="7"/>
       <c r="C708" s="7"/>
@@ -10388,7 +10438,7 @@
       <c r="K708" s="7"/>
       <c r="L708" s="1"/>
     </row>
-    <row r="709" ht="19.5" customHeight="1">
+    <row r="709" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A709" s="1"/>
       <c r="B709" s="7"/>
       <c r="C709" s="7"/>
@@ -10402,7 +10452,7 @@
       <c r="K709" s="7"/>
       <c r="L709" s="1"/>
     </row>
-    <row r="710" ht="19.5" customHeight="1">
+    <row r="710" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A710" s="1"/>
       <c r="B710" s="7"/>
       <c r="C710" s="7"/>
@@ -10416,7 +10466,7 @@
       <c r="K710" s="7"/>
       <c r="L710" s="1"/>
     </row>
-    <row r="711" ht="19.5" customHeight="1">
+    <row r="711" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A711" s="1"/>
       <c r="B711" s="7"/>
       <c r="C711" s="7"/>
@@ -10430,7 +10480,7 @@
       <c r="K711" s="7"/>
       <c r="L711" s="1"/>
     </row>
-    <row r="712" ht="19.5" customHeight="1">
+    <row r="712" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A712" s="1"/>
       <c r="B712" s="7"/>
       <c r="C712" s="7"/>
@@ -10444,7 +10494,7 @@
       <c r="K712" s="7"/>
       <c r="L712" s="1"/>
     </row>
-    <row r="713" ht="19.5" customHeight="1">
+    <row r="713" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A713" s="1"/>
       <c r="B713" s="7"/>
       <c r="C713" s="7"/>
@@ -10458,7 +10508,7 @@
       <c r="K713" s="7"/>
       <c r="L713" s="1"/>
     </row>
-    <row r="714" ht="19.5" customHeight="1">
+    <row r="714" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A714" s="1"/>
       <c r="B714" s="7"/>
       <c r="C714" s="7"/>
@@ -10472,7 +10522,7 @@
       <c r="K714" s="7"/>
       <c r="L714" s="1"/>
     </row>
-    <row r="715" ht="19.5" customHeight="1">
+    <row r="715" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A715" s="1"/>
       <c r="B715" s="7"/>
       <c r="C715" s="7"/>
@@ -10486,7 +10536,7 @@
       <c r="K715" s="7"/>
       <c r="L715" s="1"/>
     </row>
-    <row r="716" ht="19.5" customHeight="1">
+    <row r="716" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A716" s="1"/>
       <c r="B716" s="7"/>
       <c r="C716" s="7"/>
@@ -10500,7 +10550,7 @@
       <c r="K716" s="7"/>
       <c r="L716" s="1"/>
     </row>
-    <row r="717" ht="19.5" customHeight="1">
+    <row r="717" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A717" s="1"/>
       <c r="B717" s="7"/>
       <c r="C717" s="7"/>
@@ -10514,7 +10564,7 @@
       <c r="K717" s="7"/>
       <c r="L717" s="1"/>
     </row>
-    <row r="718" ht="19.5" customHeight="1">
+    <row r="718" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A718" s="1"/>
       <c r="B718" s="7"/>
       <c r="C718" s="7"/>
@@ -10528,7 +10578,7 @@
       <c r="K718" s="7"/>
       <c r="L718" s="1"/>
     </row>
-    <row r="719" ht="19.5" customHeight="1">
+    <row r="719" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A719" s="1"/>
       <c r="B719" s="7"/>
       <c r="C719" s="7"/>
@@ -10542,7 +10592,7 @@
       <c r="K719" s="7"/>
       <c r="L719" s="1"/>
     </row>
-    <row r="720" ht="19.5" customHeight="1">
+    <row r="720" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A720" s="1"/>
       <c r="B720" s="7"/>
       <c r="C720" s="7"/>
@@ -10556,7 +10606,7 @@
       <c r="K720" s="7"/>
       <c r="L720" s="1"/>
     </row>
-    <row r="721" ht="19.5" customHeight="1">
+    <row r="721" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A721" s="1"/>
       <c r="B721" s="7"/>
       <c r="C721" s="7"/>
@@ -10570,7 +10620,7 @@
       <c r="K721" s="7"/>
       <c r="L721" s="1"/>
     </row>
-    <row r="722" ht="19.5" customHeight="1">
+    <row r="722" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A722" s="1"/>
       <c r="B722" s="7"/>
       <c r="C722" s="7"/>
@@ -10584,7 +10634,7 @@
       <c r="K722" s="7"/>
       <c r="L722" s="1"/>
     </row>
-    <row r="723" ht="19.5" customHeight="1">
+    <row r="723" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A723" s="1"/>
       <c r="B723" s="7"/>
       <c r="C723" s="7"/>
@@ -10598,7 +10648,7 @@
       <c r="K723" s="7"/>
       <c r="L723" s="1"/>
     </row>
-    <row r="724" ht="19.5" customHeight="1">
+    <row r="724" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A724" s="1"/>
       <c r="B724" s="7"/>
       <c r="C724" s="7"/>
@@ -10612,7 +10662,7 @@
       <c r="K724" s="7"/>
       <c r="L724" s="1"/>
     </row>
-    <row r="725" ht="19.5" customHeight="1">
+    <row r="725" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A725" s="1"/>
       <c r="B725" s="7"/>
       <c r="C725" s="7"/>
@@ -10626,7 +10676,7 @@
       <c r="K725" s="7"/>
       <c r="L725" s="1"/>
     </row>
-    <row r="726" ht="19.5" customHeight="1">
+    <row r="726" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A726" s="1"/>
       <c r="B726" s="7"/>
       <c r="C726" s="7"/>
@@ -10640,7 +10690,7 @@
       <c r="K726" s="7"/>
       <c r="L726" s="1"/>
     </row>
-    <row r="727" ht="19.5" customHeight="1">
+    <row r="727" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A727" s="1"/>
       <c r="B727" s="7"/>
       <c r="C727" s="7"/>
@@ -10654,7 +10704,7 @@
       <c r="K727" s="7"/>
       <c r="L727" s="1"/>
     </row>
-    <row r="728" ht="19.5" customHeight="1">
+    <row r="728" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A728" s="1"/>
       <c r="B728" s="7"/>
       <c r="C728" s="7"/>
@@ -10668,7 +10718,7 @@
       <c r="K728" s="7"/>
       <c r="L728" s="1"/>
     </row>
-    <row r="729" ht="19.5" customHeight="1">
+    <row r="729" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A729" s="1"/>
       <c r="B729" s="7"/>
       <c r="C729" s="7"/>
@@ -10682,7 +10732,7 @@
       <c r="K729" s="7"/>
       <c r="L729" s="1"/>
     </row>
-    <row r="730" ht="19.5" customHeight="1">
+    <row r="730" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A730" s="1"/>
       <c r="B730" s="7"/>
       <c r="C730" s="7"/>
@@ -10696,7 +10746,7 @@
       <c r="K730" s="7"/>
       <c r="L730" s="1"/>
     </row>
-    <row r="731" ht="19.5" customHeight="1">
+    <row r="731" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A731" s="1"/>
       <c r="B731" s="7"/>
       <c r="C731" s="7"/>
@@ -10710,7 +10760,7 @@
       <c r="K731" s="7"/>
       <c r="L731" s="1"/>
     </row>
-    <row r="732" ht="19.5" customHeight="1">
+    <row r="732" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A732" s="1"/>
       <c r="B732" s="7"/>
       <c r="C732" s="7"/>
@@ -10724,7 +10774,7 @@
       <c r="K732" s="7"/>
       <c r="L732" s="1"/>
     </row>
-    <row r="733" ht="19.5" customHeight="1">
+    <row r="733" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A733" s="1"/>
       <c r="B733" s="7"/>
       <c r="C733" s="7"/>
@@ -10738,7 +10788,7 @@
       <c r="K733" s="7"/>
       <c r="L733" s="1"/>
     </row>
-    <row r="734" ht="19.5" customHeight="1">
+    <row r="734" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A734" s="1"/>
       <c r="B734" s="7"/>
       <c r="C734" s="7"/>
@@ -10752,7 +10802,7 @@
       <c r="K734" s="7"/>
       <c r="L734" s="1"/>
     </row>
-    <row r="735" ht="19.5" customHeight="1">
+    <row r="735" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A735" s="1"/>
       <c r="B735" s="7"/>
       <c r="C735" s="7"/>
@@ -10766,7 +10816,7 @@
       <c r="K735" s="7"/>
       <c r="L735" s="1"/>
     </row>
-    <row r="736" ht="19.5" customHeight="1">
+    <row r="736" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A736" s="1"/>
       <c r="B736" s="7"/>
       <c r="C736" s="7"/>
@@ -10780,7 +10830,7 @@
       <c r="K736" s="7"/>
       <c r="L736" s="1"/>
     </row>
-    <row r="737" ht="19.5" customHeight="1">
+    <row r="737" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A737" s="1"/>
       <c r="B737" s="7"/>
       <c r="C737" s="7"/>
@@ -10794,7 +10844,7 @@
       <c r="K737" s="7"/>
       <c r="L737" s="1"/>
     </row>
-    <row r="738" ht="19.5" customHeight="1">
+    <row r="738" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A738" s="1"/>
       <c r="B738" s="7"/>
       <c r="C738" s="7"/>
@@ -10808,7 +10858,7 @@
       <c r="K738" s="7"/>
       <c r="L738" s="1"/>
     </row>
-    <row r="739" ht="19.5" customHeight="1">
+    <row r="739" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A739" s="1"/>
       <c r="B739" s="7"/>
       <c r="C739" s="7"/>
@@ -10822,7 +10872,7 @@
       <c r="K739" s="7"/>
       <c r="L739" s="1"/>
     </row>
-    <row r="740" ht="19.5" customHeight="1">
+    <row r="740" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A740" s="1"/>
       <c r="B740" s="7"/>
       <c r="C740" s="7"/>
@@ -10836,7 +10886,7 @@
       <c r="K740" s="7"/>
       <c r="L740" s="1"/>
     </row>
-    <row r="741" ht="19.5" customHeight="1">
+    <row r="741" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A741" s="1"/>
       <c r="B741" s="7"/>
       <c r="C741" s="7"/>
@@ -10850,7 +10900,7 @@
       <c r="K741" s="7"/>
       <c r="L741" s="1"/>
     </row>
-    <row r="742" ht="19.5" customHeight="1">
+    <row r="742" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A742" s="1"/>
       <c r="B742" s="7"/>
       <c r="C742" s="7"/>
@@ -10864,7 +10914,7 @@
       <c r="K742" s="7"/>
       <c r="L742" s="1"/>
     </row>
-    <row r="743" ht="19.5" customHeight="1">
+    <row r="743" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A743" s="1"/>
       <c r="B743" s="7"/>
       <c r="C743" s="7"/>
@@ -10878,7 +10928,7 @@
       <c r="K743" s="7"/>
       <c r="L743" s="1"/>
     </row>
-    <row r="744" ht="19.5" customHeight="1">
+    <row r="744" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A744" s="1"/>
       <c r="B744" s="7"/>
       <c r="C744" s="7"/>
@@ -10892,7 +10942,7 @@
       <c r="K744" s="7"/>
       <c r="L744" s="1"/>
     </row>
-    <row r="745" ht="19.5" customHeight="1">
+    <row r="745" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A745" s="1"/>
       <c r="B745" s="7"/>
       <c r="C745" s="7"/>
@@ -10906,7 +10956,7 @@
       <c r="K745" s="7"/>
       <c r="L745" s="1"/>
     </row>
-    <row r="746" ht="19.5" customHeight="1">
+    <row r="746" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A746" s="1"/>
       <c r="B746" s="7"/>
       <c r="C746" s="7"/>
@@ -10920,7 +10970,7 @@
       <c r="K746" s="7"/>
       <c r="L746" s="1"/>
     </row>
-    <row r="747" ht="19.5" customHeight="1">
+    <row r="747" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A747" s="1"/>
       <c r="B747" s="7"/>
       <c r="C747" s="7"/>
@@ -10934,7 +10984,7 @@
       <c r="K747" s="7"/>
       <c r="L747" s="1"/>
     </row>
-    <row r="748" ht="19.5" customHeight="1">
+    <row r="748" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A748" s="1"/>
       <c r="B748" s="7"/>
       <c r="C748" s="7"/>
@@ -10948,7 +10998,7 @@
       <c r="K748" s="7"/>
       <c r="L748" s="1"/>
     </row>
-    <row r="749" ht="19.5" customHeight="1">
+    <row r="749" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A749" s="1"/>
       <c r="B749" s="7"/>
       <c r="C749" s="7"/>
@@ -10962,7 +11012,7 @@
       <c r="K749" s="7"/>
       <c r="L749" s="1"/>
     </row>
-    <row r="750" ht="19.5" customHeight="1">
+    <row r="750" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A750" s="1"/>
       <c r="B750" s="7"/>
       <c r="C750" s="7"/>
@@ -10976,7 +11026,7 @@
       <c r="K750" s="7"/>
       <c r="L750" s="1"/>
     </row>
-    <row r="751" ht="19.5" customHeight="1">
+    <row r="751" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A751" s="1"/>
       <c r="B751" s="7"/>
       <c r="C751" s="7"/>
@@ -10990,7 +11040,7 @@
       <c r="K751" s="7"/>
       <c r="L751" s="1"/>
     </row>
-    <row r="752" ht="19.5" customHeight="1">
+    <row r="752" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A752" s="1"/>
       <c r="B752" s="7"/>
       <c r="C752" s="7"/>
@@ -11004,7 +11054,7 @@
       <c r="K752" s="7"/>
       <c r="L752" s="1"/>
     </row>
-    <row r="753" ht="19.5" customHeight="1">
+    <row r="753" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A753" s="1"/>
       <c r="B753" s="7"/>
       <c r="C753" s="7"/>
@@ -11018,7 +11068,7 @@
       <c r="K753" s="7"/>
       <c r="L753" s="1"/>
     </row>
-    <row r="754" ht="19.5" customHeight="1">
+    <row r="754" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A754" s="1"/>
       <c r="B754" s="7"/>
       <c r="C754" s="7"/>
@@ -11032,7 +11082,7 @@
       <c r="K754" s="7"/>
       <c r="L754" s="1"/>
     </row>
-    <row r="755" ht="19.5" customHeight="1">
+    <row r="755" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A755" s="1"/>
       <c r="B755" s="7"/>
       <c r="C755" s="7"/>
@@ -11046,7 +11096,7 @@
       <c r="K755" s="7"/>
       <c r="L755" s="1"/>
     </row>
-    <row r="756" ht="19.5" customHeight="1">
+    <row r="756" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A756" s="1"/>
       <c r="B756" s="7"/>
       <c r="C756" s="7"/>
@@ -11060,7 +11110,7 @@
       <c r="K756" s="7"/>
       <c r="L756" s="1"/>
     </row>
-    <row r="757" ht="19.5" customHeight="1">
+    <row r="757" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A757" s="1"/>
       <c r="B757" s="7"/>
       <c r="C757" s="7"/>
@@ -11074,7 +11124,7 @@
       <c r="K757" s="7"/>
       <c r="L757" s="1"/>
     </row>
-    <row r="758" ht="19.5" customHeight="1">
+    <row r="758" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A758" s="1"/>
       <c r="B758" s="7"/>
       <c r="C758" s="7"/>
@@ -11088,7 +11138,7 @@
       <c r="K758" s="7"/>
       <c r="L758" s="1"/>
     </row>
-    <row r="759" ht="19.5" customHeight="1">
+    <row r="759" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A759" s="1"/>
       <c r="B759" s="7"/>
       <c r="C759" s="7"/>
@@ -11102,7 +11152,7 @@
       <c r="K759" s="7"/>
       <c r="L759" s="1"/>
     </row>
-    <row r="760" ht="19.5" customHeight="1">
+    <row r="760" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A760" s="1"/>
       <c r="B760" s="7"/>
       <c r="C760" s="7"/>
@@ -11116,7 +11166,7 @@
       <c r="K760" s="7"/>
       <c r="L760" s="1"/>
     </row>
-    <row r="761" ht="19.5" customHeight="1">
+    <row r="761" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A761" s="1"/>
       <c r="B761" s="7"/>
       <c r="C761" s="7"/>
@@ -11130,7 +11180,7 @@
       <c r="K761" s="7"/>
       <c r="L761" s="1"/>
     </row>
-    <row r="762" ht="19.5" customHeight="1">
+    <row r="762" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A762" s="1"/>
       <c r="B762" s="7"/>
       <c r="C762" s="7"/>
@@ -11144,7 +11194,7 @@
       <c r="K762" s="7"/>
       <c r="L762" s="1"/>
     </row>
-    <row r="763" ht="19.5" customHeight="1">
+    <row r="763" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A763" s="1"/>
       <c r="B763" s="7"/>
       <c r="C763" s="7"/>
@@ -11158,7 +11208,7 @@
       <c r="K763" s="7"/>
       <c r="L763" s="1"/>
     </row>
-    <row r="764" ht="19.5" customHeight="1">
+    <row r="764" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A764" s="1"/>
       <c r="B764" s="7"/>
       <c r="C764" s="7"/>
@@ -11172,7 +11222,7 @@
       <c r="K764" s="7"/>
       <c r="L764" s="1"/>
     </row>
-    <row r="765" ht="19.5" customHeight="1">
+    <row r="765" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A765" s="1"/>
       <c r="B765" s="7"/>
       <c r="C765" s="7"/>
@@ -11186,7 +11236,7 @@
       <c r="K765" s="7"/>
       <c r="L765" s="1"/>
     </row>
-    <row r="766" ht="19.5" customHeight="1">
+    <row r="766" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A766" s="1"/>
       <c r="B766" s="7"/>
       <c r="C766" s="7"/>
@@ -11200,7 +11250,7 @@
       <c r="K766" s="7"/>
       <c r="L766" s="1"/>
     </row>
-    <row r="767" ht="19.5" customHeight="1">
+    <row r="767" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A767" s="1"/>
       <c r="B767" s="7"/>
       <c r="C767" s="7"/>
@@ -11214,7 +11264,7 @@
       <c r="K767" s="7"/>
       <c r="L767" s="1"/>
     </row>
-    <row r="768" ht="19.5" customHeight="1">
+    <row r="768" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A768" s="1"/>
       <c r="B768" s="7"/>
       <c r="C768" s="7"/>
@@ -11228,7 +11278,7 @@
       <c r="K768" s="7"/>
       <c r="L768" s="1"/>
     </row>
-    <row r="769" ht="19.5" customHeight="1">
+    <row r="769" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A769" s="1"/>
       <c r="B769" s="7"/>
       <c r="C769" s="7"/>
@@ -11242,7 +11292,7 @@
       <c r="K769" s="7"/>
       <c r="L769" s="1"/>
     </row>
-    <row r="770" ht="19.5" customHeight="1">
+    <row r="770" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A770" s="1"/>
       <c r="B770" s="7"/>
       <c r="C770" s="7"/>
@@ -11256,7 +11306,7 @@
       <c r="K770" s="7"/>
       <c r="L770" s="1"/>
     </row>
-    <row r="771" ht="19.5" customHeight="1">
+    <row r="771" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A771" s="1"/>
       <c r="B771" s="7"/>
       <c r="C771" s="7"/>
@@ -11270,7 +11320,7 @@
       <c r="K771" s="7"/>
       <c r="L771" s="1"/>
     </row>
-    <row r="772" ht="19.5" customHeight="1">
+    <row r="772" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A772" s="1"/>
       <c r="B772" s="7"/>
       <c r="C772" s="7"/>
@@ -11284,7 +11334,7 @@
       <c r="K772" s="7"/>
       <c r="L772" s="1"/>
     </row>
-    <row r="773" ht="19.5" customHeight="1">
+    <row r="773" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A773" s="1"/>
       <c r="B773" s="7"/>
       <c r="C773" s="7"/>
@@ -11298,7 +11348,7 @@
       <c r="K773" s="7"/>
       <c r="L773" s="1"/>
     </row>
-    <row r="774" ht="19.5" customHeight="1">
+    <row r="774" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A774" s="1"/>
       <c r="B774" s="7"/>
       <c r="C774" s="7"/>
@@ -11312,7 +11362,7 @@
       <c r="K774" s="7"/>
       <c r="L774" s="1"/>
     </row>
-    <row r="775" ht="19.5" customHeight="1">
+    <row r="775" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A775" s="1"/>
       <c r="B775" s="7"/>
       <c r="C775" s="7"/>
@@ -11326,7 +11376,7 @@
       <c r="K775" s="7"/>
       <c r="L775" s="1"/>
     </row>
-    <row r="776" ht="19.5" customHeight="1">
+    <row r="776" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A776" s="1"/>
       <c r="B776" s="7"/>
       <c r="C776" s="7"/>
@@ -11340,7 +11390,7 @@
       <c r="K776" s="7"/>
       <c r="L776" s="1"/>
     </row>
-    <row r="777" ht="19.5" customHeight="1">
+    <row r="777" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A777" s="1"/>
       <c r="B777" s="7"/>
       <c r="C777" s="7"/>
@@ -11354,7 +11404,7 @@
       <c r="K777" s="7"/>
       <c r="L777" s="1"/>
     </row>
-    <row r="778" ht="19.5" customHeight="1">
+    <row r="778" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A778" s="1"/>
       <c r="B778" s="7"/>
       <c r="C778" s="7"/>
@@ -11368,7 +11418,7 @@
       <c r="K778" s="7"/>
       <c r="L778" s="1"/>
     </row>
-    <row r="779" ht="19.5" customHeight="1">
+    <row r="779" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A779" s="1"/>
       <c r="B779" s="7"/>
       <c r="C779" s="7"/>
@@ -11382,7 +11432,7 @@
       <c r="K779" s="7"/>
       <c r="L779" s="1"/>
     </row>
-    <row r="780" ht="19.5" customHeight="1">
+    <row r="780" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A780" s="1"/>
       <c r="B780" s="7"/>
       <c r="C780" s="7"/>
@@ -11396,7 +11446,7 @@
       <c r="K780" s="7"/>
       <c r="L780" s="1"/>
     </row>
-    <row r="781" ht="19.5" customHeight="1">
+    <row r="781" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A781" s="1"/>
       <c r="B781" s="7"/>
       <c r="C781" s="7"/>
@@ -11410,7 +11460,7 @@
       <c r="K781" s="7"/>
       <c r="L781" s="1"/>
     </row>
-    <row r="782" ht="19.5" customHeight="1">
+    <row r="782" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A782" s="1"/>
       <c r="B782" s="7"/>
       <c r="C782" s="7"/>
@@ -11424,7 +11474,7 @@
       <c r="K782" s="7"/>
       <c r="L782" s="1"/>
     </row>
-    <row r="783" ht="19.5" customHeight="1">
+    <row r="783" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A783" s="1"/>
       <c r="B783" s="7"/>
       <c r="C783" s="7"/>
@@ -11438,7 +11488,7 @@
       <c r="K783" s="7"/>
       <c r="L783" s="1"/>
     </row>
-    <row r="784" ht="19.5" customHeight="1">
+    <row r="784" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A784" s="1"/>
       <c r="B784" s="7"/>
       <c r="C784" s="7"/>
@@ -11452,7 +11502,7 @@
       <c r="K784" s="7"/>
       <c r="L784" s="1"/>
     </row>
-    <row r="785" ht="19.5" customHeight="1">
+    <row r="785" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A785" s="1"/>
       <c r="B785" s="7"/>
       <c r="C785" s="7"/>
@@ -11466,7 +11516,7 @@
       <c r="K785" s="7"/>
       <c r="L785" s="1"/>
     </row>
-    <row r="786" ht="19.5" customHeight="1">
+    <row r="786" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A786" s="1"/>
       <c r="B786" s="7"/>
       <c r="C786" s="7"/>
@@ -11480,7 +11530,7 @@
       <c r="K786" s="7"/>
       <c r="L786" s="1"/>
     </row>
-    <row r="787" ht="19.5" customHeight="1">
+    <row r="787" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A787" s="1"/>
       <c r="B787" s="7"/>
       <c r="C787" s="7"/>
@@ -11494,7 +11544,7 @@
       <c r="K787" s="7"/>
       <c r="L787" s="1"/>
     </row>
-    <row r="788" ht="19.5" customHeight="1">
+    <row r="788" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A788" s="1"/>
       <c r="B788" s="7"/>
       <c r="C788" s="7"/>
@@ -11508,7 +11558,7 @@
       <c r="K788" s="7"/>
       <c r="L788" s="1"/>
     </row>
-    <row r="789" ht="19.5" customHeight="1">
+    <row r="789" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A789" s="1"/>
       <c r="B789" s="7"/>
       <c r="C789" s="7"/>
@@ -11522,7 +11572,7 @@
       <c r="K789" s="7"/>
       <c r="L789" s="1"/>
     </row>
-    <row r="790" ht="19.5" customHeight="1">
+    <row r="790" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A790" s="1"/>
       <c r="B790" s="7"/>
       <c r="C790" s="7"/>
@@ -11536,7 +11586,7 @@
       <c r="K790" s="7"/>
       <c r="L790" s="1"/>
     </row>
-    <row r="791" ht="19.5" customHeight="1">
+    <row r="791" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A791" s="1"/>
       <c r="B791" s="7"/>
       <c r="C791" s="7"/>
@@ -11550,7 +11600,7 @@
       <c r="K791" s="7"/>
       <c r="L791" s="1"/>
     </row>
-    <row r="792" ht="19.5" customHeight="1">
+    <row r="792" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A792" s="1"/>
       <c r="B792" s="7"/>
       <c r="C792" s="7"/>
@@ -11564,7 +11614,7 @@
       <c r="K792" s="7"/>
       <c r="L792" s="1"/>
     </row>
-    <row r="793" ht="19.5" customHeight="1">
+    <row r="793" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A793" s="1"/>
       <c r="B793" s="7"/>
       <c r="C793" s="7"/>
@@ -11578,7 +11628,7 @@
       <c r="K793" s="7"/>
       <c r="L793" s="1"/>
     </row>
-    <row r="794" ht="19.5" customHeight="1">
+    <row r="794" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A794" s="1"/>
       <c r="B794" s="7"/>
       <c r="C794" s="7"/>
@@ -11592,7 +11642,7 @@
       <c r="K794" s="7"/>
       <c r="L794" s="1"/>
     </row>
-    <row r="795" ht="19.5" customHeight="1">
+    <row r="795" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A795" s="1"/>
       <c r="B795" s="7"/>
       <c r="C795" s="7"/>
@@ -11606,7 +11656,7 @@
       <c r="K795" s="7"/>
       <c r="L795" s="1"/>
     </row>
-    <row r="796" ht="19.5" customHeight="1">
+    <row r="796" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A796" s="1"/>
       <c r="B796" s="7"/>
       <c r="C796" s="7"/>
@@ -11620,7 +11670,7 @@
       <c r="K796" s="7"/>
       <c r="L796" s="1"/>
     </row>
-    <row r="797" ht="19.5" customHeight="1">
+    <row r="797" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A797" s="1"/>
       <c r="B797" s="7"/>
       <c r="C797" s="7"/>
@@ -11634,7 +11684,7 @@
       <c r="K797" s="7"/>
       <c r="L797" s="1"/>
     </row>
-    <row r="798" ht="19.5" customHeight="1">
+    <row r="798" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A798" s="1"/>
       <c r="B798" s="7"/>
       <c r="C798" s="7"/>
@@ -11648,7 +11698,7 @@
       <c r="K798" s="7"/>
       <c r="L798" s="1"/>
     </row>
-    <row r="799" ht="19.5" customHeight="1">
+    <row r="799" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A799" s="1"/>
       <c r="B799" s="7"/>
       <c r="C799" s="7"/>
@@ -11662,7 +11712,7 @@
       <c r="K799" s="7"/>
       <c r="L799" s="1"/>
     </row>
-    <row r="800" ht="19.5" customHeight="1">
+    <row r="800" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A800" s="1"/>
       <c r="B800" s="7"/>
       <c r="C800" s="7"/>
@@ -11676,7 +11726,7 @@
       <c r="K800" s="7"/>
       <c r="L800" s="1"/>
     </row>
-    <row r="801" ht="19.5" customHeight="1">
+    <row r="801" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A801" s="1"/>
       <c r="B801" s="7"/>
       <c r="C801" s="7"/>
@@ -11690,7 +11740,7 @@
       <c r="K801" s="7"/>
       <c r="L801" s="1"/>
     </row>
-    <row r="802" ht="19.5" customHeight="1">
+    <row r="802" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A802" s="1"/>
       <c r="B802" s="7"/>
       <c r="C802" s="7"/>
@@ -11704,7 +11754,7 @@
       <c r="K802" s="7"/>
       <c r="L802" s="1"/>
     </row>
-    <row r="803" ht="19.5" customHeight="1">
+    <row r="803" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A803" s="1"/>
       <c r="B803" s="7"/>
       <c r="C803" s="7"/>
@@ -11718,7 +11768,7 @@
       <c r="K803" s="7"/>
       <c r="L803" s="1"/>
     </row>
-    <row r="804" ht="19.5" customHeight="1">
+    <row r="804" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A804" s="1"/>
       <c r="B804" s="7"/>
       <c r="C804" s="7"/>
@@ -11732,7 +11782,7 @@
       <c r="K804" s="7"/>
       <c r="L804" s="1"/>
     </row>
-    <row r="805" ht="19.5" customHeight="1">
+    <row r="805" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A805" s="1"/>
       <c r="B805" s="7"/>
       <c r="C805" s="7"/>
@@ -11746,7 +11796,7 @@
       <c r="K805" s="7"/>
       <c r="L805" s="1"/>
     </row>
-    <row r="806" ht="19.5" customHeight="1">
+    <row r="806" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A806" s="1"/>
       <c r="B806" s="7"/>
       <c r="C806" s="7"/>
@@ -11760,7 +11810,7 @@
       <c r="K806" s="7"/>
       <c r="L806" s="1"/>
     </row>
-    <row r="807" ht="19.5" customHeight="1">
+    <row r="807" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A807" s="1"/>
       <c r="B807" s="7"/>
       <c r="C807" s="7"/>
@@ -11774,7 +11824,7 @@
       <c r="K807" s="7"/>
       <c r="L807" s="1"/>
     </row>
-    <row r="808" ht="19.5" customHeight="1">
+    <row r="808" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A808" s="1"/>
       <c r="B808" s="7"/>
       <c r="C808" s="7"/>
@@ -11788,7 +11838,7 @@
       <c r="K808" s="7"/>
       <c r="L808" s="1"/>
     </row>
-    <row r="809" ht="19.5" customHeight="1">
+    <row r="809" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A809" s="1"/>
       <c r="B809" s="7"/>
       <c r="C809" s="7"/>
@@ -11802,7 +11852,7 @@
       <c r="K809" s="7"/>
       <c r="L809" s="1"/>
     </row>
-    <row r="810" ht="19.5" customHeight="1">
+    <row r="810" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A810" s="1"/>
       <c r="B810" s="7"/>
       <c r="C810" s="7"/>
@@ -11816,7 +11866,7 @@
       <c r="K810" s="7"/>
       <c r="L810" s="1"/>
     </row>
-    <row r="811" ht="19.5" customHeight="1">
+    <row r="811" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A811" s="1"/>
       <c r="B811" s="7"/>
       <c r="C811" s="7"/>
@@ -11830,7 +11880,7 @@
       <c r="K811" s="7"/>
       <c r="L811" s="1"/>
     </row>
-    <row r="812" ht="19.5" customHeight="1">
+    <row r="812" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A812" s="1"/>
       <c r="B812" s="7"/>
       <c r="C812" s="7"/>
@@ -11844,7 +11894,7 @@
       <c r="K812" s="7"/>
       <c r="L812" s="1"/>
     </row>
-    <row r="813" ht="19.5" customHeight="1">
+    <row r="813" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A813" s="1"/>
       <c r="B813" s="7"/>
       <c r="C813" s="7"/>
@@ -11858,7 +11908,7 @@
       <c r="K813" s="7"/>
       <c r="L813" s="1"/>
     </row>
-    <row r="814" ht="19.5" customHeight="1">
+    <row r="814" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A814" s="1"/>
       <c r="B814" s="7"/>
       <c r="C814" s="7"/>
@@ -11872,7 +11922,7 @@
       <c r="K814" s="7"/>
       <c r="L814" s="1"/>
     </row>
-    <row r="815" ht="19.5" customHeight="1">
+    <row r="815" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A815" s="1"/>
       <c r="B815" s="7"/>
       <c r="C815" s="7"/>
@@ -11886,7 +11936,7 @@
       <c r="K815" s="7"/>
       <c r="L815" s="1"/>
     </row>
-    <row r="816" ht="19.5" customHeight="1">
+    <row r="816" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A816" s="1"/>
       <c r="B816" s="7"/>
       <c r="C816" s="7"/>
@@ -11900,7 +11950,7 @@
       <c r="K816" s="7"/>
       <c r="L816" s="1"/>
     </row>
-    <row r="817" ht="19.5" customHeight="1">
+    <row r="817" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A817" s="1"/>
       <c r="B817" s="7"/>
       <c r="C817" s="7"/>
@@ -11914,7 +11964,7 @@
       <c r="K817" s="7"/>
       <c r="L817" s="1"/>
     </row>
-    <row r="818" ht="19.5" customHeight="1">
+    <row r="818" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A818" s="1"/>
       <c r="B818" s="7"/>
       <c r="C818" s="7"/>
@@ -11928,7 +11978,7 @@
       <c r="K818" s="7"/>
       <c r="L818" s="1"/>
     </row>
-    <row r="819" ht="19.5" customHeight="1">
+    <row r="819" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A819" s="1"/>
       <c r="B819" s="7"/>
       <c r="C819" s="7"/>
@@ -11942,7 +11992,7 @@
       <c r="K819" s="7"/>
       <c r="L819" s="1"/>
     </row>
-    <row r="820" ht="19.5" customHeight="1">
+    <row r="820" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A820" s="1"/>
       <c r="B820" s="7"/>
       <c r="C820" s="7"/>
@@ -11956,7 +12006,7 @@
       <c r="K820" s="7"/>
       <c r="L820" s="1"/>
     </row>
-    <row r="821" ht="19.5" customHeight="1">
+    <row r="821" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A821" s="1"/>
       <c r="B821" s="7"/>
       <c r="C821" s="7"/>
@@ -11970,7 +12020,7 @@
       <c r="K821" s="7"/>
       <c r="L821" s="1"/>
     </row>
-    <row r="822" ht="19.5" customHeight="1">
+    <row r="822" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A822" s="1"/>
       <c r="B822" s="7"/>
       <c r="C822" s="7"/>
@@ -11984,7 +12034,7 @@
       <c r="K822" s="7"/>
       <c r="L822" s="1"/>
     </row>
-    <row r="823" ht="19.5" customHeight="1">
+    <row r="823" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A823" s="1"/>
       <c r="B823" s="7"/>
       <c r="C823" s="7"/>
@@ -11998,7 +12048,7 @@
       <c r="K823" s="7"/>
       <c r="L823" s="1"/>
     </row>
-    <row r="824" ht="19.5" customHeight="1">
+    <row r="824" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A824" s="1"/>
       <c r="B824" s="7"/>
       <c r="C824" s="7"/>
@@ -12012,7 +12062,7 @@
       <c r="K824" s="7"/>
       <c r="L824" s="1"/>
     </row>
-    <row r="825" ht="19.5" customHeight="1">
+    <row r="825" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A825" s="1"/>
       <c r="B825" s="7"/>
       <c r="C825" s="7"/>
@@ -12026,7 +12076,7 @@
       <c r="K825" s="7"/>
       <c r="L825" s="1"/>
     </row>
-    <row r="826" ht="19.5" customHeight="1">
+    <row r="826" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A826" s="1"/>
       <c r="B826" s="7"/>
       <c r="C826" s="7"/>
@@ -12040,7 +12090,7 @@
       <c r="K826" s="7"/>
       <c r="L826" s="1"/>
     </row>
-    <row r="827" ht="19.5" customHeight="1">
+    <row r="827" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A827" s="1"/>
       <c r="B827" s="7"/>
       <c r="C827" s="7"/>
@@ -12054,7 +12104,7 @@
       <c r="K827" s="7"/>
       <c r="L827" s="1"/>
     </row>
-    <row r="828" ht="19.5" customHeight="1">
+    <row r="828" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A828" s="1"/>
       <c r="B828" s="7"/>
       <c r="C828" s="7"/>
@@ -12068,7 +12118,7 @@
       <c r="K828" s="7"/>
       <c r="L828" s="1"/>
     </row>
-    <row r="829" ht="19.5" customHeight="1">
+    <row r="829" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A829" s="1"/>
       <c r="B829" s="7"/>
       <c r="C829" s="7"/>
@@ -12082,7 +12132,7 @@
       <c r="K829" s="7"/>
       <c r="L829" s="1"/>
     </row>
-    <row r="830" ht="19.5" customHeight="1">
+    <row r="830" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A830" s="1"/>
       <c r="B830" s="7"/>
       <c r="C830" s="7"/>
@@ -12096,7 +12146,7 @@
       <c r="K830" s="7"/>
       <c r="L830" s="1"/>
     </row>
-    <row r="831" ht="19.5" customHeight="1">
+    <row r="831" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A831" s="1"/>
       <c r="B831" s="7"/>
       <c r="C831" s="7"/>
@@ -12110,7 +12160,7 @@
       <c r="K831" s="7"/>
       <c r="L831" s="1"/>
     </row>
-    <row r="832" ht="19.5" customHeight="1">
+    <row r="832" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A832" s="1"/>
       <c r="B832" s="7"/>
       <c r="C832" s="7"/>
@@ -12124,7 +12174,7 @@
       <c r="K832" s="7"/>
       <c r="L832" s="1"/>
     </row>
-    <row r="833" ht="19.5" customHeight="1">
+    <row r="833" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A833" s="1"/>
       <c r="B833" s="7"/>
       <c r="C833" s="7"/>
@@ -12138,7 +12188,7 @@
       <c r="K833" s="7"/>
       <c r="L833" s="1"/>
     </row>
-    <row r="834" ht="19.5" customHeight="1">
+    <row r="834" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A834" s="1"/>
       <c r="B834" s="7"/>
       <c r="C834" s="7"/>
@@ -12152,7 +12202,7 @@
       <c r="K834" s="7"/>
       <c r="L834" s="1"/>
     </row>
-    <row r="835" ht="19.5" customHeight="1">
+    <row r="835" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A835" s="1"/>
       <c r="B835" s="7"/>
       <c r="C835" s="7"/>
@@ -12166,7 +12216,7 @@
       <c r="K835" s="7"/>
       <c r="L835" s="1"/>
     </row>
-    <row r="836" ht="19.5" customHeight="1">
+    <row r="836" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A836" s="1"/>
       <c r="B836" s="7"/>
       <c r="C836" s="7"/>
@@ -12180,7 +12230,7 @@
       <c r="K836" s="7"/>
       <c r="L836" s="1"/>
     </row>
-    <row r="837" ht="19.5" customHeight="1">
+    <row r="837" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A837" s="1"/>
       <c r="B837" s="7"/>
       <c r="C837" s="7"/>
@@ -12194,7 +12244,7 @@
       <c r="K837" s="7"/>
       <c r="L837" s="1"/>
     </row>
-    <row r="838" ht="19.5" customHeight="1">
+    <row r="838" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A838" s="1"/>
       <c r="B838" s="7"/>
       <c r="C838" s="7"/>
@@ -12208,7 +12258,7 @@
       <c r="K838" s="7"/>
       <c r="L838" s="1"/>
     </row>
-    <row r="839" ht="19.5" customHeight="1">
+    <row r="839" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A839" s="1"/>
       <c r="B839" s="7"/>
       <c r="C839" s="7"/>
@@ -12222,7 +12272,7 @@
       <c r="K839" s="7"/>
       <c r="L839" s="1"/>
     </row>
-    <row r="840" ht="19.5" customHeight="1">
+    <row r="840" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A840" s="1"/>
       <c r="B840" s="7"/>
       <c r="C840" s="7"/>
@@ -12236,7 +12286,7 @@
       <c r="K840" s="7"/>
       <c r="L840" s="1"/>
     </row>
-    <row r="841" ht="19.5" customHeight="1">
+    <row r="841" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A841" s="1"/>
       <c r="B841" s="7"/>
       <c r="C841" s="7"/>
@@ -12250,7 +12300,7 @@
       <c r="K841" s="7"/>
       <c r="L841" s="1"/>
     </row>
-    <row r="842" ht="19.5" customHeight="1">
+    <row r="842" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A842" s="1"/>
       <c r="B842" s="7"/>
       <c r="C842" s="7"/>
@@ -12264,7 +12314,7 @@
       <c r="K842" s="7"/>
       <c r="L842" s="1"/>
     </row>
-    <row r="843" ht="19.5" customHeight="1">
+    <row r="843" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A843" s="1"/>
       <c r="B843" s="7"/>
       <c r="C843" s="7"/>
@@ -12278,7 +12328,7 @@
       <c r="K843" s="7"/>
       <c r="L843" s="1"/>
     </row>
-    <row r="844" ht="19.5" customHeight="1">
+    <row r="844" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A844" s="1"/>
       <c r="B844" s="7"/>
       <c r="C844" s="7"/>
@@ -12292,7 +12342,7 @@
       <c r="K844" s="7"/>
       <c r="L844" s="1"/>
     </row>
-    <row r="845" ht="19.5" customHeight="1">
+    <row r="845" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A845" s="1"/>
       <c r="B845" s="7"/>
       <c r="C845" s="7"/>
@@ -12306,7 +12356,7 @@
       <c r="K845" s="7"/>
       <c r="L845" s="1"/>
     </row>
-    <row r="846" ht="19.5" customHeight="1">
+    <row r="846" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A846" s="1"/>
       <c r="B846" s="7"/>
       <c r="C846" s="7"/>
@@ -12320,7 +12370,7 @@
       <c r="K846" s="7"/>
       <c r="L846" s="1"/>
     </row>
-    <row r="847" ht="19.5" customHeight="1">
+    <row r="847" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A847" s="1"/>
       <c r="B847" s="7"/>
       <c r="C847" s="7"/>
@@ -12334,7 +12384,7 @@
       <c r="K847" s="7"/>
       <c r="L847" s="1"/>
     </row>
-    <row r="848" ht="19.5" customHeight="1">
+    <row r="848" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A848" s="1"/>
       <c r="B848" s="7"/>
       <c r="C848" s="7"/>
@@ -12348,7 +12398,7 @@
       <c r="K848" s="7"/>
       <c r="L848" s="1"/>
     </row>
-    <row r="849" ht="19.5" customHeight="1">
+    <row r="849" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A849" s="1"/>
       <c r="B849" s="7"/>
       <c r="C849" s="7"/>
@@ -12362,7 +12412,7 @@
       <c r="K849" s="7"/>
       <c r="L849" s="1"/>
     </row>
-    <row r="850" ht="19.5" customHeight="1">
+    <row r="850" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A850" s="1"/>
       <c r="B850" s="7"/>
       <c r="C850" s="7"/>
@@ -12376,7 +12426,7 @@
       <c r="K850" s="7"/>
       <c r="L850" s="1"/>
     </row>
-    <row r="851" ht="19.5" customHeight="1">
+    <row r="851" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A851" s="1"/>
       <c r="B851" s="7"/>
       <c r="C851" s="7"/>
@@ -12390,7 +12440,7 @@
       <c r="K851" s="7"/>
       <c r="L851" s="1"/>
     </row>
-    <row r="852" ht="19.5" customHeight="1">
+    <row r="852" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A852" s="1"/>
       <c r="B852" s="7"/>
       <c r="C852" s="7"/>
@@ -12404,7 +12454,7 @@
       <c r="K852" s="7"/>
       <c r="L852" s="1"/>
     </row>
-    <row r="853" ht="19.5" customHeight="1">
+    <row r="853" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A853" s="1"/>
       <c r="B853" s="7"/>
       <c r="C853" s="7"/>
@@ -12418,7 +12468,7 @@
       <c r="K853" s="7"/>
       <c r="L853" s="1"/>
     </row>
-    <row r="854" ht="19.5" customHeight="1">
+    <row r="854" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A854" s="1"/>
       <c r="B854" s="7"/>
       <c r="C854" s="7"/>
@@ -12432,7 +12482,7 @@
       <c r="K854" s="7"/>
       <c r="L854" s="1"/>
     </row>
-    <row r="855" ht="19.5" customHeight="1">
+    <row r="855" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A855" s="1"/>
       <c r="B855" s="7"/>
       <c r="C855" s="7"/>
@@ -12446,7 +12496,7 @@
       <c r="K855" s="7"/>
       <c r="L855" s="1"/>
     </row>
-    <row r="856" ht="19.5" customHeight="1">
+    <row r="856" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A856" s="1"/>
       <c r="B856" s="7"/>
       <c r="C856" s="7"/>
@@ -12460,7 +12510,7 @@
       <c r="K856" s="7"/>
       <c r="L856" s="1"/>
     </row>
-    <row r="857" ht="19.5" customHeight="1">
+    <row r="857" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A857" s="1"/>
       <c r="B857" s="7"/>
       <c r="C857" s="7"/>
@@ -12474,7 +12524,7 @@
       <c r="K857" s="7"/>
       <c r="L857" s="1"/>
     </row>
-    <row r="858" ht="19.5" customHeight="1">
+    <row r="858" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A858" s="1"/>
       <c r="B858" s="7"/>
       <c r="C858" s="7"/>
@@ -12488,7 +12538,7 @@
       <c r="K858" s="7"/>
       <c r="L858" s="1"/>
     </row>
-    <row r="859" ht="19.5" customHeight="1">
+    <row r="859" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A859" s="1"/>
       <c r="B859" s="7"/>
       <c r="C859" s="7"/>
@@ -12502,7 +12552,7 @@
       <c r="K859" s="7"/>
       <c r="L859" s="1"/>
     </row>
-    <row r="860" ht="19.5" customHeight="1">
+    <row r="860" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A860" s="1"/>
       <c r="B860" s="7"/>
       <c r="C860" s="7"/>
@@ -12516,7 +12566,7 @@
       <c r="K860" s="7"/>
       <c r="L860" s="1"/>
     </row>
-    <row r="861" ht="19.5" customHeight="1">
+    <row r="861" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A861" s="1"/>
       <c r="B861" s="7"/>
       <c r="C861" s="7"/>
@@ -12530,7 +12580,7 @@
       <c r="K861" s="7"/>
       <c r="L861" s="1"/>
     </row>
-    <row r="862" ht="19.5" customHeight="1">
+    <row r="862" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A862" s="1"/>
       <c r="B862" s="7"/>
       <c r="C862" s="7"/>
@@ -12544,7 +12594,7 @@
       <c r="K862" s="7"/>
       <c r="L862" s="1"/>
     </row>
-    <row r="863" ht="19.5" customHeight="1">
+    <row r="863" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A863" s="1"/>
       <c r="B863" s="7"/>
       <c r="C863" s="7"/>
@@ -12558,7 +12608,7 @@
       <c r="K863" s="7"/>
       <c r="L863" s="1"/>
     </row>
-    <row r="864" ht="19.5" customHeight="1">
+    <row r="864" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A864" s="1"/>
       <c r="B864" s="7"/>
       <c r="C864" s="7"/>
@@ -12572,7 +12622,7 @@
       <c r="K864" s="7"/>
       <c r="L864" s="1"/>
     </row>
-    <row r="865" ht="19.5" customHeight="1">
+    <row r="865" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A865" s="1"/>
       <c r="B865" s="7"/>
       <c r="C865" s="7"/>
@@ -12586,7 +12636,7 @@
       <c r="K865" s="7"/>
       <c r="L865" s="1"/>
     </row>
-    <row r="866" ht="19.5" customHeight="1">
+    <row r="866" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A866" s="1"/>
       <c r="B866" s="7"/>
       <c r="C866" s="7"/>
@@ -12600,7 +12650,7 @@
       <c r="K866" s="7"/>
       <c r="L866" s="1"/>
     </row>
-    <row r="867" ht="19.5" customHeight="1">
+    <row r="867" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A867" s="1"/>
       <c r="B867" s="7"/>
       <c r="C867" s="7"/>
@@ -12614,7 +12664,7 @@
       <c r="K867" s="7"/>
       <c r="L867" s="1"/>
     </row>
-    <row r="868" ht="19.5" customHeight="1">
+    <row r="868" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A868" s="1"/>
       <c r="B868" s="7"/>
       <c r="C868" s="7"/>
@@ -12628,7 +12678,7 @@
       <c r="K868" s="7"/>
       <c r="L868" s="1"/>
     </row>
-    <row r="869" ht="19.5" customHeight="1">
+    <row r="869" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A869" s="1"/>
       <c r="B869" s="7"/>
       <c r="C869" s="7"/>
@@ -12642,7 +12692,7 @@
       <c r="K869" s="7"/>
       <c r="L869" s="1"/>
     </row>
-    <row r="870" ht="19.5" customHeight="1">
+    <row r="870" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A870" s="1"/>
       <c r="B870" s="7"/>
       <c r="C870" s="7"/>
@@ -12656,7 +12706,7 @@
       <c r="K870" s="7"/>
       <c r="L870" s="1"/>
     </row>
-    <row r="871" ht="19.5" customHeight="1">
+    <row r="871" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A871" s="1"/>
       <c r="B871" s="7"/>
       <c r="C871" s="7"/>
@@ -12670,7 +12720,7 @@
       <c r="K871" s="7"/>
       <c r="L871" s="1"/>
     </row>
-    <row r="872" ht="19.5" customHeight="1">
+    <row r="872" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A872" s="1"/>
       <c r="B872" s="7"/>
       <c r="C872" s="7"/>
@@ -12684,7 +12734,7 @@
       <c r="K872" s="7"/>
       <c r="L872" s="1"/>
     </row>
-    <row r="873" ht="19.5" customHeight="1">
+    <row r="873" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A873" s="1"/>
       <c r="B873" s="7"/>
       <c r="C873" s="7"/>
@@ -12698,7 +12748,7 @@
       <c r="K873" s="7"/>
       <c r="L873" s="1"/>
     </row>
-    <row r="874" ht="19.5" customHeight="1">
+    <row r="874" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A874" s="1"/>
       <c r="B874" s="7"/>
       <c r="C874" s="7"/>
@@ -12712,7 +12762,7 @@
       <c r="K874" s="7"/>
       <c r="L874" s="1"/>
     </row>
-    <row r="875" ht="19.5" customHeight="1">
+    <row r="875" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A875" s="1"/>
       <c r="B875" s="7"/>
       <c r="C875" s="7"/>
@@ -12726,7 +12776,7 @@
       <c r="K875" s="7"/>
       <c r="L875" s="1"/>
     </row>
-    <row r="876" ht="19.5" customHeight="1">
+    <row r="876" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A876" s="1"/>
       <c r="B876" s="7"/>
       <c r="C876" s="7"/>
@@ -12740,7 +12790,7 @@
       <c r="K876" s="7"/>
       <c r="L876" s="1"/>
     </row>
-    <row r="877" ht="19.5" customHeight="1">
+    <row r="877" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A877" s="1"/>
       <c r="B877" s="7"/>
       <c r="C877" s="7"/>
@@ -12754,7 +12804,7 @@
       <c r="K877" s="7"/>
       <c r="L877" s="1"/>
     </row>
-    <row r="878" ht="19.5" customHeight="1">
+    <row r="878" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A878" s="1"/>
       <c r="B878" s="7"/>
       <c r="C878" s="7"/>
@@ -12768,7 +12818,7 @@
       <c r="K878" s="7"/>
       <c r="L878" s="1"/>
     </row>
-    <row r="879" ht="19.5" customHeight="1">
+    <row r="879" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A879" s="1"/>
       <c r="B879" s="7"/>
       <c r="C879" s="7"/>
@@ -12782,7 +12832,7 @@
       <c r="K879" s="7"/>
       <c r="L879" s="1"/>
     </row>
-    <row r="880" ht="19.5" customHeight="1">
+    <row r="880" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A880" s="1"/>
       <c r="B880" s="7"/>
       <c r="C880" s="7"/>
@@ -12796,7 +12846,7 @@
       <c r="K880" s="7"/>
       <c r="L880" s="1"/>
     </row>
-    <row r="881" ht="19.5" customHeight="1">
+    <row r="881" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A881" s="1"/>
       <c r="B881" s="7"/>
       <c r="C881" s="7"/>
@@ -12810,7 +12860,7 @@
       <c r="K881" s="7"/>
       <c r="L881" s="1"/>
     </row>
-    <row r="882" ht="19.5" customHeight="1">
+    <row r="882" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A882" s="1"/>
       <c r="B882" s="7"/>
       <c r="C882" s="7"/>
@@ -12824,7 +12874,7 @@
       <c r="K882" s="7"/>
       <c r="L882" s="1"/>
     </row>
-    <row r="883" ht="19.5" customHeight="1">
+    <row r="883" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A883" s="1"/>
       <c r="B883" s="7"/>
       <c r="C883" s="7"/>
@@ -12838,7 +12888,7 @@
       <c r="K883" s="7"/>
       <c r="L883" s="1"/>
     </row>
-    <row r="884" ht="19.5" customHeight="1">
+    <row r="884" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A884" s="1"/>
       <c r="B884" s="7"/>
       <c r="C884" s="7"/>
@@ -12852,7 +12902,7 @@
       <c r="K884" s="7"/>
       <c r="L884" s="1"/>
     </row>
-    <row r="885" ht="19.5" customHeight="1">
+    <row r="885" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A885" s="1"/>
       <c r="B885" s="7"/>
       <c r="C885" s="7"/>
@@ -12866,7 +12916,7 @@
       <c r="K885" s="7"/>
       <c r="L885" s="1"/>
     </row>
-    <row r="886" ht="19.5" customHeight="1">
+    <row r="886" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A886" s="1"/>
       <c r="B886" s="7"/>
       <c r="C886" s="7"/>
@@ -12880,7 +12930,7 @@
       <c r="K886" s="7"/>
       <c r="L886" s="1"/>
     </row>
-    <row r="887" ht="19.5" customHeight="1">
+    <row r="887" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A887" s="1"/>
       <c r="B887" s="7"/>
       <c r="C887" s="7"/>
@@ -12894,7 +12944,7 @@
       <c r="K887" s="7"/>
       <c r="L887" s="1"/>
     </row>
-    <row r="888" ht="19.5" customHeight="1">
+    <row r="888" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A888" s="1"/>
       <c r="B888" s="7"/>
       <c r="C888" s="7"/>
@@ -12908,7 +12958,7 @@
       <c r="K888" s="7"/>
       <c r="L888" s="1"/>
     </row>
-    <row r="889" ht="19.5" customHeight="1">
+    <row r="889" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A889" s="1"/>
       <c r="B889" s="7"/>
       <c r="C889" s="7"/>
@@ -12922,7 +12972,7 @@
       <c r="K889" s="7"/>
       <c r="L889" s="1"/>
     </row>
-    <row r="890" ht="19.5" customHeight="1">
+    <row r="890" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A890" s="1"/>
       <c r="B890" s="7"/>
       <c r="C890" s="7"/>
@@ -12936,7 +12986,7 @@
       <c r="K890" s="7"/>
       <c r="L890" s="1"/>
     </row>
-    <row r="891" ht="19.5" customHeight="1">
+    <row r="891" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A891" s="1"/>
       <c r="B891" s="7"/>
       <c r="C891" s="7"/>
@@ -12950,7 +13000,7 @@
       <c r="K891" s="7"/>
       <c r="L891" s="1"/>
     </row>
-    <row r="892" ht="19.5" customHeight="1">
+    <row r="892" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A892" s="1"/>
       <c r="B892" s="7"/>
       <c r="C892" s="7"/>
@@ -12964,7 +13014,7 @@
       <c r="K892" s="7"/>
       <c r="L892" s="1"/>
     </row>
-    <row r="893" ht="19.5" customHeight="1">
+    <row r="893" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A893" s="1"/>
       <c r="B893" s="7"/>
       <c r="C893" s="7"/>
@@ -12978,7 +13028,7 @@
       <c r="K893" s="7"/>
       <c r="L893" s="1"/>
     </row>
-    <row r="894" ht="19.5" customHeight="1">
+    <row r="894" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A894" s="1"/>
       <c r="B894" s="7"/>
       <c r="C894" s="7"/>
@@ -12992,7 +13042,7 @@
       <c r="K894" s="7"/>
       <c r="L894" s="1"/>
     </row>
-    <row r="895" ht="19.5" customHeight="1">
+    <row r="895" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A895" s="1"/>
       <c r="B895" s="7"/>
       <c r="C895" s="7"/>
@@ -13006,7 +13056,7 @@
       <c r="K895" s="7"/>
       <c r="L895" s="1"/>
     </row>
-    <row r="896" ht="19.5" customHeight="1">
+    <row r="896" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A896" s="1"/>
       <c r="B896" s="7"/>
       <c r="C896" s="7"/>
@@ -13020,7 +13070,7 @@
       <c r="K896" s="7"/>
       <c r="L896" s="1"/>
     </row>
-    <row r="897" ht="19.5" customHeight="1">
+    <row r="897" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A897" s="1"/>
       <c r="B897" s="7"/>
       <c r="C897" s="7"/>
@@ -13034,7 +13084,7 @@
       <c r="K897" s="7"/>
       <c r="L897" s="1"/>
     </row>
-    <row r="898" ht="19.5" customHeight="1">
+    <row r="898" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A898" s="1"/>
       <c r="B898" s="7"/>
       <c r="C898" s="7"/>
@@ -13048,7 +13098,7 @@
       <c r="K898" s="7"/>
       <c r="L898" s="1"/>
     </row>
-    <row r="899" ht="19.5" customHeight="1">
+    <row r="899" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A899" s="1"/>
       <c r="B899" s="7"/>
       <c r="C899" s="7"/>
@@ -13062,7 +13112,7 @@
       <c r="K899" s="7"/>
       <c r="L899" s="1"/>
     </row>
-    <row r="900" ht="19.5" customHeight="1">
+    <row r="900" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A900" s="1"/>
       <c r="B900" s="7"/>
       <c r="C900" s="7"/>
@@ -13076,7 +13126,7 @@
       <c r="K900" s="7"/>
       <c r="L900" s="1"/>
     </row>
-    <row r="901" ht="19.5" customHeight="1">
+    <row r="901" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A901" s="1"/>
       <c r="B901" s="7"/>
       <c r="C901" s="7"/>
@@ -13090,7 +13140,7 @@
       <c r="K901" s="7"/>
       <c r="L901" s="1"/>
     </row>
-    <row r="902" ht="19.5" customHeight="1">
+    <row r="902" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A902" s="1"/>
       <c r="B902" s="7"/>
       <c r="C902" s="7"/>
@@ -13104,7 +13154,7 @@
       <c r="K902" s="7"/>
       <c r="L902" s="1"/>
     </row>
-    <row r="903" ht="19.5" customHeight="1">
+    <row r="903" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A903" s="1"/>
       <c r="B903" s="7"/>
       <c r="C903" s="7"/>
@@ -13118,7 +13168,7 @@
       <c r="K903" s="7"/>
       <c r="L903" s="1"/>
     </row>
-    <row r="904" ht="19.5" customHeight="1">
+    <row r="904" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A904" s="1"/>
       <c r="B904" s="7"/>
       <c r="C904" s="7"/>
@@ -13132,7 +13182,7 @@
       <c r="K904" s="7"/>
       <c r="L904" s="1"/>
     </row>
-    <row r="905" ht="19.5" customHeight="1">
+    <row r="905" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A905" s="1"/>
       <c r="B905" s="7"/>
       <c r="C905" s="7"/>
@@ -13146,7 +13196,7 @@
       <c r="K905" s="7"/>
       <c r="L905" s="1"/>
     </row>
-    <row r="906" ht="19.5" customHeight="1">
+    <row r="906" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A906" s="1"/>
       <c r="B906" s="7"/>
       <c r="C906" s="7"/>
@@ -13160,7 +13210,7 @@
       <c r="K906" s="7"/>
       <c r="L906" s="1"/>
     </row>
-    <row r="907" ht="19.5" customHeight="1">
+    <row r="907" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A907" s="1"/>
       <c r="B907" s="7"/>
       <c r="C907" s="7"/>
@@ -13174,7 +13224,7 @@
       <c r="K907" s="7"/>
       <c r="L907" s="1"/>
     </row>
-    <row r="908" ht="19.5" customHeight="1">
+    <row r="908" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A908" s="1"/>
       <c r="B908" s="7"/>
       <c r="C908" s="7"/>
@@ -13188,7 +13238,7 @@
       <c r="K908" s="7"/>
       <c r="L908" s="1"/>
     </row>
-    <row r="909" ht="19.5" customHeight="1">
+    <row r="909" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A909" s="1"/>
       <c r="B909" s="7"/>
       <c r="C909" s="7"/>
@@ -13202,7 +13252,7 @@
       <c r="K909" s="7"/>
       <c r="L909" s="1"/>
     </row>
-    <row r="910" ht="19.5" customHeight="1">
+    <row r="910" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A910" s="1"/>
       <c r="B910" s="7"/>
       <c r="C910" s="7"/>
@@ -13216,7 +13266,7 @@
       <c r="K910" s="7"/>
       <c r="L910" s="1"/>
     </row>
-    <row r="911" ht="19.5" customHeight="1">
+    <row r="911" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A911" s="1"/>
       <c r="B911" s="7"/>
       <c r="C911" s="7"/>
@@ -13230,7 +13280,7 @@
       <c r="K911" s="7"/>
       <c r="L911" s="1"/>
     </row>
-    <row r="912" ht="19.5" customHeight="1">
+    <row r="912" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A912" s="1"/>
       <c r="B912" s="7"/>
       <c r="C912" s="7"/>
@@ -13244,7 +13294,7 @@
       <c r="K912" s="7"/>
       <c r="L912" s="1"/>
     </row>
-    <row r="913" ht="19.5" customHeight="1">
+    <row r="913" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A913" s="1"/>
       <c r="B913" s="7"/>
       <c r="C913" s="7"/>
@@ -13258,7 +13308,7 @@
       <c r="K913" s="7"/>
       <c r="L913" s="1"/>
     </row>
-    <row r="914" ht="19.5" customHeight="1">
+    <row r="914" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A914" s="1"/>
       <c r="B914" s="7"/>
       <c r="C914" s="7"/>
@@ -13272,7 +13322,7 @@
       <c r="K914" s="7"/>
       <c r="L914" s="1"/>
     </row>
-    <row r="915" ht="19.5" customHeight="1">
+    <row r="915" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A915" s="1"/>
       <c r="B915" s="7"/>
       <c r="C915" s="7"/>
@@ -13286,7 +13336,7 @@
       <c r="K915" s="7"/>
       <c r="L915" s="1"/>
     </row>
-    <row r="916" ht="19.5" customHeight="1">
+    <row r="916" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A916" s="1"/>
       <c r="B916" s="7"/>
       <c r="C916" s="7"/>
@@ -13300,7 +13350,7 @@
       <c r="K916" s="7"/>
       <c r="L916" s="1"/>
     </row>
-    <row r="917" ht="19.5" customHeight="1">
+    <row r="917" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A917" s="1"/>
       <c r="B917" s="7"/>
       <c r="C917" s="7"/>
@@ -13314,7 +13364,7 @@
       <c r="K917" s="7"/>
       <c r="L917" s="1"/>
     </row>
-    <row r="918" ht="19.5" customHeight="1">
+    <row r="918" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A918" s="1"/>
       <c r="B918" s="7"/>
       <c r="C918" s="7"/>
@@ -13328,7 +13378,7 @@
       <c r="K918" s="7"/>
       <c r="L918" s="1"/>
     </row>
-    <row r="919" ht="19.5" customHeight="1">
+    <row r="919" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A919" s="1"/>
       <c r="B919" s="7"/>
       <c r="C919" s="7"/>
@@ -13342,7 +13392,7 @@
       <c r="K919" s="7"/>
       <c r="L919" s="1"/>
     </row>
-    <row r="920" ht="19.5" customHeight="1">
+    <row r="920" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A920" s="1"/>
       <c r="B920" s="7"/>
       <c r="C920" s="7"/>
@@ -13356,7 +13406,7 @@
       <c r="K920" s="7"/>
       <c r="L920" s="1"/>
     </row>
-    <row r="921" ht="19.5" customHeight="1">
+    <row r="921" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A921" s="1"/>
       <c r="B921" s="7"/>
       <c r="C921" s="7"/>
@@ -13370,7 +13420,7 @@
       <c r="K921" s="7"/>
       <c r="L921" s="1"/>
     </row>
-    <row r="922" ht="19.5" customHeight="1">
+    <row r="922" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A922" s="1"/>
       <c r="B922" s="7"/>
       <c r="C922" s="7"/>
@@ -13384,7 +13434,7 @@
       <c r="K922" s="7"/>
       <c r="L922" s="1"/>
     </row>
-    <row r="923" ht="19.5" customHeight="1">
+    <row r="923" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A923" s="1"/>
       <c r="B923" s="7"/>
       <c r="C923" s="7"/>
@@ -13398,7 +13448,7 @@
       <c r="K923" s="7"/>
       <c r="L923" s="1"/>
     </row>
-    <row r="924" ht="19.5" customHeight="1">
+    <row r="924" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A924" s="1"/>
       <c r="B924" s="7"/>
       <c r="C924" s="7"/>
@@ -13412,7 +13462,7 @@
       <c r="K924" s="7"/>
       <c r="L924" s="1"/>
     </row>
-    <row r="925" ht="19.5" customHeight="1">
+    <row r="925" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A925" s="1"/>
       <c r="B925" s="7"/>
       <c r="C925" s="7"/>
@@ -13426,7 +13476,7 @@
       <c r="K925" s="7"/>
       <c r="L925" s="1"/>
     </row>
-    <row r="926" ht="19.5" customHeight="1">
+    <row r="926" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A926" s="1"/>
       <c r="B926" s="7"/>
       <c r="C926" s="7"/>
@@ -13440,7 +13490,7 @@
       <c r="K926" s="7"/>
       <c r="L926" s="1"/>
     </row>
-    <row r="927" ht="19.5" customHeight="1">
+    <row r="927" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A927" s="1"/>
       <c r="B927" s="7"/>
       <c r="C927" s="7"/>
@@ -13454,7 +13504,7 @@
       <c r="K927" s="7"/>
       <c r="L927" s="1"/>
     </row>
-    <row r="928" ht="19.5" customHeight="1">
+    <row r="928" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A928" s="1"/>
       <c r="B928" s="7"/>
       <c r="C928" s="7"/>
@@ -13468,7 +13518,7 @@
       <c r="K928" s="7"/>
       <c r="L928" s="1"/>
     </row>
-    <row r="929" ht="19.5" customHeight="1">
+    <row r="929" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A929" s="1"/>
       <c r="B929" s="7"/>
       <c r="C929" s="7"/>
@@ -13482,7 +13532,7 @@
       <c r="K929" s="7"/>
       <c r="L929" s="1"/>
     </row>
-    <row r="930" ht="19.5" customHeight="1">
+    <row r="930" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A930" s="1"/>
       <c r="B930" s="7"/>
       <c r="C930" s="7"/>
@@ -13496,7 +13546,7 @@
       <c r="K930" s="7"/>
       <c r="L930" s="1"/>
     </row>
-    <row r="931" ht="19.5" customHeight="1">
+    <row r="931" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A931" s="1"/>
       <c r="B931" s="7"/>
       <c r="C931" s="7"/>
@@ -13510,7 +13560,7 @@
       <c r="K931" s="7"/>
       <c r="L931" s="1"/>
     </row>
-    <row r="932" ht="19.5" customHeight="1">
+    <row r="932" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A932" s="1"/>
       <c r="B932" s="7"/>
       <c r="C932" s="7"/>
@@ -13524,7 +13574,7 @@
       <c r="K932" s="7"/>
       <c r="L932" s="1"/>
     </row>
-    <row r="933" ht="19.5" customHeight="1">
+    <row r="933" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A933" s="1"/>
       <c r="B933" s="7"/>
       <c r="C933" s="7"/>
@@ -13538,7 +13588,7 @@
       <c r="K933" s="7"/>
       <c r="L933" s="1"/>
     </row>
-    <row r="934" ht="19.5" customHeight="1">
+    <row r="934" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A934" s="1"/>
       <c r="B934" s="7"/>
       <c r="C934" s="7"/>
@@ -13552,7 +13602,7 @@
       <c r="K934" s="7"/>
       <c r="L934" s="1"/>
     </row>
-    <row r="935" ht="19.5" customHeight="1">
+    <row r="935" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A935" s="1"/>
       <c r="B935" s="7"/>
       <c r="C935" s="7"/>
@@ -13566,7 +13616,7 @@
       <c r="K935" s="7"/>
       <c r="L935" s="1"/>
     </row>
-    <row r="936" ht="19.5" customHeight="1">
+    <row r="936" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A936" s="1"/>
       <c r="B936" s="7"/>
       <c r="C936" s="7"/>
@@ -13580,7 +13630,7 @@
       <c r="K936" s="7"/>
       <c r="L936" s="1"/>
     </row>
-    <row r="937" ht="19.5" customHeight="1">
+    <row r="937" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A937" s="1"/>
       <c r="B937" s="7"/>
       <c r="C937" s="7"/>
@@ -13594,7 +13644,7 @@
       <c r="K937" s="7"/>
       <c r="L937" s="1"/>
     </row>
-    <row r="938" ht="19.5" customHeight="1">
+    <row r="938" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A938" s="1"/>
       <c r="B938" s="7"/>
       <c r="C938" s="7"/>
@@ -13608,7 +13658,7 @@
       <c r="K938" s="7"/>
       <c r="L938" s="1"/>
     </row>
-    <row r="939" ht="19.5" customHeight="1">
+    <row r="939" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A939" s="1"/>
       <c r="B939" s="7"/>
       <c r="C939" s="7"/>
@@ -13622,7 +13672,7 @@
       <c r="K939" s="7"/>
       <c r="L939" s="1"/>
     </row>
-    <row r="940" ht="19.5" customHeight="1">
+    <row r="940" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A940" s="1"/>
       <c r="B940" s="7"/>
       <c r="C940" s="7"/>
@@ -13636,7 +13686,7 @@
       <c r="K940" s="7"/>
       <c r="L940" s="1"/>
     </row>
-    <row r="941" ht="19.5" customHeight="1">
+    <row r="941" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A941" s="1"/>
       <c r="B941" s="7"/>
       <c r="C941" s="7"/>
@@ -13650,7 +13700,7 @@
       <c r="K941" s="7"/>
       <c r="L941" s="1"/>
     </row>
-    <row r="942" ht="19.5" customHeight="1">
+    <row r="942" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A942" s="1"/>
       <c r="B942" s="7"/>
       <c r="C942" s="7"/>
@@ -13664,7 +13714,7 @@
       <c r="K942" s="7"/>
       <c r="L942" s="1"/>
     </row>
-    <row r="943" ht="19.5" customHeight="1">
+    <row r="943" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A943" s="1"/>
       <c r="B943" s="7"/>
       <c r="C943" s="7"/>
@@ -13678,7 +13728,7 @@
       <c r="K943" s="7"/>
       <c r="L943" s="1"/>
     </row>
-    <row r="944" ht="19.5" customHeight="1">
+    <row r="944" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A944" s="1"/>
       <c r="B944" s="7"/>
       <c r="C944" s="7"/>
@@ -13692,7 +13742,7 @@
       <c r="K944" s="7"/>
       <c r="L944" s="1"/>
     </row>
-    <row r="945" ht="19.5" customHeight="1">
+    <row r="945" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A945" s="1"/>
       <c r="B945" s="7"/>
       <c r="C945" s="7"/>
@@ -13706,7 +13756,7 @@
       <c r="K945" s="7"/>
       <c r="L945" s="1"/>
     </row>
-    <row r="946" ht="19.5" customHeight="1">
+    <row r="946" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A946" s="1"/>
       <c r="B946" s="7"/>
       <c r="C946" s="7"/>
@@ -13720,7 +13770,7 @@
       <c r="K946" s="7"/>
       <c r="L946" s="1"/>
     </row>
-    <row r="947" ht="19.5" customHeight="1">
+    <row r="947" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A947" s="1"/>
       <c r="B947" s="7"/>
       <c r="C947" s="7"/>
@@ -13734,7 +13784,7 @@
       <c r="K947" s="7"/>
       <c r="L947" s="1"/>
     </row>
-    <row r="948" ht="19.5" customHeight="1">
+    <row r="948" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A948" s="1"/>
       <c r="B948" s="7"/>
       <c r="C948" s="7"/>
@@ -13748,7 +13798,7 @@
       <c r="K948" s="7"/>
       <c r="L948" s="1"/>
     </row>
-    <row r="949" ht="19.5" customHeight="1">
+    <row r="949" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A949" s="1"/>
       <c r="B949" s="7"/>
       <c r="C949" s="7"/>
@@ -13762,7 +13812,7 @@
       <c r="K949" s="7"/>
       <c r="L949" s="1"/>
     </row>
-    <row r="950" ht="19.5" customHeight="1">
+    <row r="950" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A950" s="1"/>
       <c r="B950" s="7"/>
       <c r="C950" s="7"/>
@@ -13776,7 +13826,7 @@
       <c r="K950" s="7"/>
       <c r="L950" s="1"/>
     </row>
-    <row r="951" ht="19.5" customHeight="1">
+    <row r="951" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A951" s="1"/>
       <c r="B951" s="7"/>
       <c r="C951" s="7"/>
@@ -13790,7 +13840,7 @@
       <c r="K951" s="7"/>
       <c r="L951" s="1"/>
     </row>
-    <row r="952" ht="19.5" customHeight="1">
+    <row r="952" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A952" s="1"/>
       <c r="B952" s="7"/>
       <c r="C952" s="7"/>
@@ -13804,7 +13854,7 @@
       <c r="K952" s="7"/>
       <c r="L952" s="1"/>
     </row>
-    <row r="953" ht="19.5" customHeight="1">
+    <row r="953" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A953" s="1"/>
       <c r="B953" s="7"/>
       <c r="C953" s="7"/>
@@ -13818,7 +13868,7 @@
       <c r="K953" s="7"/>
       <c r="L953" s="1"/>
     </row>
-    <row r="954" ht="19.5" customHeight="1">
+    <row r="954" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A954" s="1"/>
       <c r="B954" s="7"/>
       <c r="C954" s="7"/>
@@ -13832,7 +13882,7 @@
       <c r="K954" s="7"/>
       <c r="L954" s="1"/>
     </row>
-    <row r="955" ht="19.5" customHeight="1">
+    <row r="955" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A955" s="1"/>
       <c r="B955" s="7"/>
       <c r="C955" s="7"/>
@@ -13846,7 +13896,7 @@
       <c r="K955" s="7"/>
       <c r="L955" s="1"/>
     </row>
-    <row r="956" ht="19.5" customHeight="1">
+    <row r="956" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A956" s="1"/>
       <c r="B956" s="7"/>
       <c r="C956" s="7"/>
@@ -13860,7 +13910,7 @@
       <c r="K956" s="7"/>
       <c r="L956" s="1"/>
     </row>
-    <row r="957" ht="19.5" customHeight="1">
+    <row r="957" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A957" s="1"/>
       <c r="B957" s="7"/>
       <c r="C957" s="7"/>
@@ -13874,7 +13924,7 @@
       <c r="K957" s="7"/>
       <c r="L957" s="1"/>
     </row>
-    <row r="958" ht="19.5" customHeight="1">
+    <row r="958" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A958" s="1"/>
       <c r="B958" s="7"/>
       <c r="C958" s="7"/>
@@ -13888,7 +13938,7 @@
       <c r="K958" s="7"/>
       <c r="L958" s="1"/>
     </row>
-    <row r="959" ht="19.5" customHeight="1">
+    <row r="959" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A959" s="1"/>
       <c r="B959" s="7"/>
       <c r="C959" s="7"/>
@@ -13902,7 +13952,7 @@
       <c r="K959" s="7"/>
       <c r="L959" s="1"/>
     </row>
-    <row r="960" ht="19.5" customHeight="1">
+    <row r="960" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A960" s="1"/>
       <c r="B960" s="7"/>
       <c r="C960" s="7"/>
@@ -13916,7 +13966,7 @@
       <c r="K960" s="7"/>
       <c r="L960" s="1"/>
     </row>
-    <row r="961" ht="19.5" customHeight="1">
+    <row r="961" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A961" s="1"/>
       <c r="B961" s="7"/>
       <c r="C961" s="7"/>
@@ -13930,7 +13980,7 @@
       <c r="K961" s="7"/>
       <c r="L961" s="1"/>
     </row>
-    <row r="962" ht="19.5" customHeight="1">
+    <row r="962" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A962" s="1"/>
       <c r="B962" s="7"/>
       <c r="C962" s="7"/>
@@ -13944,7 +13994,7 @@
       <c r="K962" s="7"/>
       <c r="L962" s="1"/>
     </row>
-    <row r="963" ht="19.5" customHeight="1">
+    <row r="963" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A963" s="1"/>
       <c r="B963" s="7"/>
       <c r="C963" s="7"/>
@@ -13958,7 +14008,7 @@
       <c r="K963" s="7"/>
       <c r="L963" s="1"/>
     </row>
-    <row r="964" ht="19.5" customHeight="1">
+    <row r="964" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A964" s="1"/>
       <c r="B964" s="7"/>
       <c r="C964" s="7"/>
@@ -13972,7 +14022,7 @@
       <c r="K964" s="7"/>
       <c r="L964" s="1"/>
     </row>
-    <row r="965" ht="19.5" customHeight="1">
+    <row r="965" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A965" s="1"/>
       <c r="B965" s="7"/>
       <c r="C965" s="7"/>
@@ -13986,7 +14036,7 @@
       <c r="K965" s="7"/>
       <c r="L965" s="1"/>
     </row>
-    <row r="966" ht="19.5" customHeight="1">
+    <row r="966" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A966" s="1"/>
       <c r="B966" s="7"/>
       <c r="C966" s="7"/>
@@ -14000,7 +14050,7 @@
       <c r="K966" s="7"/>
       <c r="L966" s="1"/>
     </row>
-    <row r="967" ht="19.5" customHeight="1">
+    <row r="967" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A967" s="1"/>
       <c r="B967" s="7"/>
       <c r="C967" s="7"/>
@@ -14014,7 +14064,7 @@
       <c r="K967" s="7"/>
       <c r="L967" s="1"/>
     </row>
-    <row r="968" ht="19.5" customHeight="1">
+    <row r="968" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A968" s="1"/>
       <c r="B968" s="7"/>
       <c r="C968" s="7"/>
@@ -14028,7 +14078,7 @@
       <c r="K968" s="7"/>
       <c r="L968" s="1"/>
     </row>
-    <row r="969" ht="19.5" customHeight="1">
+    <row r="969" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A969" s="1"/>
       <c r="B969" s="7"/>
       <c r="C969" s="7"/>
@@ -14042,7 +14092,7 @@
       <c r="K969" s="7"/>
       <c r="L969" s="1"/>
     </row>
-    <row r="970" ht="19.5" customHeight="1">
+    <row r="970" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A970" s="1"/>
       <c r="B970" s="7"/>
       <c r="C970" s="7"/>
@@ -14056,7 +14106,7 @@
       <c r="K970" s="7"/>
       <c r="L970" s="1"/>
     </row>
-    <row r="971" ht="19.5" customHeight="1">
+    <row r="971" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A971" s="1"/>
       <c r="B971" s="7"/>
       <c r="C971" s="7"/>
@@ -14070,7 +14120,7 @@
       <c r="K971" s="7"/>
       <c r="L971" s="1"/>
     </row>
-    <row r="972" ht="19.5" customHeight="1">
+    <row r="972" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A972" s="1"/>
       <c r="B972" s="7"/>
       <c r="C972" s="7"/>
@@ -14084,7 +14134,7 @@
       <c r="K972" s="7"/>
       <c r="L972" s="1"/>
     </row>
-    <row r="973" ht="19.5" customHeight="1">
+    <row r="973" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A973" s="1"/>
       <c r="B973" s="7"/>
       <c r="C973" s="7"/>
@@ -14098,7 +14148,7 @@
       <c r="K973" s="7"/>
       <c r="L973" s="1"/>
     </row>
-    <row r="974" ht="19.5" customHeight="1">
+    <row r="974" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A974" s="1"/>
       <c r="B974" s="7"/>
       <c r="C974" s="7"/>
@@ -14112,7 +14162,7 @@
       <c r="K974" s="7"/>
       <c r="L974" s="1"/>
     </row>
-    <row r="975" ht="19.5" customHeight="1">
+    <row r="975" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A975" s="1"/>
       <c r="B975" s="7"/>
       <c r="C975" s="7"/>
@@ -14126,7 +14176,7 @@
       <c r="K975" s="7"/>
       <c r="L975" s="1"/>
     </row>
-    <row r="976" ht="19.5" customHeight="1">
+    <row r="976" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A976" s="1"/>
       <c r="B976" s="7"/>
       <c r="C976" s="7"/>
@@ -14140,7 +14190,7 @@
       <c r="K976" s="7"/>
       <c r="L976" s="1"/>
     </row>
-    <row r="977" ht="19.5" customHeight="1">
+    <row r="977" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A977" s="1"/>
       <c r="B977" s="7"/>
       <c r="C977" s="7"/>
@@ -14154,7 +14204,7 @@
       <c r="K977" s="7"/>
       <c r="L977" s="1"/>
     </row>
-    <row r="978" ht="19.5" customHeight="1">
+    <row r="978" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A978" s="1"/>
       <c r="B978" s="7"/>
       <c r="C978" s="7"/>
@@ -14168,7 +14218,7 @@
       <c r="K978" s="7"/>
       <c r="L978" s="1"/>
     </row>
-    <row r="979" ht="19.5" customHeight="1">
+    <row r="979" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A979" s="1"/>
       <c r="B979" s="7"/>
       <c r="C979" s="7"/>
@@ -14182,7 +14232,7 @@
       <c r="K979" s="7"/>
       <c r="L979" s="1"/>
     </row>
-    <row r="980" ht="19.5" customHeight="1">
+    <row r="980" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A980" s="1"/>
       <c r="B980" s="7"/>
       <c r="C980" s="7"/>
@@ -14196,7 +14246,7 @@
       <c r="K980" s="7"/>
       <c r="L980" s="1"/>
     </row>
-    <row r="981" ht="19.5" customHeight="1">
+    <row r="981" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A981" s="1"/>
       <c r="B981" s="7"/>
       <c r="C981" s="7"/>
@@ -14210,7 +14260,7 @@
       <c r="K981" s="7"/>
       <c r="L981" s="1"/>
     </row>
-    <row r="982" ht="19.5" customHeight="1">
+    <row r="982" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A982" s="1"/>
       <c r="B982" s="7"/>
       <c r="C982" s="7"/>
@@ -14224,7 +14274,7 @@
       <c r="K982" s="7"/>
       <c r="L982" s="1"/>
     </row>
-    <row r="983" ht="19.5" customHeight="1">
+    <row r="983" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A983" s="1"/>
       <c r="B983" s="7"/>
       <c r="C983" s="7"/>
@@ -14238,7 +14288,7 @@
       <c r="K983" s="7"/>
       <c r="L983" s="1"/>
     </row>
-    <row r="984" ht="19.5" customHeight="1">
+    <row r="984" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A984" s="1"/>
       <c r="B984" s="7"/>
       <c r="C984" s="7"/>
@@ -14252,7 +14302,7 @@
       <c r="K984" s="7"/>
       <c r="L984" s="1"/>
     </row>
-    <row r="985" ht="19.5" customHeight="1">
+    <row r="985" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A985" s="1"/>
       <c r="B985" s="7"/>
       <c r="C985" s="7"/>
@@ -14266,7 +14316,7 @@
       <c r="K985" s="7"/>
       <c r="L985" s="1"/>
     </row>
-    <row r="986" ht="19.5" customHeight="1">
+    <row r="986" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A986" s="1"/>
       <c r="B986" s="7"/>
       <c r="C986" s="7"/>
@@ -14280,7 +14330,7 @@
       <c r="K986" s="7"/>
       <c r="L986" s="1"/>
     </row>
-    <row r="987" ht="19.5" customHeight="1">
+    <row r="987" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A987" s="1"/>
       <c r="B987" s="7"/>
       <c r="C987" s="7"/>
@@ -14294,7 +14344,7 @@
       <c r="K987" s="7"/>
       <c r="L987" s="1"/>
     </row>
-    <row r="988" ht="19.5" customHeight="1">
+    <row r="988" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A988" s="1"/>
       <c r="B988" s="7"/>
       <c r="C988" s="7"/>
@@ -14308,7 +14358,7 @@
       <c r="K988" s="7"/>
       <c r="L988" s="1"/>
     </row>
-    <row r="989" ht="19.5" customHeight="1">
+    <row r="989" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A989" s="1"/>
       <c r="B989" s="7"/>
       <c r="C989" s="7"/>
@@ -14322,7 +14372,7 @@
       <c r="K989" s="7"/>
       <c r="L989" s="1"/>
     </row>
-    <row r="990" ht="19.5" customHeight="1">
+    <row r="990" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A990" s="1"/>
       <c r="B990" s="7"/>
       <c r="C990" s="7"/>
@@ -14336,7 +14386,7 @@
       <c r="K990" s="7"/>
       <c r="L990" s="1"/>
     </row>
-    <row r="991" ht="19.5" customHeight="1">
+    <row r="991" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A991" s="1"/>
       <c r="B991" s="7"/>
       <c r="C991" s="7"/>
@@ -14350,7 +14400,7 @@
       <c r="K991" s="7"/>
       <c r="L991" s="1"/>
     </row>
-    <row r="992" ht="19.5" customHeight="1">
+    <row r="992" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A992" s="1"/>
       <c r="B992" s="7"/>
       <c r="C992" s="7"/>
@@ -14364,7 +14414,7 @@
       <c r="K992" s="7"/>
       <c r="L992" s="1"/>
     </row>
-    <row r="993" ht="19.5" customHeight="1">
+    <row r="993" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A993" s="1"/>
       <c r="B993" s="7"/>
       <c r="C993" s="7"/>
@@ -14378,7 +14428,7 @@
       <c r="K993" s="7"/>
       <c r="L993" s="1"/>
     </row>
-    <row r="994" ht="19.5" customHeight="1">
+    <row r="994" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A994" s="1"/>
       <c r="B994" s="7"/>
       <c r="C994" s="7"/>
@@ -14392,7 +14442,7 @@
       <c r="K994" s="7"/>
       <c r="L994" s="1"/>
     </row>
-    <row r="995" ht="19.5" customHeight="1">
+    <row r="995" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A995" s="1"/>
       <c r="B995" s="7"/>
       <c r="C995" s="7"/>
@@ -14406,7 +14456,7 @@
       <c r="K995" s="7"/>
       <c r="L995" s="1"/>
     </row>
-    <row r="996" ht="19.5" customHeight="1">
+    <row r="996" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A996" s="1"/>
       <c r="B996" s="7"/>
       <c r="C996" s="7"/>
@@ -14420,7 +14470,7 @@
       <c r="K996" s="7"/>
       <c r="L996" s="1"/>
     </row>
-    <row r="997" ht="19.5" customHeight="1">
+    <row r="997" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A997" s="1"/>
       <c r="B997" s="7"/>
       <c r="C997" s="7"/>
@@ -14434,7 +14484,7 @@
       <c r="K997" s="7"/>
       <c r="L997" s="1"/>
     </row>
-    <row r="998" ht="19.5" customHeight="1">
+    <row r="998" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A998" s="1"/>
       <c r="B998" s="7"/>
       <c r="C998" s="7"/>
@@ -14448,7 +14498,7 @@
       <c r="K998" s="7"/>
       <c r="L998" s="1"/>
     </row>
-    <row r="999" ht="19.5" customHeight="1">
+    <row r="999" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A999" s="1"/>
       <c r="B999" s="7"/>
       <c r="C999" s="7"/>
@@ -14462,7 +14512,7 @@
       <c r="K999" s="7"/>
       <c r="L999" s="1"/>
     </row>
-    <row r="1000" ht="19.5" customHeight="1">
+    <row r="1000" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1000" s="1"/>
       <c r="B1000" s="7"/>
       <c r="C1000" s="7"/>
@@ -14477,7 +14527,7 @@
       <c r="L1000" s="1"/>
     </row>
   </sheetData>
-  <autoFilter ref="$B$2:$K$10"/>
+  <autoFilter ref="B2:K10"/>
   <mergeCells count="8">
     <mergeCell ref="B3:B6"/>
     <mergeCell ref="C3:C6"/>
@@ -14488,6 +14538,6 @@
     <mergeCell ref="D8:D9"/>
     <mergeCell ref="E8:E9"/>
   </mergeCells>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>